--- a/app/download_dir/system_files/шляпы_по каждому размеру.xlsx
+++ b/app/download_dir/system_files/шляпы_по каждому размеру.xlsx
@@ -14600,7 +14600,7 @@
     <row r="33" ht="13.8" customHeight="1" s="68">
       <c r="D33" s="41" t="inlineStr">
         <is>
-          <t>СНУД</t>
+          <t>ШАРФ-СНУД</t>
         </is>
       </c>
       <c r="E33" s="41" t="inlineStr">
@@ -16641,7 +16641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:E110"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.83984375" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="19.77" customWidth="1" style="41" min="2" max="2"/>
@@ -16650,6 +16650,7 @@
     <col width="29.63" customWidth="1" style="41" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="12.8" customHeight="1" s="68">
       <c r="B2" s="74" t="inlineStr">
         <is>
@@ -17799,7 +17800,7 @@
     <row r="33" ht="40.25" customFormat="1" customHeight="1" s="76">
       <c r="A33" s="79" t="inlineStr">
         <is>
-          <t>&lt;4070000032&gt; СНУД</t>
+          <t>&lt;4070000032&gt; ШАРФ-СНУД</t>
         </is>
       </c>
       <c r="B33" s="80" t="n"/>

--- a/app/download_dir/system_files/шляпы_по каждому размеру.xlsx
+++ b/app/download_dir/system_files/шляпы_по каждому размеру.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Данные" sheetId="1" state="visible" r:id="rId1"/>
@@ -253,7 +253,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="90">
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -508,6 +508,13 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -902,6 +909,7 @@
     <col width="17.78" customWidth="1" style="43" min="15" max="15"/>
     <col width="16" customWidth="1" style="43" min="16" max="16"/>
     <col width="25.96" customWidth="1" style="43" min="17" max="17"/>
+    <col width="20" customWidth="1" style="70" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="64.5" customFormat="1" customHeight="1" s="45">
@@ -984,6 +992,11 @@
 Действия документа
 Формат dd.mm.yyyy
 ( например 23.10.2023)</t>
+        </is>
+      </c>
+      <c r="R1" s="50" t="inlineStr">
+        <is>
+          <t>Вес в граммах</t>
         </is>
       </c>
       <c r="AME1" s="43" t="n"/>
@@ -1237,7 +1250,7 @@
       <c r="AMI5" s="43" t="n"/>
       <c r="AMJ5" s="43" t="n"/>
     </row>
-    <row r="6" ht="147" customFormat="1" customHeight="1" s="45">
+    <row r="6" ht="160" customFormat="1" customHeight="1" s="45">
       <c r="A6" s="56" t="inlineStr">
         <is>
           <t>КОД ТНВЭД (первые 4 цифры)</t>
@@ -1320,6 +1333,11 @@
       </c>
       <c r="P6" s="61" t="n"/>
       <c r="Q6" s="48" t="n"/>
+      <c r="R6" s="89" t="inlineStr">
+        <is>
+          <t>Обязательное поле: общий вес позиции, целое число больше 0. Просьба указать актуальный вес товара в ГРАММАХ для отчетности РОСПРИРОДНАДЗОР.</t>
+        </is>
+      </c>
       <c r="AME6" s="43" t="n"/>
       <c r="AMF6" s="43" t="n"/>
       <c r="AMG6" s="43" t="n"/>
@@ -1412,7 +1430,9 @@
           <t>23.12.2023</t>
         </is>
       </c>
-      <c r="R7" s="51" t="n"/>
+      <c r="R7" s="87" t="n">
+        <v>1000</v>
+      </c>
       <c r="S7" s="51" t="n"/>
       <c r="T7" s="51" t="n"/>
       <c r="U7" s="51" t="n"/>
@@ -1503,7 +1523,9 @@
       <c r="O8" s="67" t="n"/>
       <c r="P8" s="68" t="n"/>
       <c r="Q8" s="68" t="n"/>
-      <c r="R8" s="51" t="n"/>
+      <c r="R8" s="87" t="n">
+        <v>1000</v>
+      </c>
       <c r="S8" s="51" t="n"/>
       <c r="T8" s="51" t="n"/>
       <c r="U8" s="51" t="n"/>
@@ -1540,6 +1562,7 @@
       <c r="O9" s="69" t="n"/>
       <c r="P9" s="62" t="n"/>
       <c r="Q9" s="62" t="n"/>
+      <c r="R9" s="88" t="n"/>
       <c r="AME9" s="43" t="n"/>
       <c r="AMF9" s="43" t="n"/>
       <c r="AMG9" s="43" t="n"/>
@@ -1566,6 +1589,7 @@
       <c r="O10" s="69" t="n"/>
       <c r="P10" s="62" t="n"/>
       <c r="Q10" s="62" t="n"/>
+      <c r="R10" s="88" t="n"/>
       <c r="AME10" s="43" t="n"/>
       <c r="AMF10" s="43" t="n"/>
       <c r="AMG10" s="43" t="n"/>
@@ -1592,6 +1616,7 @@
       <c r="O11" s="69" t="n"/>
       <c r="P11" s="62" t="n"/>
       <c r="Q11" s="62" t="n"/>
+      <c r="R11" s="88" t="n"/>
       <c r="AME11" s="43" t="n"/>
       <c r="AMF11" s="43" t="n"/>
       <c r="AMG11" s="43" t="n"/>
@@ -1618,6 +1643,7 @@
       <c r="O12" s="69" t="n"/>
       <c r="P12" s="62" t="n"/>
       <c r="Q12" s="62" t="n"/>
+      <c r="R12" s="88" t="n"/>
       <c r="AME12" s="43" t="n"/>
       <c r="AMF12" s="43" t="n"/>
       <c r="AMG12" s="43" t="n"/>
@@ -1644,6 +1670,7 @@
       <c r="O13" s="69" t="n"/>
       <c r="P13" s="62" t="n"/>
       <c r="Q13" s="62" t="n"/>
+      <c r="R13" s="88" t="n"/>
       <c r="AME13" s="43" t="n"/>
       <c r="AMF13" s="43" t="n"/>
       <c r="AMG13" s="43" t="n"/>
@@ -1670,6 +1697,7 @@
       <c r="O14" s="69" t="n"/>
       <c r="P14" s="62" t="n"/>
       <c r="Q14" s="62" t="n"/>
+      <c r="R14" s="88" t="n"/>
       <c r="AME14" s="43" t="n"/>
       <c r="AMF14" s="43" t="n"/>
       <c r="AMG14" s="43" t="n"/>
@@ -1696,6 +1724,7 @@
       <c r="O15" s="69" t="n"/>
       <c r="P15" s="62" t="n"/>
       <c r="Q15" s="62" t="n"/>
+      <c r="R15" s="88" t="n"/>
       <c r="AME15" s="43" t="n"/>
       <c r="AMF15" s="43" t="n"/>
       <c r="AMG15" s="43" t="n"/>
@@ -1722,6 +1751,7 @@
       <c r="O16" s="69" t="n"/>
       <c r="P16" s="62" t="n"/>
       <c r="Q16" s="62" t="n"/>
+      <c r="R16" s="88" t="n"/>
       <c r="AME16" s="43" t="n"/>
       <c r="AMF16" s="43" t="n"/>
       <c r="AMG16" s="43" t="n"/>
@@ -1748,6 +1778,7 @@
       <c r="O17" s="69" t="n"/>
       <c r="P17" s="62" t="n"/>
       <c r="Q17" s="62" t="n"/>
+      <c r="R17" s="88" t="n"/>
       <c r="AME17" s="43" t="n"/>
       <c r="AMF17" s="43" t="n"/>
       <c r="AMG17" s="43" t="n"/>
@@ -1774,6 +1805,7 @@
       <c r="O18" s="69" t="n"/>
       <c r="P18" s="62" t="n"/>
       <c r="Q18" s="62" t="n"/>
+      <c r="R18" s="88" t="n"/>
       <c r="AME18" s="43" t="n"/>
       <c r="AMF18" s="43" t="n"/>
       <c r="AMG18" s="43" t="n"/>
@@ -1800,6 +1832,7 @@
       <c r="O19" s="69" t="n"/>
       <c r="P19" s="62" t="n"/>
       <c r="Q19" s="62" t="n"/>
+      <c r="R19" s="88" t="n"/>
       <c r="AME19" s="43" t="n"/>
       <c r="AMF19" s="43" t="n"/>
       <c r="AMG19" s="43" t="n"/>
@@ -1826,6 +1859,7 @@
       <c r="O20" s="69" t="n"/>
       <c r="P20" s="62" t="n"/>
       <c r="Q20" s="62" t="n"/>
+      <c r="R20" s="88" t="n"/>
       <c r="AME20" s="43" t="n"/>
       <c r="AMF20" s="43" t="n"/>
       <c r="AMG20" s="43" t="n"/>
@@ -1852,6 +1886,7 @@
       <c r="O21" s="69" t="n"/>
       <c r="P21" s="62" t="n"/>
       <c r="Q21" s="62" t="n"/>
+      <c r="R21" s="88" t="n"/>
       <c r="AME21" s="43" t="n"/>
       <c r="AMF21" s="43" t="n"/>
       <c r="AMG21" s="43" t="n"/>
@@ -1878,6 +1913,7 @@
       <c r="O22" s="69" t="n"/>
       <c r="P22" s="62" t="n"/>
       <c r="Q22" s="62" t="n"/>
+      <c r="R22" s="88" t="n"/>
       <c r="AME22" s="43" t="n"/>
       <c r="AMF22" s="43" t="n"/>
       <c r="AMG22" s="43" t="n"/>
@@ -1904,6 +1940,7 @@
       <c r="O23" s="69" t="n"/>
       <c r="P23" s="62" t="n"/>
       <c r="Q23" s="62" t="n"/>
+      <c r="R23" s="88" t="n"/>
       <c r="AME23" s="43" t="n"/>
       <c r="AMF23" s="43" t="n"/>
       <c r="AMG23" s="43" t="n"/>
@@ -1930,6 +1967,7 @@
       <c r="O24" s="69" t="n"/>
       <c r="P24" s="62" t="n"/>
       <c r="Q24" s="62" t="n"/>
+      <c r="R24" s="88" t="n"/>
       <c r="AME24" s="43" t="n"/>
       <c r="AMF24" s="43" t="n"/>
       <c r="AMG24" s="43" t="n"/>
@@ -1956,6 +1994,7 @@
       <c r="O25" s="69" t="n"/>
       <c r="P25" s="62" t="n"/>
       <c r="Q25" s="62" t="n"/>
+      <c r="R25" s="88" t="n"/>
       <c r="AME25" s="43" t="n"/>
       <c r="AMF25" s="43" t="n"/>
       <c r="AMG25" s="43" t="n"/>
@@ -1982,6 +2021,7 @@
       <c r="O26" s="69" t="n"/>
       <c r="P26" s="62" t="n"/>
       <c r="Q26" s="62" t="n"/>
+      <c r="R26" s="88" t="n"/>
       <c r="AME26" s="43" t="n"/>
       <c r="AMF26" s="43" t="n"/>
       <c r="AMG26" s="43" t="n"/>
@@ -2008,6 +2048,7 @@
       <c r="O27" s="69" t="n"/>
       <c r="P27" s="62" t="n"/>
       <c r="Q27" s="62" t="n"/>
+      <c r="R27" s="88" t="n"/>
       <c r="AME27" s="43" t="n"/>
       <c r="AMF27" s="43" t="n"/>
       <c r="AMG27" s="43" t="n"/>
@@ -2034,6 +2075,7 @@
       <c r="O28" s="69" t="n"/>
       <c r="P28" s="62" t="n"/>
       <c r="Q28" s="62" t="n"/>
+      <c r="R28" s="88" t="n"/>
       <c r="AME28" s="43" t="n"/>
       <c r="AMF28" s="43" t="n"/>
       <c r="AMG28" s="43" t="n"/>
@@ -2060,6 +2102,7 @@
       <c r="O29" s="69" t="n"/>
       <c r="P29" s="62" t="n"/>
       <c r="Q29" s="62" t="n"/>
+      <c r="R29" s="88" t="n"/>
       <c r="AME29" s="43" t="n"/>
       <c r="AMF29" s="43" t="n"/>
       <c r="AMG29" s="43" t="n"/>
@@ -2086,6 +2129,7 @@
       <c r="O30" s="69" t="n"/>
       <c r="P30" s="62" t="n"/>
       <c r="Q30" s="62" t="n"/>
+      <c r="R30" s="88" t="n"/>
       <c r="AME30" s="43" t="n"/>
       <c r="AMF30" s="43" t="n"/>
       <c r="AMG30" s="43" t="n"/>
@@ -2112,6 +2156,7 @@
       <c r="O31" s="69" t="n"/>
       <c r="P31" s="62" t="n"/>
       <c r="Q31" s="62" t="n"/>
+      <c r="R31" s="88" t="n"/>
       <c r="AME31" s="43" t="n"/>
       <c r="AMF31" s="43" t="n"/>
       <c r="AMG31" s="43" t="n"/>
@@ -2138,6 +2183,7 @@
       <c r="O32" s="69" t="n"/>
       <c r="P32" s="62" t="n"/>
       <c r="Q32" s="62" t="n"/>
+      <c r="R32" s="88" t="n"/>
       <c r="AME32" s="43" t="n"/>
       <c r="AMF32" s="43" t="n"/>
       <c r="AMG32" s="43" t="n"/>
@@ -2164,6 +2210,7 @@
       <c r="O33" s="69" t="n"/>
       <c r="P33" s="62" t="n"/>
       <c r="Q33" s="62" t="n"/>
+      <c r="R33" s="88" t="n"/>
       <c r="AME33" s="43" t="n"/>
       <c r="AMF33" s="43" t="n"/>
       <c r="AMG33" s="43" t="n"/>
@@ -2190,6 +2237,7 @@
       <c r="O34" s="69" t="n"/>
       <c r="P34" s="62" t="n"/>
       <c r="Q34" s="62" t="n"/>
+      <c r="R34" s="88" t="n"/>
       <c r="AME34" s="43" t="n"/>
       <c r="AMF34" s="43" t="n"/>
       <c r="AMG34" s="43" t="n"/>
@@ -2216,6 +2264,7 @@
       <c r="O35" s="69" t="n"/>
       <c r="P35" s="62" t="n"/>
       <c r="Q35" s="62" t="n"/>
+      <c r="R35" s="88" t="n"/>
       <c r="AME35" s="43" t="n"/>
       <c r="AMF35" s="43" t="n"/>
       <c r="AMG35" s="43" t="n"/>
@@ -2242,6 +2291,7 @@
       <c r="O36" s="69" t="n"/>
       <c r="P36" s="62" t="n"/>
       <c r="Q36" s="62" t="n"/>
+      <c r="R36" s="88" t="n"/>
       <c r="AME36" s="43" t="n"/>
       <c r="AMF36" s="43" t="n"/>
       <c r="AMG36" s="43" t="n"/>
@@ -2268,6 +2318,7 @@
       <c r="O37" s="69" t="n"/>
       <c r="P37" s="62" t="n"/>
       <c r="Q37" s="62" t="n"/>
+      <c r="R37" s="88" t="n"/>
       <c r="AME37" s="43" t="n"/>
       <c r="AMF37" s="43" t="n"/>
       <c r="AMG37" s="43" t="n"/>
@@ -2294,6 +2345,7 @@
       <c r="O38" s="69" t="n"/>
       <c r="P38" s="62" t="n"/>
       <c r="Q38" s="62" t="n"/>
+      <c r="R38" s="88" t="n"/>
       <c r="AME38" s="43" t="n"/>
       <c r="AMF38" s="43" t="n"/>
       <c r="AMG38" s="43" t="n"/>
@@ -2320,6 +2372,7 @@
       <c r="O39" s="69" t="n"/>
       <c r="P39" s="62" t="n"/>
       <c r="Q39" s="62" t="n"/>
+      <c r="R39" s="88" t="n"/>
       <c r="AME39" s="43" t="n"/>
       <c r="AMF39" s="43" t="n"/>
       <c r="AMG39" s="43" t="n"/>
@@ -2346,6 +2399,7 @@
       <c r="O40" s="69" t="n"/>
       <c r="P40" s="62" t="n"/>
       <c r="Q40" s="62" t="n"/>
+      <c r="R40" s="88" t="n"/>
       <c r="AME40" s="43" t="n"/>
       <c r="AMF40" s="43" t="n"/>
       <c r="AMG40" s="43" t="n"/>
@@ -2372,6 +2426,7 @@
       <c r="O41" s="69" t="n"/>
       <c r="P41" s="62" t="n"/>
       <c r="Q41" s="62" t="n"/>
+      <c r="R41" s="88" t="n"/>
       <c r="AME41" s="43" t="n"/>
       <c r="AMF41" s="43" t="n"/>
       <c r="AMG41" s="43" t="n"/>
@@ -2398,6 +2453,7 @@
       <c r="O42" s="69" t="n"/>
       <c r="P42" s="62" t="n"/>
       <c r="Q42" s="62" t="n"/>
+      <c r="R42" s="88" t="n"/>
       <c r="AME42" s="43" t="n"/>
       <c r="AMF42" s="43" t="n"/>
       <c r="AMG42" s="43" t="n"/>
@@ -2424,6 +2480,7 @@
       <c r="O43" s="69" t="n"/>
       <c r="P43" s="62" t="n"/>
       <c r="Q43" s="62" t="n"/>
+      <c r="R43" s="88" t="n"/>
       <c r="AME43" s="43" t="n"/>
       <c r="AMF43" s="43" t="n"/>
       <c r="AMG43" s="43" t="n"/>
@@ -2450,6 +2507,7 @@
       <c r="O44" s="69" t="n"/>
       <c r="P44" s="62" t="n"/>
       <c r="Q44" s="62" t="n"/>
+      <c r="R44" s="88" t="n"/>
       <c r="AME44" s="43" t="n"/>
       <c r="AMF44" s="43" t="n"/>
       <c r="AMG44" s="43" t="n"/>
@@ -2476,6 +2534,7 @@
       <c r="O45" s="69" t="n"/>
       <c r="P45" s="62" t="n"/>
       <c r="Q45" s="62" t="n"/>
+      <c r="R45" s="88" t="n"/>
       <c r="AME45" s="43" t="n"/>
       <c r="AMF45" s="43" t="n"/>
       <c r="AMG45" s="43" t="n"/>
@@ -2496,6 +2555,7 @@
       <c r="O46" s="69" t="n"/>
       <c r="P46" s="62" t="n"/>
       <c r="Q46" s="62" t="n"/>
+      <c r="R46" s="88" t="n"/>
     </row>
     <row r="47" ht="12.75" customHeight="1" s="70">
       <c r="F47" s="66" t="n"/>
@@ -2510,6 +2570,7 @@
       <c r="O47" s="69" t="n"/>
       <c r="P47" s="62" t="n"/>
       <c r="Q47" s="62" t="n"/>
+      <c r="R47" s="88" t="n"/>
     </row>
     <row r="48" ht="12.75" customHeight="1" s="70">
       <c r="F48" s="66" t="n"/>
@@ -2524,6 +2585,7 @@
       <c r="O48" s="69" t="n"/>
       <c r="P48" s="62" t="n"/>
       <c r="Q48" s="62" t="n"/>
+      <c r="R48" s="88" t="n"/>
     </row>
     <row r="49" ht="12.75" customHeight="1" s="70">
       <c r="F49" s="66" t="n"/>
@@ -2538,6 +2600,7 @@
       <c r="O49" s="69" t="n"/>
       <c r="P49" s="62" t="n"/>
       <c r="Q49" s="62" t="n"/>
+      <c r="R49" s="88" t="n"/>
     </row>
     <row r="50" ht="12.75" customHeight="1" s="70">
       <c r="F50" s="66" t="n"/>
@@ -2552,6 +2615,7 @@
       <c r="O50" s="69" t="n"/>
       <c r="P50" s="62" t="n"/>
       <c r="Q50" s="62" t="n"/>
+      <c r="R50" s="88" t="n"/>
     </row>
     <row r="51" ht="12.75" customHeight="1" s="70">
       <c r="F51" s="66" t="n"/>
@@ -2566,6 +2630,7 @@
       <c r="O51" s="69" t="n"/>
       <c r="P51" s="62" t="n"/>
       <c r="Q51" s="62" t="n"/>
+      <c r="R51" s="88" t="n"/>
     </row>
     <row r="52" ht="12.75" customHeight="1" s="70">
       <c r="F52" s="66" t="n"/>
@@ -2580,6 +2645,7 @@
       <c r="O52" s="69" t="n"/>
       <c r="P52" s="62" t="n"/>
       <c r="Q52" s="62" t="n"/>
+      <c r="R52" s="88" t="n"/>
     </row>
     <row r="53" ht="12.75" customHeight="1" s="70">
       <c r="F53" s="66" t="n"/>
@@ -2594,6 +2660,7 @@
       <c r="O53" s="69" t="n"/>
       <c r="P53" s="62" t="n"/>
       <c r="Q53" s="62" t="n"/>
+      <c r="R53" s="88" t="n"/>
     </row>
     <row r="54" ht="12.75" customHeight="1" s="70">
       <c r="F54" s="66" t="n"/>
@@ -2608,6 +2675,7 @@
       <c r="O54" s="69" t="n"/>
       <c r="P54" s="62" t="n"/>
       <c r="Q54" s="62" t="n"/>
+      <c r="R54" s="88" t="n"/>
     </row>
     <row r="55" ht="12.75" customHeight="1" s="70">
       <c r="F55" s="66" t="n"/>
@@ -2622,6 +2690,7 @@
       <c r="O55" s="69" t="n"/>
       <c r="P55" s="62" t="n"/>
       <c r="Q55" s="62" t="n"/>
+      <c r="R55" s="88" t="n"/>
     </row>
     <row r="56" ht="12.75" customHeight="1" s="70">
       <c r="F56" s="66" t="n"/>
@@ -2636,6 +2705,7 @@
       <c r="O56" s="69" t="n"/>
       <c r="P56" s="62" t="n"/>
       <c r="Q56" s="62" t="n"/>
+      <c r="R56" s="88" t="n"/>
     </row>
     <row r="57" ht="12.75" customHeight="1" s="70">
       <c r="F57" s="66" t="n"/>
@@ -2650,6 +2720,7 @@
       <c r="O57" s="69" t="n"/>
       <c r="P57" s="62" t="n"/>
       <c r="Q57" s="62" t="n"/>
+      <c r="R57" s="88" t="n"/>
     </row>
     <row r="58" ht="12.75" customHeight="1" s="70">
       <c r="F58" s="66" t="n"/>
@@ -2664,6 +2735,7 @@
       <c r="O58" s="69" t="n"/>
       <c r="P58" s="62" t="n"/>
       <c r="Q58" s="62" t="n"/>
+      <c r="R58" s="88" t="n"/>
     </row>
     <row r="59" ht="12.75" customHeight="1" s="70">
       <c r="F59" s="66" t="n"/>
@@ -2678,6 +2750,7 @@
       <c r="O59" s="69" t="n"/>
       <c r="P59" s="62" t="n"/>
       <c r="Q59" s="62" t="n"/>
+      <c r="R59" s="88" t="n"/>
     </row>
     <row r="60" ht="12.75" customHeight="1" s="70">
       <c r="F60" s="66" t="n"/>
@@ -2692,6 +2765,7 @@
       <c r="O60" s="69" t="n"/>
       <c r="P60" s="62" t="n"/>
       <c r="Q60" s="62" t="n"/>
+      <c r="R60" s="88" t="n"/>
     </row>
     <row r="61" ht="12.75" customHeight="1" s="70">
       <c r="F61" s="66" t="n"/>
@@ -2706,6 +2780,7 @@
       <c r="O61" s="69" t="n"/>
       <c r="P61" s="62" t="n"/>
       <c r="Q61" s="62" t="n"/>
+      <c r="R61" s="88" t="n"/>
     </row>
     <row r="62" ht="12.75" customHeight="1" s="70">
       <c r="F62" s="66" t="n"/>
@@ -2720,6 +2795,7 @@
       <c r="O62" s="69" t="n"/>
       <c r="P62" s="62" t="n"/>
       <c r="Q62" s="62" t="n"/>
+      <c r="R62" s="88" t="n"/>
     </row>
     <row r="63" ht="12.75" customHeight="1" s="70">
       <c r="F63" s="66" t="n"/>
@@ -2734,6 +2810,7 @@
       <c r="O63" s="69" t="n"/>
       <c r="P63" s="62" t="n"/>
       <c r="Q63" s="62" t="n"/>
+      <c r="R63" s="88" t="n"/>
     </row>
     <row r="64" ht="12.75" customHeight="1" s="70">
       <c r="F64" s="66" t="n"/>
@@ -2748,6 +2825,7 @@
       <c r="O64" s="69" t="n"/>
       <c r="P64" s="62" t="n"/>
       <c r="Q64" s="62" t="n"/>
+      <c r="R64" s="88" t="n"/>
     </row>
     <row r="65" ht="12.75" customHeight="1" s="70">
       <c r="F65" s="66" t="n"/>
@@ -2762,6 +2840,7 @@
       <c r="O65" s="69" t="n"/>
       <c r="P65" s="62" t="n"/>
       <c r="Q65" s="62" t="n"/>
+      <c r="R65" s="88" t="n"/>
     </row>
     <row r="66" ht="12.75" customHeight="1" s="70">
       <c r="F66" s="66" t="n"/>
@@ -2776,6 +2855,7 @@
       <c r="O66" s="69" t="n"/>
       <c r="P66" s="62" t="n"/>
       <c r="Q66" s="62" t="n"/>
+      <c r="R66" s="88" t="n"/>
     </row>
     <row r="67" ht="12.75" customHeight="1" s="70">
       <c r="F67" s="66" t="n"/>
@@ -2790,6 +2870,7 @@
       <c r="O67" s="69" t="n"/>
       <c r="P67" s="62" t="n"/>
       <c r="Q67" s="62" t="n"/>
+      <c r="R67" s="88" t="n"/>
     </row>
     <row r="68" ht="12.75" customHeight="1" s="70">
       <c r="F68" s="66" t="n"/>
@@ -2804,6 +2885,7 @@
       <c r="O68" s="69" t="n"/>
       <c r="P68" s="62" t="n"/>
       <c r="Q68" s="62" t="n"/>
+      <c r="R68" s="88" t="n"/>
     </row>
     <row r="69" ht="12.75" customHeight="1" s="70">
       <c r="F69" s="66" t="n"/>
@@ -2818,6 +2900,7 @@
       <c r="O69" s="69" t="n"/>
       <c r="P69" s="62" t="n"/>
       <c r="Q69" s="62" t="n"/>
+      <c r="R69" s="88" t="n"/>
     </row>
     <row r="70" ht="12.75" customHeight="1" s="70">
       <c r="F70" s="66" t="n"/>
@@ -2832,6 +2915,7 @@
       <c r="O70" s="69" t="n"/>
       <c r="P70" s="62" t="n"/>
       <c r="Q70" s="62" t="n"/>
+      <c r="R70" s="88" t="n"/>
     </row>
     <row r="71" ht="12.75" customHeight="1" s="70">
       <c r="F71" s="66" t="n"/>
@@ -2846,6 +2930,7 @@
       <c r="O71" s="69" t="n"/>
       <c r="P71" s="62" t="n"/>
       <c r="Q71" s="62" t="n"/>
+      <c r="R71" s="88" t="n"/>
     </row>
     <row r="72" ht="12.75" customHeight="1" s="70">
       <c r="F72" s="66" t="n"/>
@@ -2860,6 +2945,7 @@
       <c r="O72" s="69" t="n"/>
       <c r="P72" s="62" t="n"/>
       <c r="Q72" s="62" t="n"/>
+      <c r="R72" s="88" t="n"/>
     </row>
     <row r="73" ht="12.75" customHeight="1" s="70">
       <c r="F73" s="66" t="n"/>
@@ -2874,6 +2960,7 @@
       <c r="O73" s="69" t="n"/>
       <c r="P73" s="62" t="n"/>
       <c r="Q73" s="62" t="n"/>
+      <c r="R73" s="88" t="n"/>
     </row>
     <row r="74" ht="12.75" customHeight="1" s="70">
       <c r="F74" s="66" t="n"/>
@@ -2888,6 +2975,7 @@
       <c r="O74" s="69" t="n"/>
       <c r="P74" s="62" t="n"/>
       <c r="Q74" s="62" t="n"/>
+      <c r="R74" s="88" t="n"/>
     </row>
     <row r="75" ht="12.75" customHeight="1" s="70">
       <c r="F75" s="66" t="n"/>
@@ -2902,6 +2990,7 @@
       <c r="O75" s="69" t="n"/>
       <c r="P75" s="62" t="n"/>
       <c r="Q75" s="62" t="n"/>
+      <c r="R75" s="88" t="n"/>
     </row>
     <row r="76" ht="12.75" customHeight="1" s="70">
       <c r="F76" s="66" t="n"/>
@@ -2916,6 +3005,7 @@
       <c r="O76" s="69" t="n"/>
       <c r="P76" s="62" t="n"/>
       <c r="Q76" s="62" t="n"/>
+      <c r="R76" s="88" t="n"/>
     </row>
     <row r="77" ht="12.75" customHeight="1" s="70">
       <c r="F77" s="66" t="n"/>
@@ -2930,6 +3020,7 @@
       <c r="O77" s="69" t="n"/>
       <c r="P77" s="62" t="n"/>
       <c r="Q77" s="62" t="n"/>
+      <c r="R77" s="88" t="n"/>
     </row>
     <row r="78" ht="12.75" customHeight="1" s="70">
       <c r="F78" s="66" t="n"/>
@@ -2944,6 +3035,7 @@
       <c r="O78" s="69" t="n"/>
       <c r="P78" s="62" t="n"/>
       <c r="Q78" s="62" t="n"/>
+      <c r="R78" s="88" t="n"/>
     </row>
     <row r="79" ht="12.75" customHeight="1" s="70">
       <c r="F79" s="66" t="n"/>
@@ -2958,6 +3050,7 @@
       <c r="O79" s="69" t="n"/>
       <c r="P79" s="62" t="n"/>
       <c r="Q79" s="62" t="n"/>
+      <c r="R79" s="88" t="n"/>
     </row>
     <row r="80" ht="12.75" customHeight="1" s="70">
       <c r="F80" s="66" t="n"/>
@@ -2972,6 +3065,7 @@
       <c r="O80" s="69" t="n"/>
       <c r="P80" s="62" t="n"/>
       <c r="Q80" s="62" t="n"/>
+      <c r="R80" s="88" t="n"/>
     </row>
     <row r="81" ht="12.75" customHeight="1" s="70">
       <c r="F81" s="66" t="n"/>
@@ -2986,6 +3080,7 @@
       <c r="O81" s="69" t="n"/>
       <c r="P81" s="62" t="n"/>
       <c r="Q81" s="62" t="n"/>
+      <c r="R81" s="88" t="n"/>
     </row>
     <row r="82" ht="12.75" customHeight="1" s="70">
       <c r="F82" s="66" t="n"/>
@@ -3000,6 +3095,7 @@
       <c r="O82" s="69" t="n"/>
       <c r="P82" s="62" t="n"/>
       <c r="Q82" s="62" t="n"/>
+      <c r="R82" s="88" t="n"/>
     </row>
     <row r="83" ht="12.75" customHeight="1" s="70">
       <c r="F83" s="66" t="n"/>
@@ -3014,6 +3110,7 @@
       <c r="O83" s="69" t="n"/>
       <c r="P83" s="62" t="n"/>
       <c r="Q83" s="62" t="n"/>
+      <c r="R83" s="88" t="n"/>
     </row>
     <row r="84" ht="12.75" customHeight="1" s="70">
       <c r="F84" s="66" t="n"/>
@@ -3028,6 +3125,7 @@
       <c r="O84" s="69" t="n"/>
       <c r="P84" s="62" t="n"/>
       <c r="Q84" s="62" t="n"/>
+      <c r="R84" s="88" t="n"/>
     </row>
     <row r="85" ht="12.75" customHeight="1" s="70">
       <c r="F85" s="66" t="n"/>
@@ -3042,6 +3140,7 @@
       <c r="O85" s="69" t="n"/>
       <c r="P85" s="62" t="n"/>
       <c r="Q85" s="62" t="n"/>
+      <c r="R85" s="88" t="n"/>
     </row>
     <row r="86" ht="12.75" customHeight="1" s="70">
       <c r="F86" s="66" t="n"/>
@@ -3056,6 +3155,7 @@
       <c r="O86" s="69" t="n"/>
       <c r="P86" s="62" t="n"/>
       <c r="Q86" s="62" t="n"/>
+      <c r="R86" s="88" t="n"/>
     </row>
     <row r="87" ht="12.75" customHeight="1" s="70">
       <c r="F87" s="66" t="n"/>
@@ -3070,6 +3170,7 @@
       <c r="O87" s="69" t="n"/>
       <c r="P87" s="62" t="n"/>
       <c r="Q87" s="62" t="n"/>
+      <c r="R87" s="88" t="n"/>
     </row>
     <row r="88" ht="12.75" customHeight="1" s="70">
       <c r="F88" s="66" t="n"/>
@@ -3084,6 +3185,7 @@
       <c r="O88" s="69" t="n"/>
       <c r="P88" s="62" t="n"/>
       <c r="Q88" s="62" t="n"/>
+      <c r="R88" s="88" t="n"/>
     </row>
     <row r="89" ht="12.75" customHeight="1" s="70">
       <c r="F89" s="66" t="n"/>
@@ -3098,6 +3200,7 @@
       <c r="O89" s="69" t="n"/>
       <c r="P89" s="62" t="n"/>
       <c r="Q89" s="62" t="n"/>
+      <c r="R89" s="88" t="n"/>
     </row>
     <row r="90" ht="12.75" customHeight="1" s="70">
       <c r="F90" s="66" t="n"/>
@@ -3112,6 +3215,7 @@
       <c r="O90" s="69" t="n"/>
       <c r="P90" s="62" t="n"/>
       <c r="Q90" s="62" t="n"/>
+      <c r="R90" s="88" t="n"/>
     </row>
     <row r="91" ht="12.75" customHeight="1" s="70">
       <c r="F91" s="66" t="n"/>
@@ -3126,6 +3230,7 @@
       <c r="O91" s="69" t="n"/>
       <c r="P91" s="62" t="n"/>
       <c r="Q91" s="62" t="n"/>
+      <c r="R91" s="88" t="n"/>
     </row>
     <row r="92" ht="12.75" customHeight="1" s="70">
       <c r="F92" s="66" t="n"/>
@@ -3140,6 +3245,7 @@
       <c r="O92" s="69" t="n"/>
       <c r="P92" s="62" t="n"/>
       <c r="Q92" s="62" t="n"/>
+      <c r="R92" s="88" t="n"/>
     </row>
     <row r="93" ht="12.75" customHeight="1" s="70">
       <c r="F93" s="66" t="n"/>
@@ -3154,6 +3260,7 @@
       <c r="O93" s="69" t="n"/>
       <c r="P93" s="62" t="n"/>
       <c r="Q93" s="62" t="n"/>
+      <c r="R93" s="88" t="n"/>
     </row>
     <row r="94" ht="12.75" customHeight="1" s="70">
       <c r="F94" s="66" t="n"/>
@@ -3168,6 +3275,7 @@
       <c r="O94" s="69" t="n"/>
       <c r="P94" s="62" t="n"/>
       <c r="Q94" s="62" t="n"/>
+      <c r="R94" s="88" t="n"/>
     </row>
     <row r="95" ht="12.75" customHeight="1" s="70">
       <c r="F95" s="66" t="n"/>
@@ -3182,6 +3290,7 @@
       <c r="O95" s="69" t="n"/>
       <c r="P95" s="62" t="n"/>
       <c r="Q95" s="62" t="n"/>
+      <c r="R95" s="88" t="n"/>
     </row>
     <row r="96" ht="12.75" customHeight="1" s="70">
       <c r="F96" s="66" t="n"/>
@@ -3196,6 +3305,7 @@
       <c r="O96" s="69" t="n"/>
       <c r="P96" s="62" t="n"/>
       <c r="Q96" s="62" t="n"/>
+      <c r="R96" s="88" t="n"/>
     </row>
     <row r="97" ht="12.75" customHeight="1" s="70">
       <c r="F97" s="66" t="n"/>
@@ -3210,6 +3320,7 @@
       <c r="O97" s="69" t="n"/>
       <c r="P97" s="62" t="n"/>
       <c r="Q97" s="62" t="n"/>
+      <c r="R97" s="88" t="n"/>
     </row>
     <row r="98" ht="12.75" customHeight="1" s="70">
       <c r="F98" s="66" t="n"/>
@@ -3224,6 +3335,7 @@
       <c r="O98" s="69" t="n"/>
       <c r="P98" s="62" t="n"/>
       <c r="Q98" s="62" t="n"/>
+      <c r="R98" s="88" t="n"/>
     </row>
     <row r="99" ht="12.75" customHeight="1" s="70">
       <c r="F99" s="66" t="n"/>
@@ -3238,6 +3350,7 @@
       <c r="O99" s="69" t="n"/>
       <c r="P99" s="62" t="n"/>
       <c r="Q99" s="62" t="n"/>
+      <c r="R99" s="88" t="n"/>
     </row>
     <row r="100" ht="12.75" customHeight="1" s="70">
       <c r="F100" s="66" t="n"/>
@@ -3252,6 +3365,7 @@
       <c r="O100" s="69" t="n"/>
       <c r="P100" s="62" t="n"/>
       <c r="Q100" s="62" t="n"/>
+      <c r="R100" s="88" t="n"/>
     </row>
     <row r="101" ht="12.75" customHeight="1" s="70">
       <c r="F101" s="66" t="n"/>
@@ -3266,6 +3380,7 @@
       <c r="O101" s="69" t="n"/>
       <c r="P101" s="62" t="n"/>
       <c r="Q101" s="62" t="n"/>
+      <c r="R101" s="88" t="n"/>
     </row>
     <row r="102" ht="12.75" customHeight="1" s="70">
       <c r="F102" s="66" t="n"/>
@@ -3280,6 +3395,7 @@
       <c r="O102" s="69" t="n"/>
       <c r="P102" s="62" t="n"/>
       <c r="Q102" s="62" t="n"/>
+      <c r="R102" s="88" t="n"/>
     </row>
     <row r="103" ht="12.75" customHeight="1" s="70">
       <c r="F103" s="66" t="n"/>
@@ -3294,6 +3410,7 @@
       <c r="O103" s="69" t="n"/>
       <c r="P103" s="62" t="n"/>
       <c r="Q103" s="62" t="n"/>
+      <c r="R103" s="88" t="n"/>
     </row>
     <row r="104" ht="12.75" customHeight="1" s="70">
       <c r="F104" s="66" t="n"/>
@@ -3308,6 +3425,7 @@
       <c r="O104" s="69" t="n"/>
       <c r="P104" s="62" t="n"/>
       <c r="Q104" s="62" t="n"/>
+      <c r="R104" s="88" t="n"/>
     </row>
     <row r="105" ht="12.75" customHeight="1" s="70">
       <c r="F105" s="66" t="n"/>
@@ -3322,6 +3440,7 @@
       <c r="O105" s="69" t="n"/>
       <c r="P105" s="62" t="n"/>
       <c r="Q105" s="62" t="n"/>
+      <c r="R105" s="88" t="n"/>
     </row>
     <row r="106" ht="12.75" customHeight="1" s="70">
       <c r="F106" s="66" t="n"/>
@@ -3336,6 +3455,7 @@
       <c r="O106" s="69" t="n"/>
       <c r="P106" s="62" t="n"/>
       <c r="Q106" s="62" t="n"/>
+      <c r="R106" s="88" t="n"/>
     </row>
     <row r="107" ht="12.75" customHeight="1" s="70">
       <c r="F107" s="66" t="n"/>
@@ -3350,6 +3470,7 @@
       <c r="O107" s="69" t="n"/>
       <c r="P107" s="62" t="n"/>
       <c r="Q107" s="62" t="n"/>
+      <c r="R107" s="88" t="n"/>
     </row>
     <row r="108" ht="12.75" customHeight="1" s="70">
       <c r="F108" s="66" t="n"/>
@@ -3364,6 +3485,7 @@
       <c r="O108" s="69" t="n"/>
       <c r="P108" s="62" t="n"/>
       <c r="Q108" s="62" t="n"/>
+      <c r="R108" s="88" t="n"/>
     </row>
     <row r="109" ht="12.75" customHeight="1" s="70">
       <c r="F109" s="66" t="n"/>
@@ -3378,6 +3500,7 @@
       <c r="O109" s="69" t="n"/>
       <c r="P109" s="62" t="n"/>
       <c r="Q109" s="62" t="n"/>
+      <c r="R109" s="88" t="n"/>
     </row>
     <row r="110" ht="12.75" customHeight="1" s="70">
       <c r="F110" s="66" t="n"/>
@@ -3392,6 +3515,7 @@
       <c r="O110" s="69" t="n"/>
       <c r="P110" s="62" t="n"/>
       <c r="Q110" s="62" t="n"/>
+      <c r="R110" s="88" t="n"/>
     </row>
     <row r="111" ht="12.75" customHeight="1" s="70">
       <c r="F111" s="66" t="n"/>
@@ -3406,6 +3530,7 @@
       <c r="O111" s="69" t="n"/>
       <c r="P111" s="62" t="n"/>
       <c r="Q111" s="62" t="n"/>
+      <c r="R111" s="88" t="n"/>
     </row>
     <row r="112" ht="12.75" customHeight="1" s="70">
       <c r="F112" s="66" t="n"/>
@@ -3420,6 +3545,7 @@
       <c r="O112" s="69" t="n"/>
       <c r="P112" s="62" t="n"/>
       <c r="Q112" s="62" t="n"/>
+      <c r="R112" s="88" t="n"/>
     </row>
     <row r="113" ht="12.75" customHeight="1" s="70">
       <c r="F113" s="66" t="n"/>
@@ -3434,6 +3560,7 @@
       <c r="O113" s="69" t="n"/>
       <c r="P113" s="62" t="n"/>
       <c r="Q113" s="62" t="n"/>
+      <c r="R113" s="88" t="n"/>
     </row>
     <row r="114" ht="12.75" customHeight="1" s="70">
       <c r="F114" s="66" t="n"/>
@@ -3448,6 +3575,7 @@
       <c r="O114" s="69" t="n"/>
       <c r="P114" s="62" t="n"/>
       <c r="Q114" s="62" t="n"/>
+      <c r="R114" s="88" t="n"/>
     </row>
     <row r="115" ht="12.75" customHeight="1" s="70">
       <c r="F115" s="66" t="n"/>
@@ -3462,6 +3590,7 @@
       <c r="O115" s="69" t="n"/>
       <c r="P115" s="62" t="n"/>
       <c r="Q115" s="62" t="n"/>
+      <c r="R115" s="88" t="n"/>
     </row>
     <row r="116" ht="12.75" customHeight="1" s="70">
       <c r="F116" s="66" t="n"/>
@@ -3476,6 +3605,7 @@
       <c r="O116" s="69" t="n"/>
       <c r="P116" s="62" t="n"/>
       <c r="Q116" s="62" t="n"/>
+      <c r="R116" s="88" t="n"/>
     </row>
     <row r="117" ht="12.75" customHeight="1" s="70">
       <c r="F117" s="66" t="n"/>
@@ -3490,6 +3620,7 @@
       <c r="O117" s="69" t="n"/>
       <c r="P117" s="62" t="n"/>
       <c r="Q117" s="62" t="n"/>
+      <c r="R117" s="88" t="n"/>
     </row>
     <row r="118" ht="12.75" customHeight="1" s="70">
       <c r="F118" s="66" t="n"/>
@@ -3504,6 +3635,7 @@
       <c r="O118" s="69" t="n"/>
       <c r="P118" s="62" t="n"/>
       <c r="Q118" s="62" t="n"/>
+      <c r="R118" s="88" t="n"/>
     </row>
     <row r="119" ht="12.75" customHeight="1" s="70">
       <c r="F119" s="66" t="n"/>
@@ -3518,6 +3650,7 @@
       <c r="O119" s="69" t="n"/>
       <c r="P119" s="62" t="n"/>
       <c r="Q119" s="62" t="n"/>
+      <c r="R119" s="88" t="n"/>
     </row>
     <row r="120" ht="12.75" customHeight="1" s="70">
       <c r="F120" s="66" t="n"/>
@@ -3532,6 +3665,7 @@
       <c r="O120" s="69" t="n"/>
       <c r="P120" s="62" t="n"/>
       <c r="Q120" s="62" t="n"/>
+      <c r="R120" s="88" t="n"/>
     </row>
     <row r="121" ht="12.75" customHeight="1" s="70">
       <c r="F121" s="66" t="n"/>
@@ -3546,6 +3680,7 @@
       <c r="O121" s="69" t="n"/>
       <c r="P121" s="62" t="n"/>
       <c r="Q121" s="62" t="n"/>
+      <c r="R121" s="88" t="n"/>
     </row>
     <row r="122" ht="12.75" customHeight="1" s="70">
       <c r="F122" s="66" t="n"/>
@@ -3560,6 +3695,7 @@
       <c r="O122" s="69" t="n"/>
       <c r="P122" s="62" t="n"/>
       <c r="Q122" s="62" t="n"/>
+      <c r="R122" s="88" t="n"/>
     </row>
     <row r="123" ht="12.75" customHeight="1" s="70">
       <c r="F123" s="66" t="n"/>
@@ -3574,6 +3710,7 @@
       <c r="O123" s="69" t="n"/>
       <c r="P123" s="62" t="n"/>
       <c r="Q123" s="62" t="n"/>
+      <c r="R123" s="88" t="n"/>
     </row>
     <row r="124" ht="12.75" customHeight="1" s="70">
       <c r="F124" s="66" t="n"/>
@@ -3588,6 +3725,7 @@
       <c r="O124" s="69" t="n"/>
       <c r="P124" s="62" t="n"/>
       <c r="Q124" s="62" t="n"/>
+      <c r="R124" s="88" t="n"/>
     </row>
     <row r="125" ht="12.75" customHeight="1" s="70">
       <c r="F125" s="66" t="n"/>
@@ -3602,6 +3740,7 @@
       <c r="O125" s="69" t="n"/>
       <c r="P125" s="62" t="n"/>
       <c r="Q125" s="62" t="n"/>
+      <c r="R125" s="88" t="n"/>
     </row>
     <row r="126" ht="12.75" customHeight="1" s="70">
       <c r="F126" s="66" t="n"/>
@@ -3616,6 +3755,7 @@
       <c r="O126" s="69" t="n"/>
       <c r="P126" s="62" t="n"/>
       <c r="Q126" s="62" t="n"/>
+      <c r="R126" s="88" t="n"/>
     </row>
     <row r="127" ht="12.75" customHeight="1" s="70">
       <c r="F127" s="66" t="n"/>
@@ -3630,6 +3770,7 @@
       <c r="O127" s="69" t="n"/>
       <c r="P127" s="62" t="n"/>
       <c r="Q127" s="62" t="n"/>
+      <c r="R127" s="88" t="n"/>
     </row>
     <row r="128" ht="12.75" customHeight="1" s="70">
       <c r="F128" s="66" t="n"/>
@@ -3644,6 +3785,7 @@
       <c r="O128" s="69" t="n"/>
       <c r="P128" s="62" t="n"/>
       <c r="Q128" s="62" t="n"/>
+      <c r="R128" s="88" t="n"/>
     </row>
     <row r="129" ht="12.75" customHeight="1" s="70">
       <c r="F129" s="66" t="n"/>
@@ -3658,6 +3800,7 @@
       <c r="O129" s="69" t="n"/>
       <c r="P129" s="62" t="n"/>
       <c r="Q129" s="62" t="n"/>
+      <c r="R129" s="88" t="n"/>
     </row>
     <row r="130" ht="12.75" customHeight="1" s="70">
       <c r="F130" s="66" t="n"/>
@@ -3672,6 +3815,7 @@
       <c r="O130" s="69" t="n"/>
       <c r="P130" s="62" t="n"/>
       <c r="Q130" s="62" t="n"/>
+      <c r="R130" s="88" t="n"/>
     </row>
     <row r="131" ht="12.75" customHeight="1" s="70">
       <c r="F131" s="66" t="n"/>
@@ -3686,6 +3830,7 @@
       <c r="O131" s="69" t="n"/>
       <c r="P131" s="62" t="n"/>
       <c r="Q131" s="62" t="n"/>
+      <c r="R131" s="88" t="n"/>
     </row>
     <row r="132" ht="12.75" customHeight="1" s="70">
       <c r="F132" s="66" t="n"/>
@@ -3700,6 +3845,7 @@
       <c r="O132" s="69" t="n"/>
       <c r="P132" s="62" t="n"/>
       <c r="Q132" s="62" t="n"/>
+      <c r="R132" s="88" t="n"/>
     </row>
     <row r="133" ht="12.75" customHeight="1" s="70">
       <c r="F133" s="66" t="n"/>
@@ -3714,6 +3860,7 @@
       <c r="O133" s="69" t="n"/>
       <c r="P133" s="62" t="n"/>
       <c r="Q133" s="62" t="n"/>
+      <c r="R133" s="88" t="n"/>
     </row>
     <row r="134" ht="12.75" customHeight="1" s="70">
       <c r="F134" s="66" t="n"/>
@@ -3728,6 +3875,7 @@
       <c r="O134" s="69" t="n"/>
       <c r="P134" s="62" t="n"/>
       <c r="Q134" s="62" t="n"/>
+      <c r="R134" s="88" t="n"/>
     </row>
     <row r="135" ht="12.75" customHeight="1" s="70">
       <c r="F135" s="66" t="n"/>
@@ -3742,6 +3890,7 @@
       <c r="O135" s="69" t="n"/>
       <c r="P135" s="62" t="n"/>
       <c r="Q135" s="62" t="n"/>
+      <c r="R135" s="88" t="n"/>
     </row>
     <row r="136" ht="12.75" customHeight="1" s="70">
       <c r="F136" s="66" t="n"/>
@@ -3756,6 +3905,7 @@
       <c r="O136" s="69" t="n"/>
       <c r="P136" s="62" t="n"/>
       <c r="Q136" s="62" t="n"/>
+      <c r="R136" s="88" t="n"/>
     </row>
     <row r="137" ht="12.75" customHeight="1" s="70">
       <c r="F137" s="66" t="n"/>
@@ -3770,6 +3920,7 @@
       <c r="O137" s="69" t="n"/>
       <c r="P137" s="62" t="n"/>
       <c r="Q137" s="62" t="n"/>
+      <c r="R137" s="88" t="n"/>
     </row>
     <row r="138" ht="12.75" customHeight="1" s="70">
       <c r="F138" s="66" t="n"/>
@@ -3784,6 +3935,7 @@
       <c r="O138" s="69" t="n"/>
       <c r="P138" s="62" t="n"/>
       <c r="Q138" s="62" t="n"/>
+      <c r="R138" s="88" t="n"/>
     </row>
     <row r="139" ht="12.75" customHeight="1" s="70">
       <c r="F139" s="66" t="n"/>
@@ -3798,6 +3950,7 @@
       <c r="O139" s="69" t="n"/>
       <c r="P139" s="62" t="n"/>
       <c r="Q139" s="62" t="n"/>
+      <c r="R139" s="88" t="n"/>
     </row>
     <row r="140" ht="12.75" customHeight="1" s="70">
       <c r="F140" s="66" t="n"/>
@@ -3812,6 +3965,7 @@
       <c r="O140" s="69" t="n"/>
       <c r="P140" s="62" t="n"/>
       <c r="Q140" s="62" t="n"/>
+      <c r="R140" s="88" t="n"/>
     </row>
     <row r="141" ht="12.75" customHeight="1" s="70">
       <c r="F141" s="66" t="n"/>
@@ -3826,6 +3980,7 @@
       <c r="O141" s="69" t="n"/>
       <c r="P141" s="62" t="n"/>
       <c r="Q141" s="62" t="n"/>
+      <c r="R141" s="88" t="n"/>
     </row>
     <row r="142" ht="12.75" customHeight="1" s="70">
       <c r="F142" s="66" t="n"/>
@@ -3840,6 +3995,7 @@
       <c r="O142" s="69" t="n"/>
       <c r="P142" s="62" t="n"/>
       <c r="Q142" s="62" t="n"/>
+      <c r="R142" s="88" t="n"/>
     </row>
     <row r="143" ht="12.75" customHeight="1" s="70">
       <c r="F143" s="66" t="n"/>
@@ -3854,6 +4010,7 @@
       <c r="O143" s="69" t="n"/>
       <c r="P143" s="62" t="n"/>
       <c r="Q143" s="62" t="n"/>
+      <c r="R143" s="88" t="n"/>
     </row>
     <row r="144" ht="12.75" customHeight="1" s="70">
       <c r="F144" s="66" t="n"/>
@@ -3868,6 +4025,7 @@
       <c r="O144" s="69" t="n"/>
       <c r="P144" s="62" t="n"/>
       <c r="Q144" s="62" t="n"/>
+      <c r="R144" s="88" t="n"/>
     </row>
     <row r="145" ht="12.75" customHeight="1" s="70">
       <c r="F145" s="66" t="n"/>
@@ -3882,6 +4040,7 @@
       <c r="O145" s="69" t="n"/>
       <c r="P145" s="62" t="n"/>
       <c r="Q145" s="62" t="n"/>
+      <c r="R145" s="88" t="n"/>
     </row>
     <row r="146" ht="12.75" customHeight="1" s="70">
       <c r="F146" s="66" t="n"/>
@@ -3896,6 +4055,7 @@
       <c r="O146" s="69" t="n"/>
       <c r="P146" s="62" t="n"/>
       <c r="Q146" s="62" t="n"/>
+      <c r="R146" s="88" t="n"/>
     </row>
     <row r="147" ht="12.75" customHeight="1" s="70">
       <c r="F147" s="66" t="n"/>
@@ -3910,6 +4070,7 @@
       <c r="O147" s="69" t="n"/>
       <c r="P147" s="62" t="n"/>
       <c r="Q147" s="62" t="n"/>
+      <c r="R147" s="88" t="n"/>
     </row>
     <row r="148" ht="12.75" customHeight="1" s="70">
       <c r="F148" s="66" t="n"/>
@@ -3924,6 +4085,7 @@
       <c r="O148" s="69" t="n"/>
       <c r="P148" s="62" t="n"/>
       <c r="Q148" s="62" t="n"/>
+      <c r="R148" s="88" t="n"/>
     </row>
     <row r="149" ht="12.75" customHeight="1" s="70">
       <c r="F149" s="66" t="n"/>
@@ -3938,6 +4100,7 @@
       <c r="O149" s="69" t="n"/>
       <c r="P149" s="62" t="n"/>
       <c r="Q149" s="62" t="n"/>
+      <c r="R149" s="88" t="n"/>
     </row>
     <row r="150" ht="12.75" customHeight="1" s="70">
       <c r="F150" s="66" t="n"/>
@@ -3952,6 +4115,7 @@
       <c r="O150" s="69" t="n"/>
       <c r="P150" s="62" t="n"/>
       <c r="Q150" s="62" t="n"/>
+      <c r="R150" s="88" t="n"/>
     </row>
     <row r="151" ht="12.75" customHeight="1" s="70">
       <c r="F151" s="66" t="n"/>
@@ -3966,6 +4130,7 @@
       <c r="O151" s="69" t="n"/>
       <c r="P151" s="62" t="n"/>
       <c r="Q151" s="62" t="n"/>
+      <c r="R151" s="88" t="n"/>
     </row>
     <row r="152" ht="12.75" customHeight="1" s="70">
       <c r="F152" s="66" t="n"/>
@@ -3980,6 +4145,7 @@
       <c r="O152" s="69" t="n"/>
       <c r="P152" s="62" t="n"/>
       <c r="Q152" s="62" t="n"/>
+      <c r="R152" s="88" t="n"/>
     </row>
     <row r="153" ht="12.75" customHeight="1" s="70">
       <c r="F153" s="66" t="n"/>
@@ -3994,6 +4160,7 @@
       <c r="O153" s="69" t="n"/>
       <c r="P153" s="62" t="n"/>
       <c r="Q153" s="62" t="n"/>
+      <c r="R153" s="88" t="n"/>
     </row>
     <row r="154" ht="12.75" customHeight="1" s="70">
       <c r="F154" s="66" t="n"/>
@@ -4008,6 +4175,7 @@
       <c r="O154" s="69" t="n"/>
       <c r="P154" s="62" t="n"/>
       <c r="Q154" s="62" t="n"/>
+      <c r="R154" s="88" t="n"/>
     </row>
     <row r="155" ht="12.75" customHeight="1" s="70">
       <c r="F155" s="66" t="n"/>
@@ -4022,6 +4190,7 @@
       <c r="O155" s="69" t="n"/>
       <c r="P155" s="62" t="n"/>
       <c r="Q155" s="62" t="n"/>
+      <c r="R155" s="88" t="n"/>
     </row>
     <row r="156" ht="12.75" customHeight="1" s="70">
       <c r="F156" s="66" t="n"/>
@@ -4036,6 +4205,7 @@
       <c r="O156" s="69" t="n"/>
       <c r="P156" s="62" t="n"/>
       <c r="Q156" s="62" t="n"/>
+      <c r="R156" s="88" t="n"/>
     </row>
     <row r="157" ht="12.75" customHeight="1" s="70">
       <c r="F157" s="66" t="n"/>
@@ -4050,6 +4220,7 @@
       <c r="O157" s="69" t="n"/>
       <c r="P157" s="62" t="n"/>
       <c r="Q157" s="62" t="n"/>
+      <c r="R157" s="88" t="n"/>
     </row>
     <row r="158" ht="12.75" customHeight="1" s="70">
       <c r="F158" s="66" t="n"/>
@@ -4064,6 +4235,7 @@
       <c r="O158" s="69" t="n"/>
       <c r="P158" s="62" t="n"/>
       <c r="Q158" s="62" t="n"/>
+      <c r="R158" s="88" t="n"/>
     </row>
     <row r="159" ht="12.75" customHeight="1" s="70">
       <c r="F159" s="66" t="n"/>
@@ -4078,6 +4250,7 @@
       <c r="O159" s="69" t="n"/>
       <c r="P159" s="62" t="n"/>
       <c r="Q159" s="62" t="n"/>
+      <c r="R159" s="88" t="n"/>
     </row>
     <row r="160" ht="12.75" customHeight="1" s="70">
       <c r="F160" s="66" t="n"/>
@@ -4092,6 +4265,7 @@
       <c r="O160" s="69" t="n"/>
       <c r="P160" s="62" t="n"/>
       <c r="Q160" s="62" t="n"/>
+      <c r="R160" s="88" t="n"/>
     </row>
     <row r="161" ht="12.75" customHeight="1" s="70">
       <c r="F161" s="66" t="n"/>
@@ -4106,6 +4280,7 @@
       <c r="O161" s="69" t="n"/>
       <c r="P161" s="62" t="n"/>
       <c r="Q161" s="62" t="n"/>
+      <c r="R161" s="88" t="n"/>
     </row>
     <row r="162" ht="12.75" customHeight="1" s="70">
       <c r="F162" s="66" t="n"/>
@@ -4120,6 +4295,7 @@
       <c r="O162" s="69" t="n"/>
       <c r="P162" s="62" t="n"/>
       <c r="Q162" s="62" t="n"/>
+      <c r="R162" s="88" t="n"/>
     </row>
     <row r="163" ht="12.75" customHeight="1" s="70">
       <c r="F163" s="66" t="n"/>
@@ -4134,6 +4310,7 @@
       <c r="O163" s="69" t="n"/>
       <c r="P163" s="62" t="n"/>
       <c r="Q163" s="62" t="n"/>
+      <c r="R163" s="88" t="n"/>
     </row>
     <row r="164" ht="12.75" customHeight="1" s="70">
       <c r="F164" s="66" t="n"/>
@@ -4148,6 +4325,7 @@
       <c r="O164" s="69" t="n"/>
       <c r="P164" s="62" t="n"/>
       <c r="Q164" s="62" t="n"/>
+      <c r="R164" s="88" t="n"/>
     </row>
     <row r="165" ht="12.75" customHeight="1" s="70">
       <c r="F165" s="66" t="n"/>
@@ -4162,6 +4340,7 @@
       <c r="O165" s="69" t="n"/>
       <c r="P165" s="62" t="n"/>
       <c r="Q165" s="62" t="n"/>
+      <c r="R165" s="88" t="n"/>
     </row>
     <row r="166" ht="12.75" customHeight="1" s="70">
       <c r="F166" s="66" t="n"/>
@@ -4176,6 +4355,7 @@
       <c r="O166" s="69" t="n"/>
       <c r="P166" s="62" t="n"/>
       <c r="Q166" s="62" t="n"/>
+      <c r="R166" s="88" t="n"/>
     </row>
     <row r="167" ht="12.75" customHeight="1" s="70">
       <c r="F167" s="66" t="n"/>
@@ -4190,6 +4370,7 @@
       <c r="O167" s="69" t="n"/>
       <c r="P167" s="62" t="n"/>
       <c r="Q167" s="62" t="n"/>
+      <c r="R167" s="88" t="n"/>
     </row>
     <row r="168" ht="12.75" customHeight="1" s="70">
       <c r="F168" s="66" t="n"/>
@@ -4204,6 +4385,7 @@
       <c r="O168" s="69" t="n"/>
       <c r="P168" s="62" t="n"/>
       <c r="Q168" s="62" t="n"/>
+      <c r="R168" s="88" t="n"/>
     </row>
     <row r="169" ht="12.75" customHeight="1" s="70">
       <c r="F169" s="66" t="n"/>
@@ -4218,6 +4400,7 @@
       <c r="O169" s="69" t="n"/>
       <c r="P169" s="62" t="n"/>
       <c r="Q169" s="62" t="n"/>
+      <c r="R169" s="88" t="n"/>
     </row>
     <row r="170" ht="12.75" customHeight="1" s="70">
       <c r="F170" s="66" t="n"/>
@@ -4232,6 +4415,7 @@
       <c r="O170" s="69" t="n"/>
       <c r="P170" s="62" t="n"/>
       <c r="Q170" s="62" t="n"/>
+      <c r="R170" s="88" t="n"/>
     </row>
     <row r="171" ht="12.75" customHeight="1" s="70">
       <c r="F171" s="66" t="n"/>
@@ -4246,6 +4430,7 @@
       <c r="O171" s="69" t="n"/>
       <c r="P171" s="62" t="n"/>
       <c r="Q171" s="62" t="n"/>
+      <c r="R171" s="88" t="n"/>
     </row>
     <row r="172" ht="12.75" customHeight="1" s="70">
       <c r="F172" s="66" t="n"/>
@@ -4260,6 +4445,7 @@
       <c r="O172" s="69" t="n"/>
       <c r="P172" s="62" t="n"/>
       <c r="Q172" s="62" t="n"/>
+      <c r="R172" s="88" t="n"/>
     </row>
     <row r="173" ht="12.75" customHeight="1" s="70">
       <c r="F173" s="66" t="n"/>
@@ -4274,6 +4460,7 @@
       <c r="O173" s="69" t="n"/>
       <c r="P173" s="62" t="n"/>
       <c r="Q173" s="62" t="n"/>
+      <c r="R173" s="88" t="n"/>
     </row>
     <row r="174" ht="12.75" customHeight="1" s="70">
       <c r="F174" s="66" t="n"/>
@@ -4288,6 +4475,7 @@
       <c r="O174" s="69" t="n"/>
       <c r="P174" s="62" t="n"/>
       <c r="Q174" s="62" t="n"/>
+      <c r="R174" s="88" t="n"/>
     </row>
     <row r="175" ht="12.75" customHeight="1" s="70">
       <c r="F175" s="66" t="n"/>
@@ -4302,6 +4490,7 @@
       <c r="O175" s="69" t="n"/>
       <c r="P175" s="62" t="n"/>
       <c r="Q175" s="62" t="n"/>
+      <c r="R175" s="88" t="n"/>
     </row>
     <row r="176" ht="12.75" customHeight="1" s="70">
       <c r="F176" s="66" t="n"/>
@@ -4316,6 +4505,7 @@
       <c r="O176" s="69" t="n"/>
       <c r="P176" s="62" t="n"/>
       <c r="Q176" s="62" t="n"/>
+      <c r="R176" s="88" t="n"/>
     </row>
     <row r="177" ht="12.75" customHeight="1" s="70">
       <c r="F177" s="66" t="n"/>
@@ -4330,6 +4520,7 @@
       <c r="O177" s="69" t="n"/>
       <c r="P177" s="62" t="n"/>
       <c r="Q177" s="62" t="n"/>
+      <c r="R177" s="88" t="n"/>
     </row>
     <row r="178" ht="12.75" customHeight="1" s="70">
       <c r="F178" s="66" t="n"/>
@@ -4344,6 +4535,7 @@
       <c r="O178" s="69" t="n"/>
       <c r="P178" s="62" t="n"/>
       <c r="Q178" s="62" t="n"/>
+      <c r="R178" s="88" t="n"/>
     </row>
     <row r="179" ht="12.75" customHeight="1" s="70">
       <c r="F179" s="66" t="n"/>
@@ -4358,6 +4550,7 @@
       <c r="O179" s="69" t="n"/>
       <c r="P179" s="62" t="n"/>
       <c r="Q179" s="62" t="n"/>
+      <c r="R179" s="88" t="n"/>
     </row>
     <row r="180" ht="12.75" customHeight="1" s="70">
       <c r="F180" s="66" t="n"/>
@@ -4372,6 +4565,7 @@
       <c r="O180" s="69" t="n"/>
       <c r="P180" s="62" t="n"/>
       <c r="Q180" s="62" t="n"/>
+      <c r="R180" s="88" t="n"/>
     </row>
     <row r="181" ht="12.75" customHeight="1" s="70">
       <c r="F181" s="66" t="n"/>
@@ -4386,6 +4580,7 @@
       <c r="O181" s="69" t="n"/>
       <c r="P181" s="62" t="n"/>
       <c r="Q181" s="62" t="n"/>
+      <c r="R181" s="88" t="n"/>
     </row>
     <row r="182" ht="12.75" customHeight="1" s="70">
       <c r="F182" s="66" t="n"/>
@@ -4400,6 +4595,7 @@
       <c r="O182" s="69" t="n"/>
       <c r="P182" s="62" t="n"/>
       <c r="Q182" s="62" t="n"/>
+      <c r="R182" s="88" t="n"/>
     </row>
     <row r="183" ht="12.75" customHeight="1" s="70">
       <c r="F183" s="66" t="n"/>
@@ -4414,6 +4610,7 @@
       <c r="O183" s="69" t="n"/>
       <c r="P183" s="62" t="n"/>
       <c r="Q183" s="62" t="n"/>
+      <c r="R183" s="88" t="n"/>
     </row>
     <row r="184" ht="12.75" customHeight="1" s="70">
       <c r="F184" s="66" t="n"/>
@@ -4428,6 +4625,7 @@
       <c r="O184" s="69" t="n"/>
       <c r="P184" s="62" t="n"/>
       <c r="Q184" s="62" t="n"/>
+      <c r="R184" s="88" t="n"/>
     </row>
     <row r="185" ht="12.75" customHeight="1" s="70">
       <c r="F185" s="66" t="n"/>
@@ -4442,6 +4640,7 @@
       <c r="O185" s="69" t="n"/>
       <c r="P185" s="62" t="n"/>
       <c r="Q185" s="62" t="n"/>
+      <c r="R185" s="88" t="n"/>
     </row>
     <row r="186" ht="12.75" customHeight="1" s="70">
       <c r="F186" s="66" t="n"/>
@@ -4456,6 +4655,7 @@
       <c r="O186" s="69" t="n"/>
       <c r="P186" s="62" t="n"/>
       <c r="Q186" s="62" t="n"/>
+      <c r="R186" s="88" t="n"/>
     </row>
     <row r="187" ht="12.75" customHeight="1" s="70">
       <c r="F187" s="66" t="n"/>
@@ -4470,6 +4670,7 @@
       <c r="O187" s="69" t="n"/>
       <c r="P187" s="62" t="n"/>
       <c r="Q187" s="62" t="n"/>
+      <c r="R187" s="88" t="n"/>
     </row>
     <row r="188" ht="12.75" customHeight="1" s="70">
       <c r="F188" s="66" t="n"/>
@@ -4484,6 +4685,7 @@
       <c r="O188" s="69" t="n"/>
       <c r="P188" s="62" t="n"/>
       <c r="Q188" s="62" t="n"/>
+      <c r="R188" s="88" t="n"/>
     </row>
     <row r="189" ht="12.75" customHeight="1" s="70">
       <c r="F189" s="66" t="n"/>
@@ -4498,6 +4700,7 @@
       <c r="O189" s="69" t="n"/>
       <c r="P189" s="62" t="n"/>
       <c r="Q189" s="62" t="n"/>
+      <c r="R189" s="88" t="n"/>
     </row>
     <row r="190" ht="12.75" customHeight="1" s="70">
       <c r="F190" s="66" t="n"/>
@@ -4512,6 +4715,7 @@
       <c r="O190" s="69" t="n"/>
       <c r="P190" s="62" t="n"/>
       <c r="Q190" s="62" t="n"/>
+      <c r="R190" s="88" t="n"/>
     </row>
     <row r="191" ht="12.75" customHeight="1" s="70">
       <c r="F191" s="66" t="n"/>
@@ -4526,6 +4730,7 @@
       <c r="O191" s="69" t="n"/>
       <c r="P191" s="62" t="n"/>
       <c r="Q191" s="62" t="n"/>
+      <c r="R191" s="88" t="n"/>
     </row>
     <row r="192" ht="12.75" customHeight="1" s="70">
       <c r="F192" s="66" t="n"/>
@@ -4540,6 +4745,7 @@
       <c r="O192" s="69" t="n"/>
       <c r="P192" s="62" t="n"/>
       <c r="Q192" s="62" t="n"/>
+      <c r="R192" s="88" t="n"/>
     </row>
     <row r="193" ht="12.75" customHeight="1" s="70">
       <c r="F193" s="66" t="n"/>
@@ -4554,6 +4760,7 @@
       <c r="O193" s="69" t="n"/>
       <c r="P193" s="62" t="n"/>
       <c r="Q193" s="62" t="n"/>
+      <c r="R193" s="88" t="n"/>
     </row>
     <row r="194" ht="12.75" customHeight="1" s="70">
       <c r="F194" s="66" t="n"/>
@@ -4568,6 +4775,7 @@
       <c r="O194" s="69" t="n"/>
       <c r="P194" s="62" t="n"/>
       <c r="Q194" s="62" t="n"/>
+      <c r="R194" s="88" t="n"/>
     </row>
     <row r="195" ht="12.75" customHeight="1" s="70">
       <c r="F195" s="66" t="n"/>
@@ -4582,6 +4790,7 @@
       <c r="O195" s="69" t="n"/>
       <c r="P195" s="62" t="n"/>
       <c r="Q195" s="62" t="n"/>
+      <c r="R195" s="88" t="n"/>
     </row>
     <row r="196" ht="12.75" customHeight="1" s="70">
       <c r="F196" s="66" t="n"/>
@@ -4596,6 +4805,7 @@
       <c r="O196" s="69" t="n"/>
       <c r="P196" s="62" t="n"/>
       <c r="Q196" s="62" t="n"/>
+      <c r="R196" s="88" t="n"/>
     </row>
     <row r="197" ht="12.75" customHeight="1" s="70">
       <c r="F197" s="66" t="n"/>
@@ -4610,6 +4820,7 @@
       <c r="O197" s="69" t="n"/>
       <c r="P197" s="62" t="n"/>
       <c r="Q197" s="62" t="n"/>
+      <c r="R197" s="88" t="n"/>
     </row>
     <row r="198" ht="12.75" customHeight="1" s="70">
       <c r="F198" s="66" t="n"/>
@@ -4624,6 +4835,7 @@
       <c r="O198" s="69" t="n"/>
       <c r="P198" s="62" t="n"/>
       <c r="Q198" s="62" t="n"/>
+      <c r="R198" s="88" t="n"/>
     </row>
     <row r="199" ht="12.75" customHeight="1" s="70">
       <c r="F199" s="66" t="n"/>
@@ -4638,6 +4850,7 @@
       <c r="O199" s="69" t="n"/>
       <c r="P199" s="62" t="n"/>
       <c r="Q199" s="62" t="n"/>
+      <c r="R199" s="88" t="n"/>
     </row>
     <row r="200" ht="12.75" customHeight="1" s="70">
       <c r="F200" s="66" t="n"/>
@@ -4652,6 +4865,7 @@
       <c r="O200" s="69" t="n"/>
       <c r="P200" s="62" t="n"/>
       <c r="Q200" s="62" t="n"/>
+      <c r="R200" s="88" t="n"/>
     </row>
     <row r="201" ht="12.75" customHeight="1" s="70">
       <c r="F201" s="66" t="n"/>
@@ -4666,6 +4880,7 @@
       <c r="O201" s="69" t="n"/>
       <c r="P201" s="62" t="n"/>
       <c r="Q201" s="62" t="n"/>
+      <c r="R201" s="88" t="n"/>
     </row>
     <row r="202" ht="12.75" customHeight="1" s="70">
       <c r="F202" s="66" t="n"/>
@@ -4680,6 +4895,7 @@
       <c r="O202" s="69" t="n"/>
       <c r="P202" s="62" t="n"/>
       <c r="Q202" s="62" t="n"/>
+      <c r="R202" s="88" t="n"/>
     </row>
     <row r="203" ht="12.75" customHeight="1" s="70">
       <c r="F203" s="66" t="n"/>
@@ -4694,6 +4910,7 @@
       <c r="O203" s="69" t="n"/>
       <c r="P203" s="62" t="n"/>
       <c r="Q203" s="62" t="n"/>
+      <c r="R203" s="88" t="n"/>
     </row>
     <row r="204" ht="12.75" customHeight="1" s="70">
       <c r="F204" s="66" t="n"/>
@@ -4708,6 +4925,7 @@
       <c r="O204" s="69" t="n"/>
       <c r="P204" s="62" t="n"/>
       <c r="Q204" s="62" t="n"/>
+      <c r="R204" s="88" t="n"/>
     </row>
     <row r="205" ht="12.75" customHeight="1" s="70">
       <c r="F205" s="66" t="n"/>
@@ -4722,6 +4940,7 @@
       <c r="O205" s="69" t="n"/>
       <c r="P205" s="62" t="n"/>
       <c r="Q205" s="62" t="n"/>
+      <c r="R205" s="88" t="n"/>
     </row>
     <row r="206" ht="12.75" customHeight="1" s="70">
       <c r="F206" s="66" t="n"/>
@@ -4736,6 +4955,7 @@
       <c r="O206" s="69" t="n"/>
       <c r="P206" s="62" t="n"/>
       <c r="Q206" s="62" t="n"/>
+      <c r="R206" s="88" t="n"/>
     </row>
     <row r="207" ht="12.75" customHeight="1" s="70">
       <c r="F207" s="66" t="n"/>
@@ -4750,6 +4970,7 @@
       <c r="O207" s="69" t="n"/>
       <c r="P207" s="62" t="n"/>
       <c r="Q207" s="62" t="n"/>
+      <c r="R207" s="88" t="n"/>
     </row>
     <row r="208" ht="12.75" customHeight="1" s="70">
       <c r="F208" s="66" t="n"/>
@@ -4764,6 +4985,7 @@
       <c r="O208" s="69" t="n"/>
       <c r="P208" s="62" t="n"/>
       <c r="Q208" s="62" t="n"/>
+      <c r="R208" s="88" t="n"/>
     </row>
     <row r="209" ht="12.75" customHeight="1" s="70">
       <c r="F209" s="66" t="n"/>
@@ -4778,6 +5000,7 @@
       <c r="O209" s="69" t="n"/>
       <c r="P209" s="62" t="n"/>
       <c r="Q209" s="62" t="n"/>
+      <c r="R209" s="88" t="n"/>
     </row>
     <row r="210" ht="12.75" customHeight="1" s="70">
       <c r="F210" s="66" t="n"/>
@@ -4792,6 +5015,7 @@
       <c r="O210" s="69" t="n"/>
       <c r="P210" s="62" t="n"/>
       <c r="Q210" s="62" t="n"/>
+      <c r="R210" s="88" t="n"/>
     </row>
     <row r="211" ht="12.75" customHeight="1" s="70">
       <c r="F211" s="66" t="n"/>
@@ -4806,6 +5030,7 @@
       <c r="O211" s="69" t="n"/>
       <c r="P211" s="62" t="n"/>
       <c r="Q211" s="62" t="n"/>
+      <c r="R211" s="88" t="n"/>
     </row>
     <row r="212" ht="12.75" customHeight="1" s="70">
       <c r="F212" s="66" t="n"/>
@@ -4820,6 +5045,7 @@
       <c r="O212" s="69" t="n"/>
       <c r="P212" s="62" t="n"/>
       <c r="Q212" s="62" t="n"/>
+      <c r="R212" s="88" t="n"/>
     </row>
     <row r="213" ht="12.75" customHeight="1" s="70">
       <c r="F213" s="66" t="n"/>
@@ -4834,6 +5060,7 @@
       <c r="O213" s="69" t="n"/>
       <c r="P213" s="62" t="n"/>
       <c r="Q213" s="62" t="n"/>
+      <c r="R213" s="88" t="n"/>
     </row>
     <row r="214" ht="12.75" customHeight="1" s="70">
       <c r="F214" s="66" t="n"/>
@@ -4848,6 +5075,7 @@
       <c r="O214" s="69" t="n"/>
       <c r="P214" s="62" t="n"/>
       <c r="Q214" s="62" t="n"/>
+      <c r="R214" s="88" t="n"/>
     </row>
     <row r="215" ht="12.75" customHeight="1" s="70">
       <c r="F215" s="66" t="n"/>
@@ -4862,6 +5090,7 @@
       <c r="O215" s="69" t="n"/>
       <c r="P215" s="62" t="n"/>
       <c r="Q215" s="62" t="n"/>
+      <c r="R215" s="88" t="n"/>
     </row>
     <row r="216" ht="12.75" customHeight="1" s="70">
       <c r="F216" s="66" t="n"/>
@@ -4876,6 +5105,7 @@
       <c r="O216" s="69" t="n"/>
       <c r="P216" s="62" t="n"/>
       <c r="Q216" s="62" t="n"/>
+      <c r="R216" s="88" t="n"/>
     </row>
     <row r="217" ht="12.75" customHeight="1" s="70">
       <c r="F217" s="66" t="n"/>
@@ -4890,6 +5120,7 @@
       <c r="O217" s="69" t="n"/>
       <c r="P217" s="62" t="n"/>
       <c r="Q217" s="62" t="n"/>
+      <c r="R217" s="88" t="n"/>
     </row>
     <row r="218" ht="12.75" customHeight="1" s="70">
       <c r="F218" s="66" t="n"/>
@@ -4904,6 +5135,7 @@
       <c r="O218" s="69" t="n"/>
       <c r="P218" s="62" t="n"/>
       <c r="Q218" s="62" t="n"/>
+      <c r="R218" s="88" t="n"/>
     </row>
     <row r="219" ht="12.75" customHeight="1" s="70">
       <c r="F219" s="66" t="n"/>
@@ -4918,6 +5150,7 @@
       <c r="O219" s="69" t="n"/>
       <c r="P219" s="62" t="n"/>
       <c r="Q219" s="62" t="n"/>
+      <c r="R219" s="88" t="n"/>
     </row>
     <row r="220" ht="12.75" customHeight="1" s="70">
       <c r="F220" s="66" t="n"/>
@@ -4932,6 +5165,7 @@
       <c r="O220" s="69" t="n"/>
       <c r="P220" s="62" t="n"/>
       <c r="Q220" s="62" t="n"/>
+      <c r="R220" s="88" t="n"/>
     </row>
     <row r="221" ht="12.75" customHeight="1" s="70">
       <c r="F221" s="66" t="n"/>
@@ -4946,6 +5180,7 @@
       <c r="O221" s="69" t="n"/>
       <c r="P221" s="62" t="n"/>
       <c r="Q221" s="62" t="n"/>
+      <c r="R221" s="88" t="n"/>
     </row>
     <row r="222" ht="12.75" customHeight="1" s="70">
       <c r="F222" s="66" t="n"/>
@@ -4960,6 +5195,7 @@
       <c r="O222" s="69" t="n"/>
       <c r="P222" s="62" t="n"/>
       <c r="Q222" s="62" t="n"/>
+      <c r="R222" s="88" t="n"/>
     </row>
     <row r="223" ht="12.75" customHeight="1" s="70">
       <c r="F223" s="66" t="n"/>
@@ -4974,6 +5210,7 @@
       <c r="O223" s="69" t="n"/>
       <c r="P223" s="62" t="n"/>
       <c r="Q223" s="62" t="n"/>
+      <c r="R223" s="88" t="n"/>
     </row>
     <row r="224" ht="12.75" customHeight="1" s="70">
       <c r="F224" s="66" t="n"/>
@@ -4988,6 +5225,7 @@
       <c r="O224" s="69" t="n"/>
       <c r="P224" s="62" t="n"/>
       <c r="Q224" s="62" t="n"/>
+      <c r="R224" s="88" t="n"/>
     </row>
     <row r="225" ht="12.75" customHeight="1" s="70">
       <c r="F225" s="66" t="n"/>
@@ -5002,6 +5240,7 @@
       <c r="O225" s="69" t="n"/>
       <c r="P225" s="62" t="n"/>
       <c r="Q225" s="62" t="n"/>
+      <c r="R225" s="88" t="n"/>
     </row>
     <row r="226" ht="12.75" customHeight="1" s="70">
       <c r="F226" s="66" t="n"/>
@@ -5016,6 +5255,7 @@
       <c r="O226" s="69" t="n"/>
       <c r="P226" s="62" t="n"/>
       <c r="Q226" s="62" t="n"/>
+      <c r="R226" s="88" t="n"/>
     </row>
     <row r="227" ht="12.75" customHeight="1" s="70">
       <c r="F227" s="66" t="n"/>
@@ -5030,6 +5270,7 @@
       <c r="O227" s="69" t="n"/>
       <c r="P227" s="62" t="n"/>
       <c r="Q227" s="62" t="n"/>
+      <c r="R227" s="88" t="n"/>
     </row>
     <row r="228" ht="12.75" customHeight="1" s="70">
       <c r="F228" s="66" t="n"/>
@@ -5044,6 +5285,7 @@
       <c r="O228" s="69" t="n"/>
       <c r="P228" s="62" t="n"/>
       <c r="Q228" s="62" t="n"/>
+      <c r="R228" s="88" t="n"/>
     </row>
     <row r="229" ht="12.75" customHeight="1" s="70">
       <c r="F229" s="66" t="n"/>
@@ -5058,6 +5300,7 @@
       <c r="O229" s="69" t="n"/>
       <c r="P229" s="62" t="n"/>
       <c r="Q229" s="62" t="n"/>
+      <c r="R229" s="88" t="n"/>
     </row>
     <row r="230" ht="12.75" customHeight="1" s="70">
       <c r="F230" s="66" t="n"/>
@@ -5072,6 +5315,7 @@
       <c r="O230" s="69" t="n"/>
       <c r="P230" s="62" t="n"/>
       <c r="Q230" s="62" t="n"/>
+      <c r="R230" s="88" t="n"/>
     </row>
     <row r="231" ht="12.75" customHeight="1" s="70">
       <c r="F231" s="66" t="n"/>
@@ -5086,6 +5330,7 @@
       <c r="O231" s="69" t="n"/>
       <c r="P231" s="62" t="n"/>
       <c r="Q231" s="62" t="n"/>
+      <c r="R231" s="88" t="n"/>
     </row>
     <row r="232" ht="12.75" customHeight="1" s="70">
       <c r="F232" s="66" t="n"/>
@@ -5100,6 +5345,7 @@
       <c r="O232" s="69" t="n"/>
       <c r="P232" s="62" t="n"/>
       <c r="Q232" s="62" t="n"/>
+      <c r="R232" s="88" t="n"/>
     </row>
     <row r="233" ht="12.75" customHeight="1" s="70">
       <c r="F233" s="66" t="n"/>
@@ -5114,6 +5360,7 @@
       <c r="O233" s="69" t="n"/>
       <c r="P233" s="62" t="n"/>
       <c r="Q233" s="62" t="n"/>
+      <c r="R233" s="88" t="n"/>
     </row>
     <row r="234" ht="12.75" customHeight="1" s="70">
       <c r="F234" s="66" t="n"/>
@@ -5128,6 +5375,7 @@
       <c r="O234" s="69" t="n"/>
       <c r="P234" s="62" t="n"/>
       <c r="Q234" s="62" t="n"/>
+      <c r="R234" s="88" t="n"/>
     </row>
     <row r="235" ht="12.75" customHeight="1" s="70">
       <c r="F235" s="66" t="n"/>
@@ -5142,6 +5390,7 @@
       <c r="O235" s="69" t="n"/>
       <c r="P235" s="62" t="n"/>
       <c r="Q235" s="62" t="n"/>
+      <c r="R235" s="88" t="n"/>
     </row>
     <row r="236" ht="12.75" customHeight="1" s="70">
       <c r="F236" s="66" t="n"/>
@@ -5156,6 +5405,7 @@
       <c r="O236" s="69" t="n"/>
       <c r="P236" s="62" t="n"/>
       <c r="Q236" s="62" t="n"/>
+      <c r="R236" s="88" t="n"/>
     </row>
     <row r="237" ht="12.75" customHeight="1" s="70">
       <c r="F237" s="66" t="n"/>
@@ -5170,6 +5420,7 @@
       <c r="O237" s="69" t="n"/>
       <c r="P237" s="62" t="n"/>
       <c r="Q237" s="62" t="n"/>
+      <c r="R237" s="88" t="n"/>
     </row>
     <row r="238" ht="12.75" customHeight="1" s="70">
       <c r="F238" s="66" t="n"/>
@@ -5184,6 +5435,7 @@
       <c r="O238" s="69" t="n"/>
       <c r="P238" s="62" t="n"/>
       <c r="Q238" s="62" t="n"/>
+      <c r="R238" s="88" t="n"/>
     </row>
     <row r="239" ht="12.75" customHeight="1" s="70">
       <c r="F239" s="66" t="n"/>
@@ -5198,6 +5450,7 @@
       <c r="O239" s="69" t="n"/>
       <c r="P239" s="62" t="n"/>
       <c r="Q239" s="62" t="n"/>
+      <c r="R239" s="88" t="n"/>
     </row>
     <row r="240" ht="12.75" customHeight="1" s="70">
       <c r="F240" s="66" t="n"/>
@@ -5212,6 +5465,7 @@
       <c r="O240" s="69" t="n"/>
       <c r="P240" s="62" t="n"/>
       <c r="Q240" s="62" t="n"/>
+      <c r="R240" s="88" t="n"/>
     </row>
     <row r="241" ht="12.75" customHeight="1" s="70">
       <c r="F241" s="66" t="n"/>
@@ -5226,6 +5480,7 @@
       <c r="O241" s="69" t="n"/>
       <c r="P241" s="62" t="n"/>
       <c r="Q241" s="62" t="n"/>
+      <c r="R241" s="88" t="n"/>
     </row>
     <row r="242" ht="12.75" customHeight="1" s="70">
       <c r="F242" s="66" t="n"/>
@@ -5240,6 +5495,7 @@
       <c r="O242" s="69" t="n"/>
       <c r="P242" s="62" t="n"/>
       <c r="Q242" s="62" t="n"/>
+      <c r="R242" s="88" t="n"/>
     </row>
     <row r="243" ht="12.75" customHeight="1" s="70">
       <c r="F243" s="66" t="n"/>
@@ -5254,6 +5510,7 @@
       <c r="O243" s="69" t="n"/>
       <c r="P243" s="62" t="n"/>
       <c r="Q243" s="62" t="n"/>
+      <c r="R243" s="88" t="n"/>
     </row>
     <row r="244" ht="12.75" customHeight="1" s="70">
       <c r="F244" s="66" t="n"/>
@@ -5268,6 +5525,7 @@
       <c r="O244" s="69" t="n"/>
       <c r="P244" s="62" t="n"/>
       <c r="Q244" s="62" t="n"/>
+      <c r="R244" s="88" t="n"/>
     </row>
     <row r="245" ht="12.75" customHeight="1" s="70">
       <c r="F245" s="66" t="n"/>
@@ -5282,6 +5540,7 @@
       <c r="O245" s="69" t="n"/>
       <c r="P245" s="62" t="n"/>
       <c r="Q245" s="62" t="n"/>
+      <c r="R245" s="88" t="n"/>
     </row>
     <row r="246" ht="12.75" customHeight="1" s="70">
       <c r="F246" s="66" t="n"/>
@@ -5296,6 +5555,7 @@
       <c r="O246" s="69" t="n"/>
       <c r="P246" s="62" t="n"/>
       <c r="Q246" s="62" t="n"/>
+      <c r="R246" s="88" t="n"/>
     </row>
     <row r="247" ht="12.75" customHeight="1" s="70">
       <c r="F247" s="66" t="n"/>
@@ -5310,6 +5570,7 @@
       <c r="O247" s="69" t="n"/>
       <c r="P247" s="62" t="n"/>
       <c r="Q247" s="62" t="n"/>
+      <c r="R247" s="88" t="n"/>
     </row>
     <row r="248" ht="12.75" customHeight="1" s="70">
       <c r="F248" s="66" t="n"/>
@@ -5324,6 +5585,7 @@
       <c r="O248" s="69" t="n"/>
       <c r="P248" s="62" t="n"/>
       <c r="Q248" s="62" t="n"/>
+      <c r="R248" s="88" t="n"/>
     </row>
     <row r="249" ht="12.75" customHeight="1" s="70">
       <c r="F249" s="66" t="n"/>
@@ -5338,6 +5600,7 @@
       <c r="O249" s="69" t="n"/>
       <c r="P249" s="62" t="n"/>
       <c r="Q249" s="62" t="n"/>
+      <c r="R249" s="88" t="n"/>
     </row>
     <row r="250" ht="12.75" customHeight="1" s="70">
       <c r="F250" s="66" t="n"/>
@@ -5352,6 +5615,7 @@
       <c r="O250" s="69" t="n"/>
       <c r="P250" s="62" t="n"/>
       <c r="Q250" s="62" t="n"/>
+      <c r="R250" s="88" t="n"/>
     </row>
     <row r="251" ht="12.75" customHeight="1" s="70">
       <c r="F251" s="66" t="n"/>
@@ -5366,6 +5630,7 @@
       <c r="O251" s="69" t="n"/>
       <c r="P251" s="62" t="n"/>
       <c r="Q251" s="62" t="n"/>
+      <c r="R251" s="88" t="n"/>
     </row>
     <row r="252" ht="12.75" customHeight="1" s="70">
       <c r="F252" s="66" t="n"/>
@@ -5380,6 +5645,7 @@
       <c r="O252" s="69" t="n"/>
       <c r="P252" s="62" t="n"/>
       <c r="Q252" s="62" t="n"/>
+      <c r="R252" s="88" t="n"/>
     </row>
     <row r="253" ht="12.75" customHeight="1" s="70">
       <c r="F253" s="66" t="n"/>
@@ -5394,6 +5660,7 @@
       <c r="O253" s="69" t="n"/>
       <c r="P253" s="62" t="n"/>
       <c r="Q253" s="62" t="n"/>
+      <c r="R253" s="88" t="n"/>
     </row>
     <row r="254" ht="12.75" customHeight="1" s="70">
       <c r="F254" s="66" t="n"/>
@@ -5408,6 +5675,7 @@
       <c r="O254" s="69" t="n"/>
       <c r="P254" s="62" t="n"/>
       <c r="Q254" s="62" t="n"/>
+      <c r="R254" s="88" t="n"/>
     </row>
     <row r="255" ht="12.75" customHeight="1" s="70">
       <c r="F255" s="66" t="n"/>
@@ -5422,6 +5690,7 @@
       <c r="O255" s="69" t="n"/>
       <c r="P255" s="62" t="n"/>
       <c r="Q255" s="62" t="n"/>
+      <c r="R255" s="88" t="n"/>
     </row>
     <row r="256" ht="12.75" customHeight="1" s="70">
       <c r="F256" s="66" t="n"/>
@@ -5436,6 +5705,7 @@
       <c r="O256" s="69" t="n"/>
       <c r="P256" s="62" t="n"/>
       <c r="Q256" s="62" t="n"/>
+      <c r="R256" s="88" t="n"/>
     </row>
     <row r="257" ht="12.75" customHeight="1" s="70">
       <c r="F257" s="66" t="n"/>
@@ -5450,6 +5720,7 @@
       <c r="O257" s="69" t="n"/>
       <c r="P257" s="62" t="n"/>
       <c r="Q257" s="62" t="n"/>
+      <c r="R257" s="88" t="n"/>
     </row>
     <row r="258" ht="12.75" customHeight="1" s="70">
       <c r="F258" s="66" t="n"/>
@@ -5464,6 +5735,7 @@
       <c r="O258" s="69" t="n"/>
       <c r="P258" s="62" t="n"/>
       <c r="Q258" s="62" t="n"/>
+      <c r="R258" s="88" t="n"/>
     </row>
     <row r="259" ht="12.75" customHeight="1" s="70">
       <c r="F259" s="66" t="n"/>
@@ -5478,6 +5750,7 @@
       <c r="O259" s="69" t="n"/>
       <c r="P259" s="62" t="n"/>
       <c r="Q259" s="62" t="n"/>
+      <c r="R259" s="88" t="n"/>
     </row>
     <row r="260" ht="12.75" customHeight="1" s="70">
       <c r="F260" s="66" t="n"/>
@@ -5492,6 +5765,7 @@
       <c r="O260" s="69" t="n"/>
       <c r="P260" s="62" t="n"/>
       <c r="Q260" s="62" t="n"/>
+      <c r="R260" s="88" t="n"/>
     </row>
     <row r="261" ht="12.75" customHeight="1" s="70">
       <c r="F261" s="66" t="n"/>
@@ -5506,6 +5780,7 @@
       <c r="O261" s="69" t="n"/>
       <c r="P261" s="62" t="n"/>
       <c r="Q261" s="62" t="n"/>
+      <c r="R261" s="88" t="n"/>
     </row>
     <row r="262" ht="12.75" customHeight="1" s="70">
       <c r="F262" s="66" t="n"/>
@@ -5520,6 +5795,7 @@
       <c r="O262" s="69" t="n"/>
       <c r="P262" s="62" t="n"/>
       <c r="Q262" s="62" t="n"/>
+      <c r="R262" s="88" t="n"/>
     </row>
     <row r="263" ht="12.75" customHeight="1" s="70">
       <c r="F263" s="66" t="n"/>
@@ -5534,6 +5810,7 @@
       <c r="O263" s="69" t="n"/>
       <c r="P263" s="62" t="n"/>
       <c r="Q263" s="62" t="n"/>
+      <c r="R263" s="88" t="n"/>
     </row>
     <row r="264" ht="12.75" customHeight="1" s="70">
       <c r="F264" s="66" t="n"/>
@@ -5548,6 +5825,7 @@
       <c r="O264" s="69" t="n"/>
       <c r="P264" s="62" t="n"/>
       <c r="Q264" s="62" t="n"/>
+      <c r="R264" s="88" t="n"/>
     </row>
     <row r="265" ht="12.75" customHeight="1" s="70">
       <c r="F265" s="66" t="n"/>
@@ -5562,6 +5840,7 @@
       <c r="O265" s="69" t="n"/>
       <c r="P265" s="62" t="n"/>
       <c r="Q265" s="62" t="n"/>
+      <c r="R265" s="88" t="n"/>
     </row>
     <row r="266" ht="12.75" customHeight="1" s="70">
       <c r="F266" s="66" t="n"/>
@@ -5576,6 +5855,7 @@
       <c r="O266" s="69" t="n"/>
       <c r="P266" s="62" t="n"/>
       <c r="Q266" s="62" t="n"/>
+      <c r="R266" s="88" t="n"/>
     </row>
     <row r="267" ht="12.75" customHeight="1" s="70">
       <c r="F267" s="66" t="n"/>
@@ -5590,6 +5870,7 @@
       <c r="O267" s="69" t="n"/>
       <c r="P267" s="62" t="n"/>
       <c r="Q267" s="62" t="n"/>
+      <c r="R267" s="88" t="n"/>
     </row>
     <row r="268" ht="12.75" customHeight="1" s="70">
       <c r="F268" s="66" t="n"/>
@@ -5604,6 +5885,7 @@
       <c r="O268" s="69" t="n"/>
       <c r="P268" s="62" t="n"/>
       <c r="Q268" s="62" t="n"/>
+      <c r="R268" s="88" t="n"/>
     </row>
     <row r="269" ht="12.75" customHeight="1" s="70">
       <c r="F269" s="66" t="n"/>
@@ -5618,6 +5900,7 @@
       <c r="O269" s="69" t="n"/>
       <c r="P269" s="62" t="n"/>
       <c r="Q269" s="62" t="n"/>
+      <c r="R269" s="88" t="n"/>
     </row>
     <row r="270" ht="12.75" customHeight="1" s="70">
       <c r="F270" s="66" t="n"/>
@@ -5632,6 +5915,7 @@
       <c r="O270" s="69" t="n"/>
       <c r="P270" s="62" t="n"/>
       <c r="Q270" s="62" t="n"/>
+      <c r="R270" s="88" t="n"/>
     </row>
     <row r="271" ht="12.75" customHeight="1" s="70">
       <c r="F271" s="66" t="n"/>
@@ -5646,6 +5930,7 @@
       <c r="O271" s="69" t="n"/>
       <c r="P271" s="62" t="n"/>
       <c r="Q271" s="62" t="n"/>
+      <c r="R271" s="88" t="n"/>
     </row>
     <row r="272" ht="12.75" customHeight="1" s="70">
       <c r="F272" s="66" t="n"/>
@@ -5660,6 +5945,7 @@
       <c r="O272" s="69" t="n"/>
       <c r="P272" s="62" t="n"/>
       <c r="Q272" s="62" t="n"/>
+      <c r="R272" s="88" t="n"/>
     </row>
     <row r="273" ht="12.75" customHeight="1" s="70">
       <c r="F273" s="66" t="n"/>
@@ -5674,6 +5960,7 @@
       <c r="O273" s="69" t="n"/>
       <c r="P273" s="62" t="n"/>
       <c r="Q273" s="62" t="n"/>
+      <c r="R273" s="88" t="n"/>
     </row>
     <row r="274" ht="12.75" customHeight="1" s="70">
       <c r="F274" s="66" t="n"/>
@@ -5688,6 +5975,7 @@
       <c r="O274" s="69" t="n"/>
       <c r="P274" s="62" t="n"/>
       <c r="Q274" s="62" t="n"/>
+      <c r="R274" s="88" t="n"/>
     </row>
     <row r="275" ht="12.75" customHeight="1" s="70">
       <c r="F275" s="66" t="n"/>
@@ -5702,6 +5990,7 @@
       <c r="O275" s="69" t="n"/>
       <c r="P275" s="62" t="n"/>
       <c r="Q275" s="62" t="n"/>
+      <c r="R275" s="88" t="n"/>
     </row>
     <row r="276" ht="12.75" customHeight="1" s="70">
       <c r="F276" s="66" t="n"/>
@@ -5716,6 +6005,7 @@
       <c r="O276" s="69" t="n"/>
       <c r="P276" s="62" t="n"/>
       <c r="Q276" s="62" t="n"/>
+      <c r="R276" s="88" t="n"/>
     </row>
     <row r="277" ht="12.75" customHeight="1" s="70">
       <c r="F277" s="66" t="n"/>
@@ -5730,6 +6020,7 @@
       <c r="O277" s="69" t="n"/>
       <c r="P277" s="62" t="n"/>
       <c r="Q277" s="62" t="n"/>
+      <c r="R277" s="88" t="n"/>
     </row>
     <row r="278" ht="12.75" customHeight="1" s="70">
       <c r="F278" s="66" t="n"/>
@@ -5744,6 +6035,7 @@
       <c r="O278" s="69" t="n"/>
       <c r="P278" s="62" t="n"/>
       <c r="Q278" s="62" t="n"/>
+      <c r="R278" s="88" t="n"/>
     </row>
     <row r="279" ht="12.75" customHeight="1" s="70">
       <c r="F279" s="66" t="n"/>
@@ -5758,6 +6050,7 @@
       <c r="O279" s="69" t="n"/>
       <c r="P279" s="62" t="n"/>
       <c r="Q279" s="62" t="n"/>
+      <c r="R279" s="88" t="n"/>
     </row>
     <row r="280" ht="12.75" customHeight="1" s="70">
       <c r="F280" s="66" t="n"/>
@@ -5772,6 +6065,7 @@
       <c r="O280" s="69" t="n"/>
       <c r="P280" s="62" t="n"/>
       <c r="Q280" s="62" t="n"/>
+      <c r="R280" s="88" t="n"/>
     </row>
     <row r="281" ht="12.75" customHeight="1" s="70">
       <c r="F281" s="66" t="n"/>
@@ -5786,6 +6080,7 @@
       <c r="O281" s="69" t="n"/>
       <c r="P281" s="62" t="n"/>
       <c r="Q281" s="62" t="n"/>
+      <c r="R281" s="88" t="n"/>
     </row>
     <row r="282" ht="12.75" customHeight="1" s="70">
       <c r="F282" s="66" t="n"/>
@@ -5800,6 +6095,7 @@
       <c r="O282" s="69" t="n"/>
       <c r="P282" s="62" t="n"/>
       <c r="Q282" s="62" t="n"/>
+      <c r="R282" s="88" t="n"/>
     </row>
     <row r="283" ht="12.75" customHeight="1" s="70">
       <c r="F283" s="66" t="n"/>
@@ -5814,6 +6110,7 @@
       <c r="O283" s="69" t="n"/>
       <c r="P283" s="62" t="n"/>
       <c r="Q283" s="62" t="n"/>
+      <c r="R283" s="88" t="n"/>
     </row>
     <row r="284" ht="12.75" customHeight="1" s="70">
       <c r="F284" s="66" t="n"/>
@@ -5828,6 +6125,7 @@
       <c r="O284" s="69" t="n"/>
       <c r="P284" s="62" t="n"/>
       <c r="Q284" s="62" t="n"/>
+      <c r="R284" s="88" t="n"/>
     </row>
     <row r="285" ht="12.75" customHeight="1" s="70">
       <c r="F285" s="66" t="n"/>
@@ -5842,6 +6140,7 @@
       <c r="O285" s="69" t="n"/>
       <c r="P285" s="62" t="n"/>
       <c r="Q285" s="62" t="n"/>
+      <c r="R285" s="88" t="n"/>
     </row>
     <row r="286" ht="12.75" customHeight="1" s="70">
       <c r="F286" s="66" t="n"/>
@@ -5856,6 +6155,7 @@
       <c r="O286" s="69" t="n"/>
       <c r="P286" s="62" t="n"/>
       <c r="Q286" s="62" t="n"/>
+      <c r="R286" s="88" t="n"/>
     </row>
     <row r="287" ht="12.75" customHeight="1" s="70">
       <c r="F287" s="66" t="n"/>
@@ -5870,6 +6170,7 @@
       <c r="O287" s="69" t="n"/>
       <c r="P287" s="62" t="n"/>
       <c r="Q287" s="62" t="n"/>
+      <c r="R287" s="88" t="n"/>
     </row>
     <row r="288" ht="12.75" customHeight="1" s="70">
       <c r="F288" s="66" t="n"/>
@@ -5884,6 +6185,7 @@
       <c r="O288" s="69" t="n"/>
       <c r="P288" s="62" t="n"/>
       <c r="Q288" s="62" t="n"/>
+      <c r="R288" s="88" t="n"/>
     </row>
     <row r="289" ht="12.75" customHeight="1" s="70">
       <c r="F289" s="66" t="n"/>
@@ -5898,6 +6200,7 @@
       <c r="O289" s="69" t="n"/>
       <c r="P289" s="62" t="n"/>
       <c r="Q289" s="62" t="n"/>
+      <c r="R289" s="88" t="n"/>
     </row>
     <row r="290" ht="12.75" customHeight="1" s="70">
       <c r="F290" s="66" t="n"/>
@@ -5912,6 +6215,7 @@
       <c r="O290" s="69" t="n"/>
       <c r="P290" s="62" t="n"/>
       <c r="Q290" s="62" t="n"/>
+      <c r="R290" s="88" t="n"/>
     </row>
     <row r="291" ht="12.75" customHeight="1" s="70">
       <c r="F291" s="66" t="n"/>
@@ -5926,6 +6230,7 @@
       <c r="O291" s="69" t="n"/>
       <c r="P291" s="62" t="n"/>
       <c r="Q291" s="62" t="n"/>
+      <c r="R291" s="88" t="n"/>
     </row>
     <row r="292" ht="12.75" customHeight="1" s="70">
       <c r="F292" s="66" t="n"/>
@@ -5940,6 +6245,7 @@
       <c r="O292" s="69" t="n"/>
       <c r="P292" s="62" t="n"/>
       <c r="Q292" s="62" t="n"/>
+      <c r="R292" s="88" t="n"/>
     </row>
     <row r="293" ht="12.75" customHeight="1" s="70">
       <c r="F293" s="66" t="n"/>
@@ -5954,6 +6260,7 @@
       <c r="O293" s="69" t="n"/>
       <c r="P293" s="62" t="n"/>
       <c r="Q293" s="62" t="n"/>
+      <c r="R293" s="88" t="n"/>
     </row>
     <row r="294" ht="12.75" customHeight="1" s="70">
       <c r="F294" s="66" t="n"/>
@@ -5968,6 +6275,7 @@
       <c r="O294" s="69" t="n"/>
       <c r="P294" s="62" t="n"/>
       <c r="Q294" s="62" t="n"/>
+      <c r="R294" s="88" t="n"/>
     </row>
     <row r="295" ht="12.75" customHeight="1" s="70">
       <c r="F295" s="66" t="n"/>
@@ -5982,6 +6290,7 @@
       <c r="O295" s="69" t="n"/>
       <c r="P295" s="62" t="n"/>
       <c r="Q295" s="62" t="n"/>
+      <c r="R295" s="88" t="n"/>
     </row>
     <row r="296" ht="12.75" customHeight="1" s="70">
       <c r="F296" s="66" t="n"/>
@@ -5996,6 +6305,7 @@
       <c r="O296" s="69" t="n"/>
       <c r="P296" s="62" t="n"/>
       <c r="Q296" s="62" t="n"/>
+      <c r="R296" s="88" t="n"/>
     </row>
     <row r="297" ht="12.75" customHeight="1" s="70">
       <c r="F297" s="66" t="n"/>
@@ -6010,6 +6320,7 @@
       <c r="O297" s="69" t="n"/>
       <c r="P297" s="62" t="n"/>
       <c r="Q297" s="62" t="n"/>
+      <c r="R297" s="88" t="n"/>
     </row>
     <row r="298" ht="12.75" customHeight="1" s="70">
       <c r="F298" s="66" t="n"/>
@@ -6024,6 +6335,7 @@
       <c r="O298" s="69" t="n"/>
       <c r="P298" s="62" t="n"/>
       <c r="Q298" s="62" t="n"/>
+      <c r="R298" s="88" t="n"/>
     </row>
     <row r="299" ht="12.75" customHeight="1" s="70">
       <c r="F299" s="66" t="n"/>
@@ -6038,6 +6350,7 @@
       <c r="O299" s="69" t="n"/>
       <c r="P299" s="62" t="n"/>
       <c r="Q299" s="62" t="n"/>
+      <c r="R299" s="88" t="n"/>
     </row>
     <row r="300" ht="12.75" customHeight="1" s="70">
       <c r="F300" s="66" t="n"/>
@@ -6052,6 +6365,7 @@
       <c r="O300" s="69" t="n"/>
       <c r="P300" s="62" t="n"/>
       <c r="Q300" s="62" t="n"/>
+      <c r="R300" s="88" t="n"/>
     </row>
     <row r="301" ht="12.75" customHeight="1" s="70">
       <c r="F301" s="66" t="n"/>
@@ -6066,6 +6380,7 @@
       <c r="O301" s="69" t="n"/>
       <c r="P301" s="62" t="n"/>
       <c r="Q301" s="62" t="n"/>
+      <c r="R301" s="88" t="n"/>
     </row>
     <row r="302" ht="12.75" customHeight="1" s="70">
       <c r="F302" s="66" t="n"/>
@@ -6080,6 +6395,7 @@
       <c r="O302" s="69" t="n"/>
       <c r="P302" s="62" t="n"/>
       <c r="Q302" s="62" t="n"/>
+      <c r="R302" s="88" t="n"/>
     </row>
     <row r="303" ht="12.75" customHeight="1" s="70">
       <c r="F303" s="66" t="n"/>
@@ -6094,6 +6410,7 @@
       <c r="O303" s="69" t="n"/>
       <c r="P303" s="62" t="n"/>
       <c r="Q303" s="62" t="n"/>
+      <c r="R303" s="88" t="n"/>
     </row>
     <row r="304" ht="12.75" customHeight="1" s="70">
       <c r="F304" s="66" t="n"/>
@@ -6108,6 +6425,7 @@
       <c r="O304" s="69" t="n"/>
       <c r="P304" s="62" t="n"/>
       <c r="Q304" s="62" t="n"/>
+      <c r="R304" s="88" t="n"/>
     </row>
     <row r="305" ht="12.75" customHeight="1" s="70">
       <c r="F305" s="66" t="n"/>
@@ -6122,6 +6440,7 @@
       <c r="O305" s="69" t="n"/>
       <c r="P305" s="62" t="n"/>
       <c r="Q305" s="62" t="n"/>
+      <c r="R305" s="88" t="n"/>
     </row>
     <row r="306" ht="12.75" customHeight="1" s="70">
       <c r="F306" s="66" t="n"/>
@@ -6136,6 +6455,7 @@
       <c r="O306" s="69" t="n"/>
       <c r="P306" s="62" t="n"/>
       <c r="Q306" s="62" t="n"/>
+      <c r="R306" s="88" t="n"/>
     </row>
     <row r="307" ht="12.75" customHeight="1" s="70">
       <c r="F307" s="66" t="n"/>
@@ -6150,6 +6470,7 @@
       <c r="O307" s="69" t="n"/>
       <c r="P307" s="62" t="n"/>
       <c r="Q307" s="62" t="n"/>
+      <c r="R307" s="88" t="n"/>
     </row>
     <row r="308" ht="12.75" customHeight="1" s="70">
       <c r="F308" s="66" t="n"/>
@@ -6164,6 +6485,7 @@
       <c r="O308" s="69" t="n"/>
       <c r="P308" s="62" t="n"/>
       <c r="Q308" s="62" t="n"/>
+      <c r="R308" s="88" t="n"/>
     </row>
     <row r="309" ht="12.75" customHeight="1" s="70">
       <c r="F309" s="66" t="n"/>
@@ -6178,6 +6500,7 @@
       <c r="O309" s="69" t="n"/>
       <c r="P309" s="62" t="n"/>
       <c r="Q309" s="62" t="n"/>
+      <c r="R309" s="88" t="n"/>
     </row>
     <row r="310" ht="12.75" customHeight="1" s="70">
       <c r="F310" s="66" t="n"/>
@@ -6192,6 +6515,7 @@
       <c r="O310" s="69" t="n"/>
       <c r="P310" s="62" t="n"/>
       <c r="Q310" s="62" t="n"/>
+      <c r="R310" s="88" t="n"/>
     </row>
     <row r="311" ht="12.75" customHeight="1" s="70">
       <c r="F311" s="66" t="n"/>
@@ -6206,6 +6530,7 @@
       <c r="O311" s="69" t="n"/>
       <c r="P311" s="62" t="n"/>
       <c r="Q311" s="62" t="n"/>
+      <c r="R311" s="88" t="n"/>
     </row>
     <row r="312" ht="12.75" customHeight="1" s="70">
       <c r="F312" s="66" t="n"/>
@@ -6220,6 +6545,7 @@
       <c r="O312" s="69" t="n"/>
       <c r="P312" s="62" t="n"/>
       <c r="Q312" s="62" t="n"/>
+      <c r="R312" s="88" t="n"/>
     </row>
     <row r="313" ht="12.75" customHeight="1" s="70">
       <c r="F313" s="66" t="n"/>
@@ -6234,6 +6560,7 @@
       <c r="O313" s="69" t="n"/>
       <c r="P313" s="62" t="n"/>
       <c r="Q313" s="62" t="n"/>
+      <c r="R313" s="88" t="n"/>
     </row>
     <row r="314" ht="12.75" customHeight="1" s="70">
       <c r="F314" s="66" t="n"/>
@@ -6248,6 +6575,7 @@
       <c r="O314" s="69" t="n"/>
       <c r="P314" s="62" t="n"/>
       <c r="Q314" s="62" t="n"/>
+      <c r="R314" s="88" t="n"/>
     </row>
     <row r="315" ht="12.75" customHeight="1" s="70">
       <c r="F315" s="66" t="n"/>
@@ -6262,6 +6590,7 @@
       <c r="O315" s="69" t="n"/>
       <c r="P315" s="62" t="n"/>
       <c r="Q315" s="62" t="n"/>
+      <c r="R315" s="88" t="n"/>
     </row>
     <row r="316" ht="12.75" customHeight="1" s="70">
       <c r="F316" s="66" t="n"/>
@@ -6276,6 +6605,7 @@
       <c r="O316" s="69" t="n"/>
       <c r="P316" s="62" t="n"/>
       <c r="Q316" s="62" t="n"/>
+      <c r="R316" s="88" t="n"/>
     </row>
     <row r="317" ht="12.75" customHeight="1" s="70">
       <c r="F317" s="66" t="n"/>
@@ -6290,6 +6620,7 @@
       <c r="O317" s="69" t="n"/>
       <c r="P317" s="62" t="n"/>
       <c r="Q317" s="62" t="n"/>
+      <c r="R317" s="88" t="n"/>
     </row>
     <row r="318" ht="12.75" customHeight="1" s="70">
       <c r="F318" s="66" t="n"/>
@@ -6304,6 +6635,7 @@
       <c r="O318" s="69" t="n"/>
       <c r="P318" s="62" t="n"/>
       <c r="Q318" s="62" t="n"/>
+      <c r="R318" s="88" t="n"/>
     </row>
     <row r="319" ht="12.75" customHeight="1" s="70">
       <c r="F319" s="66" t="n"/>
@@ -6318,6 +6650,7 @@
       <c r="O319" s="69" t="n"/>
       <c r="P319" s="62" t="n"/>
       <c r="Q319" s="62" t="n"/>
+      <c r="R319" s="88" t="n"/>
     </row>
     <row r="320" ht="12.75" customHeight="1" s="70">
       <c r="F320" s="66" t="n"/>
@@ -6332,6 +6665,7 @@
       <c r="O320" s="69" t="n"/>
       <c r="P320" s="62" t="n"/>
       <c r="Q320" s="62" t="n"/>
+      <c r="R320" s="88" t="n"/>
     </row>
     <row r="321" ht="12.75" customHeight="1" s="70">
       <c r="F321" s="66" t="n"/>
@@ -6346,6 +6680,7 @@
       <c r="O321" s="69" t="n"/>
       <c r="P321" s="62" t="n"/>
       <c r="Q321" s="62" t="n"/>
+      <c r="R321" s="88" t="n"/>
     </row>
     <row r="322" ht="12.75" customHeight="1" s="70">
       <c r="F322" s="66" t="n"/>
@@ -6360,6 +6695,7 @@
       <c r="O322" s="69" t="n"/>
       <c r="P322" s="62" t="n"/>
       <c r="Q322" s="62" t="n"/>
+      <c r="R322" s="88" t="n"/>
     </row>
     <row r="323" ht="12.75" customHeight="1" s="70">
       <c r="F323" s="66" t="n"/>
@@ -6374,6 +6710,7 @@
       <c r="O323" s="69" t="n"/>
       <c r="P323" s="62" t="n"/>
       <c r="Q323" s="62" t="n"/>
+      <c r="R323" s="88" t="n"/>
     </row>
     <row r="324" ht="12.75" customHeight="1" s="70">
       <c r="F324" s="66" t="n"/>
@@ -6388,6 +6725,7 @@
       <c r="O324" s="69" t="n"/>
       <c r="P324" s="62" t="n"/>
       <c r="Q324" s="62" t="n"/>
+      <c r="R324" s="88" t="n"/>
     </row>
     <row r="325" ht="12.75" customHeight="1" s="70">
       <c r="F325" s="66" t="n"/>
@@ -6402,6 +6740,7 @@
       <c r="O325" s="69" t="n"/>
       <c r="P325" s="62" t="n"/>
       <c r="Q325" s="62" t="n"/>
+      <c r="R325" s="88" t="n"/>
     </row>
     <row r="326" ht="12.75" customHeight="1" s="70">
       <c r="F326" s="66" t="n"/>
@@ -6416,6 +6755,7 @@
       <c r="O326" s="69" t="n"/>
       <c r="P326" s="62" t="n"/>
       <c r="Q326" s="62" t="n"/>
+      <c r="R326" s="88" t="n"/>
     </row>
     <row r="327" ht="12.75" customHeight="1" s="70">
       <c r="F327" s="66" t="n"/>
@@ -6430,6 +6770,7 @@
       <c r="O327" s="69" t="n"/>
       <c r="P327" s="62" t="n"/>
       <c r="Q327" s="62" t="n"/>
+      <c r="R327" s="88" t="n"/>
     </row>
     <row r="328" ht="12.75" customHeight="1" s="70">
       <c r="F328" s="66" t="n"/>
@@ -6444,6 +6785,7 @@
       <c r="O328" s="69" t="n"/>
       <c r="P328" s="62" t="n"/>
       <c r="Q328" s="62" t="n"/>
+      <c r="R328" s="88" t="n"/>
     </row>
     <row r="329" ht="12.75" customHeight="1" s="70">
       <c r="F329" s="66" t="n"/>
@@ -6458,6 +6800,7 @@
       <c r="O329" s="69" t="n"/>
       <c r="P329" s="62" t="n"/>
       <c r="Q329" s="62" t="n"/>
+      <c r="R329" s="88" t="n"/>
     </row>
     <row r="330" ht="12.75" customHeight="1" s="70">
       <c r="F330" s="66" t="n"/>
@@ -6472,6 +6815,7 @@
       <c r="O330" s="69" t="n"/>
       <c r="P330" s="62" t="n"/>
       <c r="Q330" s="62" t="n"/>
+      <c r="R330" s="88" t="n"/>
     </row>
     <row r="331" ht="12.75" customHeight="1" s="70">
       <c r="F331" s="66" t="n"/>
@@ -6486,6 +6830,7 @@
       <c r="O331" s="69" t="n"/>
       <c r="P331" s="62" t="n"/>
       <c r="Q331" s="62" t="n"/>
+      <c r="R331" s="88" t="n"/>
     </row>
     <row r="332" ht="12.75" customHeight="1" s="70">
       <c r="F332" s="66" t="n"/>
@@ -6500,6 +6845,7 @@
       <c r="O332" s="69" t="n"/>
       <c r="P332" s="62" t="n"/>
       <c r="Q332" s="62" t="n"/>
+      <c r="R332" s="88" t="n"/>
     </row>
     <row r="333" ht="12.75" customHeight="1" s="70">
       <c r="F333" s="66" t="n"/>
@@ -6514,6 +6860,7 @@
       <c r="O333" s="69" t="n"/>
       <c r="P333" s="62" t="n"/>
       <c r="Q333" s="62" t="n"/>
+      <c r="R333" s="88" t="n"/>
     </row>
     <row r="334" ht="12.75" customHeight="1" s="70">
       <c r="F334" s="66" t="n"/>
@@ -6528,6 +6875,7 @@
       <c r="O334" s="69" t="n"/>
       <c r="P334" s="62" t="n"/>
       <c r="Q334" s="62" t="n"/>
+      <c r="R334" s="88" t="n"/>
     </row>
     <row r="335" ht="12.75" customHeight="1" s="70">
       <c r="F335" s="66" t="n"/>
@@ -6542,6 +6890,7 @@
       <c r="O335" s="69" t="n"/>
       <c r="P335" s="62" t="n"/>
       <c r="Q335" s="62" t="n"/>
+      <c r="R335" s="88" t="n"/>
     </row>
     <row r="336" ht="12.75" customHeight="1" s="70">
       <c r="F336" s="66" t="n"/>
@@ -6556,6 +6905,7 @@
       <c r="O336" s="69" t="n"/>
       <c r="P336" s="62" t="n"/>
       <c r="Q336" s="62" t="n"/>
+      <c r="R336" s="88" t="n"/>
     </row>
     <row r="337" ht="12.75" customHeight="1" s="70">
       <c r="F337" s="66" t="n"/>
@@ -6570,6 +6920,7 @@
       <c r="O337" s="69" t="n"/>
       <c r="P337" s="62" t="n"/>
       <c r="Q337" s="62" t="n"/>
+      <c r="R337" s="88" t="n"/>
     </row>
     <row r="338" ht="12.75" customHeight="1" s="70">
       <c r="F338" s="66" t="n"/>
@@ -6584,6 +6935,7 @@
       <c r="O338" s="69" t="n"/>
       <c r="P338" s="62" t="n"/>
       <c r="Q338" s="62" t="n"/>
+      <c r="R338" s="88" t="n"/>
     </row>
     <row r="339" ht="12.75" customHeight="1" s="70">
       <c r="F339" s="66" t="n"/>
@@ -6598,6 +6950,7 @@
       <c r="O339" s="69" t="n"/>
       <c r="P339" s="62" t="n"/>
       <c r="Q339" s="62" t="n"/>
+      <c r="R339" s="88" t="n"/>
     </row>
     <row r="340" ht="12.75" customHeight="1" s="70">
       <c r="F340" s="66" t="n"/>
@@ -6612,6 +6965,7 @@
       <c r="O340" s="69" t="n"/>
       <c r="P340" s="62" t="n"/>
       <c r="Q340" s="62" t="n"/>
+      <c r="R340" s="88" t="n"/>
     </row>
     <row r="341" ht="12.75" customHeight="1" s="70">
       <c r="F341" s="66" t="n"/>
@@ -6626,6 +6980,7 @@
       <c r="O341" s="69" t="n"/>
       <c r="P341" s="62" t="n"/>
       <c r="Q341" s="62" t="n"/>
+      <c r="R341" s="88" t="n"/>
     </row>
     <row r="342" ht="12.75" customHeight="1" s="70">
       <c r="F342" s="66" t="n"/>
@@ -6640,6 +6995,7 @@
       <c r="O342" s="69" t="n"/>
       <c r="P342" s="62" t="n"/>
       <c r="Q342" s="62" t="n"/>
+      <c r="R342" s="88" t="n"/>
     </row>
     <row r="343" ht="12.75" customHeight="1" s="70">
       <c r="F343" s="66" t="n"/>
@@ -6654,6 +7010,7 @@
       <c r="O343" s="69" t="n"/>
       <c r="P343" s="62" t="n"/>
       <c r="Q343" s="62" t="n"/>
+      <c r="R343" s="88" t="n"/>
     </row>
     <row r="344" ht="12.75" customHeight="1" s="70">
       <c r="F344" s="66" t="n"/>
@@ -6668,6 +7025,7 @@
       <c r="O344" s="69" t="n"/>
       <c r="P344" s="62" t="n"/>
       <c r="Q344" s="62" t="n"/>
+      <c r="R344" s="88" t="n"/>
     </row>
     <row r="345" ht="12.75" customHeight="1" s="70">
       <c r="F345" s="66" t="n"/>
@@ -6682,6 +7040,7 @@
       <c r="O345" s="69" t="n"/>
       <c r="P345" s="62" t="n"/>
       <c r="Q345" s="62" t="n"/>
+      <c r="R345" s="88" t="n"/>
     </row>
     <row r="346" ht="12.75" customHeight="1" s="70">
       <c r="F346" s="66" t="n"/>
@@ -6696,6 +7055,7 @@
       <c r="O346" s="69" t="n"/>
       <c r="P346" s="62" t="n"/>
       <c r="Q346" s="62" t="n"/>
+      <c r="R346" s="88" t="n"/>
     </row>
     <row r="347" ht="12.75" customHeight="1" s="70">
       <c r="F347" s="66" t="n"/>
@@ -6710,6 +7070,7 @@
       <c r="O347" s="69" t="n"/>
       <c r="P347" s="62" t="n"/>
       <c r="Q347" s="62" t="n"/>
+      <c r="R347" s="88" t="n"/>
     </row>
     <row r="348" ht="12.75" customHeight="1" s="70">
       <c r="F348" s="66" t="n"/>
@@ -6724,6 +7085,7 @@
       <c r="O348" s="69" t="n"/>
       <c r="P348" s="62" t="n"/>
       <c r="Q348" s="62" t="n"/>
+      <c r="R348" s="88" t="n"/>
     </row>
     <row r="349" ht="12.75" customHeight="1" s="70">
       <c r="F349" s="66" t="n"/>
@@ -6738,6 +7100,7 @@
       <c r="O349" s="69" t="n"/>
       <c r="P349" s="62" t="n"/>
       <c r="Q349" s="62" t="n"/>
+      <c r="R349" s="88" t="n"/>
     </row>
     <row r="350" ht="12.75" customHeight="1" s="70">
       <c r="F350" s="66" t="n"/>
@@ -6752,6 +7115,7 @@
       <c r="O350" s="69" t="n"/>
       <c r="P350" s="62" t="n"/>
       <c r="Q350" s="62" t="n"/>
+      <c r="R350" s="88" t="n"/>
     </row>
     <row r="351" ht="12.75" customHeight="1" s="70">
       <c r="F351" s="66" t="n"/>
@@ -6766,6 +7130,7 @@
       <c r="O351" s="69" t="n"/>
       <c r="P351" s="62" t="n"/>
       <c r="Q351" s="62" t="n"/>
+      <c r="R351" s="88" t="n"/>
     </row>
     <row r="352" ht="12.75" customHeight="1" s="70">
       <c r="F352" s="66" t="n"/>
@@ -6780,6 +7145,7 @@
       <c r="O352" s="69" t="n"/>
       <c r="P352" s="62" t="n"/>
       <c r="Q352" s="62" t="n"/>
+      <c r="R352" s="88" t="n"/>
     </row>
     <row r="353" ht="12.75" customHeight="1" s="70">
       <c r="F353" s="66" t="n"/>
@@ -6794,6 +7160,7 @@
       <c r="O353" s="69" t="n"/>
       <c r="P353" s="62" t="n"/>
       <c r="Q353" s="62" t="n"/>
+      <c r="R353" s="88" t="n"/>
     </row>
     <row r="354" ht="12.75" customHeight="1" s="70">
       <c r="F354" s="66" t="n"/>
@@ -6808,6 +7175,7 @@
       <c r="O354" s="69" t="n"/>
       <c r="P354" s="62" t="n"/>
       <c r="Q354" s="62" t="n"/>
+      <c r="R354" s="88" t="n"/>
     </row>
     <row r="355" ht="12.75" customHeight="1" s="70">
       <c r="F355" s="66" t="n"/>
@@ -6822,6 +7190,7 @@
       <c r="O355" s="69" t="n"/>
       <c r="P355" s="62" t="n"/>
       <c r="Q355" s="62" t="n"/>
+      <c r="R355" s="88" t="n"/>
     </row>
     <row r="356" ht="12.75" customHeight="1" s="70">
       <c r="F356" s="66" t="n"/>
@@ -6836,6 +7205,7 @@
       <c r="O356" s="69" t="n"/>
       <c r="P356" s="62" t="n"/>
       <c r="Q356" s="62" t="n"/>
+      <c r="R356" s="88" t="n"/>
     </row>
     <row r="357" ht="12.75" customHeight="1" s="70">
       <c r="F357" s="66" t="n"/>
@@ -6850,6 +7220,7 @@
       <c r="O357" s="69" t="n"/>
       <c r="P357" s="62" t="n"/>
       <c r="Q357" s="62" t="n"/>
+      <c r="R357" s="88" t="n"/>
     </row>
     <row r="358" ht="12.75" customHeight="1" s="70">
       <c r="F358" s="66" t="n"/>
@@ -6864,6 +7235,7 @@
       <c r="O358" s="69" t="n"/>
       <c r="P358" s="62" t="n"/>
       <c r="Q358" s="62" t="n"/>
+      <c r="R358" s="88" t="n"/>
     </row>
     <row r="359" ht="12.75" customHeight="1" s="70">
       <c r="F359" s="66" t="n"/>
@@ -6878,6 +7250,7 @@
       <c r="O359" s="69" t="n"/>
       <c r="P359" s="62" t="n"/>
       <c r="Q359" s="62" t="n"/>
+      <c r="R359" s="88" t="n"/>
     </row>
     <row r="360" ht="12.75" customHeight="1" s="70">
       <c r="F360" s="66" t="n"/>
@@ -6892,6 +7265,7 @@
       <c r="O360" s="69" t="n"/>
       <c r="P360" s="62" t="n"/>
       <c r="Q360" s="62" t="n"/>
+      <c r="R360" s="88" t="n"/>
     </row>
     <row r="361" ht="12.75" customHeight="1" s="70">
       <c r="F361" s="66" t="n"/>
@@ -6906,6 +7280,7 @@
       <c r="O361" s="69" t="n"/>
       <c r="P361" s="62" t="n"/>
       <c r="Q361" s="62" t="n"/>
+      <c r="R361" s="88" t="n"/>
     </row>
     <row r="362" ht="12.75" customHeight="1" s="70">
       <c r="F362" s="66" t="n"/>
@@ -6920,6 +7295,7 @@
       <c r="O362" s="69" t="n"/>
       <c r="P362" s="62" t="n"/>
       <c r="Q362" s="62" t="n"/>
+      <c r="R362" s="88" t="n"/>
     </row>
     <row r="363" ht="12.75" customHeight="1" s="70">
       <c r="F363" s="66" t="n"/>
@@ -6934,6 +7310,7 @@
       <c r="O363" s="69" t="n"/>
       <c r="P363" s="62" t="n"/>
       <c r="Q363" s="62" t="n"/>
+      <c r="R363" s="88" t="n"/>
     </row>
     <row r="364" ht="12.75" customHeight="1" s="70">
       <c r="F364" s="66" t="n"/>
@@ -6948,6 +7325,7 @@
       <c r="O364" s="69" t="n"/>
       <c r="P364" s="62" t="n"/>
       <c r="Q364" s="62" t="n"/>
+      <c r="R364" s="88" t="n"/>
     </row>
     <row r="365" ht="12.75" customHeight="1" s="70">
       <c r="F365" s="66" t="n"/>
@@ -6962,6 +7340,7 @@
       <c r="O365" s="69" t="n"/>
       <c r="P365" s="62" t="n"/>
       <c r="Q365" s="62" t="n"/>
+      <c r="R365" s="88" t="n"/>
     </row>
     <row r="366" ht="12.75" customHeight="1" s="70">
       <c r="F366" s="66" t="n"/>
@@ -6976,6 +7355,7 @@
       <c r="O366" s="69" t="n"/>
       <c r="P366" s="62" t="n"/>
       <c r="Q366" s="62" t="n"/>
+      <c r="R366" s="88" t="n"/>
     </row>
     <row r="367" ht="12.75" customHeight="1" s="70">
       <c r="F367" s="66" t="n"/>
@@ -6990,6 +7370,7 @@
       <c r="O367" s="69" t="n"/>
       <c r="P367" s="62" t="n"/>
       <c r="Q367" s="62" t="n"/>
+      <c r="R367" s="88" t="n"/>
     </row>
     <row r="368" ht="12.75" customHeight="1" s="70">
       <c r="F368" s="66" t="n"/>
@@ -7004,6 +7385,7 @@
       <c r="O368" s="69" t="n"/>
       <c r="P368" s="62" t="n"/>
       <c r="Q368" s="62" t="n"/>
+      <c r="R368" s="88" t="n"/>
     </row>
     <row r="369" ht="12.75" customHeight="1" s="70">
       <c r="F369" s="66" t="n"/>
@@ -7018,6 +7400,7 @@
       <c r="O369" s="69" t="n"/>
       <c r="P369" s="62" t="n"/>
       <c r="Q369" s="62" t="n"/>
+      <c r="R369" s="88" t="n"/>
     </row>
     <row r="370" ht="12.75" customHeight="1" s="70">
       <c r="F370" s="66" t="n"/>
@@ -7032,6 +7415,7 @@
       <c r="O370" s="69" t="n"/>
       <c r="P370" s="62" t="n"/>
       <c r="Q370" s="62" t="n"/>
+      <c r="R370" s="88" t="n"/>
     </row>
     <row r="371" ht="12.75" customHeight="1" s="70">
       <c r="F371" s="66" t="n"/>
@@ -7046,6 +7430,7 @@
       <c r="O371" s="69" t="n"/>
       <c r="P371" s="62" t="n"/>
       <c r="Q371" s="62" t="n"/>
+      <c r="R371" s="88" t="n"/>
     </row>
     <row r="372" ht="12.75" customHeight="1" s="70">
       <c r="F372" s="66" t="n"/>
@@ -7060,6 +7445,7 @@
       <c r="O372" s="69" t="n"/>
       <c r="P372" s="62" t="n"/>
       <c r="Q372" s="62" t="n"/>
+      <c r="R372" s="88" t="n"/>
     </row>
     <row r="373" ht="12.75" customHeight="1" s="70">
       <c r="F373" s="66" t="n"/>
@@ -7074,6 +7460,7 @@
       <c r="O373" s="69" t="n"/>
       <c r="P373" s="62" t="n"/>
       <c r="Q373" s="62" t="n"/>
+      <c r="R373" s="88" t="n"/>
     </row>
     <row r="374" ht="12.75" customHeight="1" s="70">
       <c r="F374" s="66" t="n"/>
@@ -7088,6 +7475,7 @@
       <c r="O374" s="69" t="n"/>
       <c r="P374" s="62" t="n"/>
       <c r="Q374" s="62" t="n"/>
+      <c r="R374" s="88" t="n"/>
     </row>
     <row r="375" ht="12.75" customHeight="1" s="70">
       <c r="F375" s="66" t="n"/>
@@ -7102,6 +7490,7 @@
       <c r="O375" s="69" t="n"/>
       <c r="P375" s="62" t="n"/>
       <c r="Q375" s="62" t="n"/>
+      <c r="R375" s="88" t="n"/>
     </row>
     <row r="376" ht="12.75" customHeight="1" s="70">
       <c r="F376" s="66" t="n"/>
@@ -7116,6 +7505,7 @@
       <c r="O376" s="69" t="n"/>
       <c r="P376" s="62" t="n"/>
       <c r="Q376" s="62" t="n"/>
+      <c r="R376" s="88" t="n"/>
     </row>
     <row r="377" ht="12.75" customHeight="1" s="70">
       <c r="F377" s="66" t="n"/>
@@ -7130,6 +7520,7 @@
       <c r="O377" s="69" t="n"/>
       <c r="P377" s="62" t="n"/>
       <c r="Q377" s="62" t="n"/>
+      <c r="R377" s="88" t="n"/>
     </row>
     <row r="378" ht="12.75" customHeight="1" s="70">
       <c r="F378" s="66" t="n"/>
@@ -7144,6 +7535,7 @@
       <c r="O378" s="69" t="n"/>
       <c r="P378" s="62" t="n"/>
       <c r="Q378" s="62" t="n"/>
+      <c r="R378" s="88" t="n"/>
     </row>
     <row r="379" ht="12.75" customHeight="1" s="70">
       <c r="F379" s="66" t="n"/>
@@ -7158,6 +7550,7 @@
       <c r="O379" s="69" t="n"/>
       <c r="P379" s="62" t="n"/>
       <c r="Q379" s="62" t="n"/>
+      <c r="R379" s="88" t="n"/>
     </row>
     <row r="380" ht="12.75" customHeight="1" s="70">
       <c r="F380" s="66" t="n"/>
@@ -7172,6 +7565,7 @@
       <c r="O380" s="69" t="n"/>
       <c r="P380" s="62" t="n"/>
       <c r="Q380" s="62" t="n"/>
+      <c r="R380" s="88" t="n"/>
     </row>
     <row r="381" ht="12.75" customHeight="1" s="70">
       <c r="F381" s="66" t="n"/>
@@ -7186,6 +7580,7 @@
       <c r="O381" s="69" t="n"/>
       <c r="P381" s="62" t="n"/>
       <c r="Q381" s="62" t="n"/>
+      <c r="R381" s="88" t="n"/>
     </row>
     <row r="382" ht="12.75" customHeight="1" s="70">
       <c r="F382" s="66" t="n"/>
@@ -7200,6 +7595,7 @@
       <c r="O382" s="69" t="n"/>
       <c r="P382" s="62" t="n"/>
       <c r="Q382" s="62" t="n"/>
+      <c r="R382" s="88" t="n"/>
     </row>
     <row r="383" ht="12.75" customHeight="1" s="70">
       <c r="F383" s="66" t="n"/>
@@ -7214,6 +7610,7 @@
       <c r="O383" s="69" t="n"/>
       <c r="P383" s="62" t="n"/>
       <c r="Q383" s="62" t="n"/>
+      <c r="R383" s="88" t="n"/>
     </row>
     <row r="384" ht="12.75" customHeight="1" s="70">
       <c r="F384" s="66" t="n"/>
@@ -7228,6 +7625,7 @@
       <c r="O384" s="69" t="n"/>
       <c r="P384" s="62" t="n"/>
       <c r="Q384" s="62" t="n"/>
+      <c r="R384" s="88" t="n"/>
     </row>
     <row r="385" ht="12.75" customHeight="1" s="70">
       <c r="F385" s="66" t="n"/>
@@ -7242,6 +7640,7 @@
       <c r="O385" s="69" t="n"/>
       <c r="P385" s="62" t="n"/>
       <c r="Q385" s="62" t="n"/>
+      <c r="R385" s="88" t="n"/>
     </row>
     <row r="386" ht="12.75" customHeight="1" s="70">
       <c r="F386" s="66" t="n"/>
@@ -7256,6 +7655,7 @@
       <c r="O386" s="69" t="n"/>
       <c r="P386" s="62" t="n"/>
       <c r="Q386" s="62" t="n"/>
+      <c r="R386" s="88" t="n"/>
     </row>
     <row r="387" ht="12.75" customHeight="1" s="70">
       <c r="F387" s="66" t="n"/>
@@ -7270,6 +7670,7 @@
       <c r="O387" s="69" t="n"/>
       <c r="P387" s="62" t="n"/>
       <c r="Q387" s="62" t="n"/>
+      <c r="R387" s="88" t="n"/>
     </row>
     <row r="388" ht="12.75" customHeight="1" s="70">
       <c r="F388" s="66" t="n"/>
@@ -7284,6 +7685,7 @@
       <c r="O388" s="69" t="n"/>
       <c r="P388" s="62" t="n"/>
       <c r="Q388" s="62" t="n"/>
+      <c r="R388" s="88" t="n"/>
     </row>
     <row r="389" ht="12.75" customHeight="1" s="70">
       <c r="F389" s="66" t="n"/>
@@ -7298,6 +7700,7 @@
       <c r="O389" s="69" t="n"/>
       <c r="P389" s="62" t="n"/>
       <c r="Q389" s="62" t="n"/>
+      <c r="R389" s="88" t="n"/>
     </row>
     <row r="390" ht="12.75" customHeight="1" s="70">
       <c r="F390" s="66" t="n"/>
@@ -7312,6 +7715,7 @@
       <c r="O390" s="69" t="n"/>
       <c r="P390" s="62" t="n"/>
       <c r="Q390" s="62" t="n"/>
+      <c r="R390" s="88" t="n"/>
     </row>
     <row r="391" ht="12.75" customHeight="1" s="70">
       <c r="F391" s="66" t="n"/>
@@ -7326,6 +7730,7 @@
       <c r="O391" s="69" t="n"/>
       <c r="P391" s="62" t="n"/>
       <c r="Q391" s="62" t="n"/>
+      <c r="R391" s="88" t="n"/>
     </row>
     <row r="392" ht="12.75" customHeight="1" s="70">
       <c r="F392" s="66" t="n"/>
@@ -7340,6 +7745,7 @@
       <c r="O392" s="69" t="n"/>
       <c r="P392" s="62" t="n"/>
       <c r="Q392" s="62" t="n"/>
+      <c r="R392" s="88" t="n"/>
     </row>
     <row r="393" ht="12.75" customHeight="1" s="70">
       <c r="F393" s="66" t="n"/>
@@ -7354,6 +7760,7 @@
       <c r="O393" s="69" t="n"/>
       <c r="P393" s="62" t="n"/>
       <c r="Q393" s="62" t="n"/>
+      <c r="R393" s="88" t="n"/>
     </row>
     <row r="394" ht="12.75" customHeight="1" s="70">
       <c r="F394" s="66" t="n"/>
@@ -7368,6 +7775,7 @@
       <c r="O394" s="69" t="n"/>
       <c r="P394" s="62" t="n"/>
       <c r="Q394" s="62" t="n"/>
+      <c r="R394" s="88" t="n"/>
     </row>
     <row r="395" ht="12.75" customHeight="1" s="70">
       <c r="F395" s="66" t="n"/>
@@ -7382,6 +7790,7 @@
       <c r="O395" s="69" t="n"/>
       <c r="P395" s="62" t="n"/>
       <c r="Q395" s="62" t="n"/>
+      <c r="R395" s="88" t="n"/>
     </row>
     <row r="396" ht="12.75" customHeight="1" s="70">
       <c r="F396" s="66" t="n"/>
@@ -7396,6 +7805,7 @@
       <c r="O396" s="69" t="n"/>
       <c r="P396" s="62" t="n"/>
       <c r="Q396" s="62" t="n"/>
+      <c r="R396" s="88" t="n"/>
     </row>
     <row r="397" ht="12.75" customHeight="1" s="70">
       <c r="F397" s="66" t="n"/>
@@ -7410,6 +7820,7 @@
       <c r="O397" s="69" t="n"/>
       <c r="P397" s="62" t="n"/>
       <c r="Q397" s="62" t="n"/>
+      <c r="R397" s="88" t="n"/>
     </row>
     <row r="398" ht="12.75" customHeight="1" s="70">
       <c r="F398" s="66" t="n"/>
@@ -7424,6 +7835,7 @@
       <c r="O398" s="69" t="n"/>
       <c r="P398" s="62" t="n"/>
       <c r="Q398" s="62" t="n"/>
+      <c r="R398" s="88" t="n"/>
     </row>
     <row r="399" ht="12.75" customHeight="1" s="70">
       <c r="F399" s="66" t="n"/>
@@ -7438,6 +7850,7 @@
       <c r="O399" s="69" t="n"/>
       <c r="P399" s="62" t="n"/>
       <c r="Q399" s="62" t="n"/>
+      <c r="R399" s="88" t="n"/>
     </row>
     <row r="400" ht="12.75" customHeight="1" s="70">
       <c r="F400" s="66" t="n"/>
@@ -7452,6 +7865,7 @@
       <c r="O400" s="69" t="n"/>
       <c r="P400" s="62" t="n"/>
       <c r="Q400" s="62" t="n"/>
+      <c r="R400" s="88" t="n"/>
     </row>
     <row r="401" ht="12.75" customHeight="1" s="70">
       <c r="F401" s="66" t="n"/>
@@ -7462,6 +7876,7 @@
       <c r="O401" s="69" t="n"/>
       <c r="P401" s="62" t="n"/>
       <c r="Q401" s="62" t="n"/>
+      <c r="R401" s="88" t="n"/>
     </row>
     <row r="402" ht="12.75" customHeight="1" s="70">
       <c r="F402" s="66" t="n"/>
@@ -7472,6 +7887,7 @@
       <c r="O402" s="69" t="n"/>
       <c r="P402" s="62" t="n"/>
       <c r="Q402" s="62" t="n"/>
+      <c r="R402" s="88" t="n"/>
     </row>
     <row r="403" ht="12.75" customHeight="1" s="70">
       <c r="F403" s="66" t="n"/>
@@ -7482,6 +7898,7 @@
       <c r="O403" s="69" t="n"/>
       <c r="P403" s="62" t="n"/>
       <c r="Q403" s="62" t="n"/>
+      <c r="R403" s="88" t="n"/>
     </row>
     <row r="404" ht="12.75" customHeight="1" s="70">
       <c r="F404" s="66" t="n"/>
@@ -7492,6 +7909,7 @@
       <c r="O404" s="69" t="n"/>
       <c r="P404" s="62" t="n"/>
       <c r="Q404" s="62" t="n"/>
+      <c r="R404" s="88" t="n"/>
     </row>
     <row r="405" ht="12.75" customHeight="1" s="70">
       <c r="F405" s="66" t="n"/>
@@ -7502,6 +7920,7 @@
       <c r="O405" s="69" t="n"/>
       <c r="P405" s="62" t="n"/>
       <c r="Q405" s="62" t="n"/>
+      <c r="R405" s="88" t="n"/>
     </row>
     <row r="406" ht="12.75" customHeight="1" s="70">
       <c r="F406" s="66" t="n"/>
@@ -7512,6 +7931,7 @@
       <c r="O406" s="69" t="n"/>
       <c r="P406" s="62" t="n"/>
       <c r="Q406" s="62" t="n"/>
+      <c r="R406" s="88" t="n"/>
     </row>
     <row r="407" ht="12.75" customHeight="1" s="70">
       <c r="F407" s="66" t="n"/>
@@ -7522,6 +7942,7 @@
       <c r="O407" s="69" t="n"/>
       <c r="P407" s="62" t="n"/>
       <c r="Q407" s="62" t="n"/>
+      <c r="R407" s="88" t="n"/>
     </row>
     <row r="408" ht="12.75" customHeight="1" s="70">
       <c r="F408" s="66" t="n"/>
@@ -7532,6 +7953,7 @@
       <c r="O408" s="69" t="n"/>
       <c r="P408" s="62" t="n"/>
       <c r="Q408" s="62" t="n"/>
+      <c r="R408" s="88" t="n"/>
     </row>
     <row r="409" ht="12.75" customHeight="1" s="70">
       <c r="F409" s="66" t="n"/>
@@ -7542,6 +7964,7 @@
       <c r="O409" s="69" t="n"/>
       <c r="P409" s="62" t="n"/>
       <c r="Q409" s="62" t="n"/>
+      <c r="R409" s="88" t="n"/>
     </row>
     <row r="410" ht="12.75" customHeight="1" s="70">
       <c r="F410" s="66" t="n"/>
@@ -7552,6 +7975,7 @@
       <c r="O410" s="69" t="n"/>
       <c r="P410" s="62" t="n"/>
       <c r="Q410" s="62" t="n"/>
+      <c r="R410" s="88" t="n"/>
     </row>
     <row r="411" ht="12.75" customHeight="1" s="70">
       <c r="F411" s="66" t="n"/>
@@ -7562,6 +7986,7 @@
       <c r="O411" s="69" t="n"/>
       <c r="P411" s="62" t="n"/>
       <c r="Q411" s="62" t="n"/>
+      <c r="R411" s="88" t="n"/>
     </row>
     <row r="412" ht="12.75" customHeight="1" s="70">
       <c r="F412" s="66" t="n"/>
@@ -7572,6 +7997,7 @@
       <c r="O412" s="69" t="n"/>
       <c r="P412" s="62" t="n"/>
       <c r="Q412" s="62" t="n"/>
+      <c r="R412" s="88" t="n"/>
     </row>
     <row r="413" ht="12.75" customHeight="1" s="70">
       <c r="F413" s="66" t="n"/>
@@ -7582,6 +8008,7 @@
       <c r="O413" s="69" t="n"/>
       <c r="P413" s="62" t="n"/>
       <c r="Q413" s="62" t="n"/>
+      <c r="R413" s="88" t="n"/>
     </row>
     <row r="414" ht="12.75" customHeight="1" s="70">
       <c r="F414" s="66" t="n"/>
@@ -7592,6 +8019,7 @@
       <c r="O414" s="69" t="n"/>
       <c r="P414" s="62" t="n"/>
       <c r="Q414" s="62" t="n"/>
+      <c r="R414" s="88" t="n"/>
     </row>
     <row r="415" ht="12.75" customHeight="1" s="70">
       <c r="F415" s="66" t="n"/>
@@ -7602,6 +8030,7 @@
       <c r="O415" s="69" t="n"/>
       <c r="P415" s="62" t="n"/>
       <c r="Q415" s="62" t="n"/>
+      <c r="R415" s="88" t="n"/>
     </row>
     <row r="416" ht="12.75" customHeight="1" s="70">
       <c r="F416" s="66" t="n"/>
@@ -7612,6 +8041,7 @@
       <c r="O416" s="69" t="n"/>
       <c r="P416" s="62" t="n"/>
       <c r="Q416" s="62" t="n"/>
+      <c r="R416" s="88" t="n"/>
     </row>
     <row r="417" ht="12.75" customHeight="1" s="70">
       <c r="F417" s="66" t="n"/>
@@ -7622,6 +8052,7 @@
       <c r="O417" s="69" t="n"/>
       <c r="P417" s="62" t="n"/>
       <c r="Q417" s="62" t="n"/>
+      <c r="R417" s="88" t="n"/>
     </row>
     <row r="418" ht="12.75" customHeight="1" s="70">
       <c r="F418" s="66" t="n"/>
@@ -7632,6 +8063,7 @@
       <c r="O418" s="69" t="n"/>
       <c r="P418" s="62" t="n"/>
       <c r="Q418" s="62" t="n"/>
+      <c r="R418" s="88" t="n"/>
     </row>
     <row r="419" ht="12.75" customHeight="1" s="70">
       <c r="F419" s="66" t="n"/>
@@ -7642,6 +8074,7 @@
       <c r="O419" s="69" t="n"/>
       <c r="P419" s="62" t="n"/>
       <c r="Q419" s="62" t="n"/>
+      <c r="R419" s="88" t="n"/>
     </row>
     <row r="420" ht="12.75" customHeight="1" s="70">
       <c r="F420" s="66" t="n"/>
@@ -7652,6 +8085,7 @@
       <c r="O420" s="69" t="n"/>
       <c r="P420" s="62" t="n"/>
       <c r="Q420" s="62" t="n"/>
+      <c r="R420" s="88" t="n"/>
     </row>
     <row r="421" ht="12.75" customHeight="1" s="70">
       <c r="F421" s="66" t="n"/>
@@ -7662,6 +8096,7 @@
       <c r="O421" s="69" t="n"/>
       <c r="P421" s="62" t="n"/>
       <c r="Q421" s="62" t="n"/>
+      <c r="R421" s="88" t="n"/>
     </row>
     <row r="422" ht="12.75" customHeight="1" s="70">
       <c r="F422" s="66" t="n"/>
@@ -7672,6 +8107,7 @@
       <c r="O422" s="69" t="n"/>
       <c r="P422" s="62" t="n"/>
       <c r="Q422" s="62" t="n"/>
+      <c r="R422" s="88" t="n"/>
     </row>
     <row r="423" ht="12.75" customHeight="1" s="70">
       <c r="F423" s="66" t="n"/>
@@ -7682,6 +8118,7 @@
       <c r="O423" s="69" t="n"/>
       <c r="P423" s="62" t="n"/>
       <c r="Q423" s="62" t="n"/>
+      <c r="R423" s="88" t="n"/>
     </row>
     <row r="424" ht="12.75" customHeight="1" s="70">
       <c r="F424" s="66" t="n"/>
@@ -7692,6 +8129,7 @@
       <c r="O424" s="69" t="n"/>
       <c r="P424" s="62" t="n"/>
       <c r="Q424" s="62" t="n"/>
+      <c r="R424" s="88" t="n"/>
     </row>
     <row r="425" ht="12.75" customHeight="1" s="70">
       <c r="F425" s="66" t="n"/>
@@ -7702,6 +8140,7 @@
       <c r="O425" s="69" t="n"/>
       <c r="P425" s="62" t="n"/>
       <c r="Q425" s="62" t="n"/>
+      <c r="R425" s="88" t="n"/>
     </row>
     <row r="426" ht="12.75" customHeight="1" s="70">
       <c r="F426" s="66" t="n"/>
@@ -7712,6 +8151,7 @@
       <c r="O426" s="69" t="n"/>
       <c r="P426" s="62" t="n"/>
       <c r="Q426" s="62" t="n"/>
+      <c r="R426" s="88" t="n"/>
     </row>
     <row r="427" ht="12.75" customHeight="1" s="70">
       <c r="F427" s="66" t="n"/>
@@ -7722,6 +8162,7 @@
       <c r="O427" s="69" t="n"/>
       <c r="P427" s="62" t="n"/>
       <c r="Q427" s="62" t="n"/>
+      <c r="R427" s="88" t="n"/>
     </row>
     <row r="428" ht="12.75" customHeight="1" s="70">
       <c r="F428" s="66" t="n"/>
@@ -7732,6 +8173,7 @@
       <c r="O428" s="69" t="n"/>
       <c r="P428" s="62" t="n"/>
       <c r="Q428" s="62" t="n"/>
+      <c r="R428" s="88" t="n"/>
     </row>
     <row r="429" ht="12.75" customHeight="1" s="70">
       <c r="F429" s="66" t="n"/>
@@ -7742,6 +8184,7 @@
       <c r="O429" s="69" t="n"/>
       <c r="P429" s="62" t="n"/>
       <c r="Q429" s="62" t="n"/>
+      <c r="R429" s="88" t="n"/>
     </row>
     <row r="430" ht="12.75" customHeight="1" s="70">
       <c r="F430" s="66" t="n"/>
@@ -7752,6 +8195,7 @@
       <c r="O430" s="69" t="n"/>
       <c r="P430" s="62" t="n"/>
       <c r="Q430" s="62" t="n"/>
+      <c r="R430" s="88" t="n"/>
     </row>
     <row r="431" ht="12.75" customHeight="1" s="70">
       <c r="F431" s="66" t="n"/>
@@ -7762,6 +8206,7 @@
       <c r="O431" s="69" t="n"/>
       <c r="P431" s="62" t="n"/>
       <c r="Q431" s="62" t="n"/>
+      <c r="R431" s="88" t="n"/>
     </row>
     <row r="432" ht="12.75" customHeight="1" s="70">
       <c r="F432" s="66" t="n"/>
@@ -7772,6 +8217,7 @@
       <c r="O432" s="69" t="n"/>
       <c r="P432" s="62" t="n"/>
       <c r="Q432" s="62" t="n"/>
+      <c r="R432" s="88" t="n"/>
     </row>
     <row r="433" ht="12.75" customHeight="1" s="70">
       <c r="F433" s="66" t="n"/>
@@ -7782,6 +8228,7 @@
       <c r="O433" s="69" t="n"/>
       <c r="P433" s="62" t="n"/>
       <c r="Q433" s="62" t="n"/>
+      <c r="R433" s="88" t="n"/>
     </row>
     <row r="434" ht="12.75" customHeight="1" s="70">
       <c r="F434" s="66" t="n"/>
@@ -7792,6 +8239,7 @@
       <c r="O434" s="69" t="n"/>
       <c r="P434" s="62" t="n"/>
       <c r="Q434" s="62" t="n"/>
+      <c r="R434" s="88" t="n"/>
     </row>
     <row r="435" ht="12.75" customHeight="1" s="70">
       <c r="F435" s="66" t="n"/>
@@ -7802,6 +8250,7 @@
       <c r="O435" s="69" t="n"/>
       <c r="P435" s="62" t="n"/>
       <c r="Q435" s="62" t="n"/>
+      <c r="R435" s="88" t="n"/>
     </row>
     <row r="436" ht="12.75" customHeight="1" s="70">
       <c r="F436" s="66" t="n"/>
@@ -7812,6 +8261,7 @@
       <c r="O436" s="69" t="n"/>
       <c r="P436" s="62" t="n"/>
       <c r="Q436" s="62" t="n"/>
+      <c r="R436" s="88" t="n"/>
     </row>
     <row r="437" ht="12.75" customHeight="1" s="70">
       <c r="F437" s="66" t="n"/>
@@ -7822,6 +8272,7 @@
       <c r="O437" s="69" t="n"/>
       <c r="P437" s="62" t="n"/>
       <c r="Q437" s="62" t="n"/>
+      <c r="R437" s="88" t="n"/>
     </row>
     <row r="438" ht="12.75" customHeight="1" s="70">
       <c r="F438" s="66" t="n"/>
@@ -7832,6 +8283,7 @@
       <c r="O438" s="69" t="n"/>
       <c r="P438" s="62" t="n"/>
       <c r="Q438" s="62" t="n"/>
+      <c r="R438" s="88" t="n"/>
     </row>
     <row r="439" ht="12.75" customHeight="1" s="70">
       <c r="F439" s="66" t="n"/>
@@ -7842,6 +8294,7 @@
       <c r="O439" s="69" t="n"/>
       <c r="P439" s="62" t="n"/>
       <c r="Q439" s="62" t="n"/>
+      <c r="R439" s="88" t="n"/>
     </row>
     <row r="440" ht="12.75" customHeight="1" s="70">
       <c r="F440" s="66" t="n"/>
@@ -7852,6 +8305,7 @@
       <c r="O440" s="69" t="n"/>
       <c r="P440" s="62" t="n"/>
       <c r="Q440" s="62" t="n"/>
+      <c r="R440" s="88" t="n"/>
     </row>
     <row r="441" ht="12.75" customHeight="1" s="70">
       <c r="F441" s="66" t="n"/>
@@ -7862,6 +8316,7 @@
       <c r="O441" s="69" t="n"/>
       <c r="P441" s="62" t="n"/>
       <c r="Q441" s="62" t="n"/>
+      <c r="R441" s="88" t="n"/>
     </row>
     <row r="442" ht="12.75" customHeight="1" s="70">
       <c r="F442" s="66" t="n"/>
@@ -7872,6 +8327,7 @@
       <c r="O442" s="69" t="n"/>
       <c r="P442" s="62" t="n"/>
       <c r="Q442" s="62" t="n"/>
+      <c r="R442" s="88" t="n"/>
     </row>
     <row r="443" ht="12.75" customHeight="1" s="70">
       <c r="F443" s="66" t="n"/>
@@ -7882,6 +8338,7 @@
       <c r="O443" s="69" t="n"/>
       <c r="P443" s="62" t="n"/>
       <c r="Q443" s="62" t="n"/>
+      <c r="R443" s="88" t="n"/>
     </row>
     <row r="444" ht="12.75" customHeight="1" s="70">
       <c r="F444" s="66" t="n"/>
@@ -7892,6 +8349,7 @@
       <c r="O444" s="69" t="n"/>
       <c r="P444" s="62" t="n"/>
       <c r="Q444" s="62" t="n"/>
+      <c r="R444" s="88" t="n"/>
     </row>
     <row r="445" ht="12.75" customHeight="1" s="70">
       <c r="F445" s="66" t="n"/>
@@ -7902,6 +8360,7 @@
       <c r="O445" s="69" t="n"/>
       <c r="P445" s="62" t="n"/>
       <c r="Q445" s="62" t="n"/>
+      <c r="R445" s="88" t="n"/>
     </row>
     <row r="446" ht="12.75" customHeight="1" s="70">
       <c r="F446" s="66" t="n"/>
@@ -7912,6 +8371,7 @@
       <c r="O446" s="69" t="n"/>
       <c r="P446" s="62" t="n"/>
       <c r="Q446" s="62" t="n"/>
+      <c r="R446" s="88" t="n"/>
     </row>
     <row r="447" ht="12.75" customHeight="1" s="70">
       <c r="F447" s="66" t="n"/>
@@ -7922,6 +8382,7 @@
       <c r="O447" s="69" t="n"/>
       <c r="P447" s="62" t="n"/>
       <c r="Q447" s="62" t="n"/>
+      <c r="R447" s="88" t="n"/>
     </row>
     <row r="448" ht="12.75" customHeight="1" s="70">
       <c r="F448" s="66" t="n"/>
@@ -7932,6 +8393,7 @@
       <c r="O448" s="69" t="n"/>
       <c r="P448" s="62" t="n"/>
       <c r="Q448" s="62" t="n"/>
+      <c r="R448" s="88" t="n"/>
     </row>
     <row r="449" ht="12.75" customHeight="1" s="70">
       <c r="F449" s="66" t="n"/>
@@ -7942,6 +8404,7 @@
       <c r="O449" s="69" t="n"/>
       <c r="P449" s="62" t="n"/>
       <c r="Q449" s="62" t="n"/>
+      <c r="R449" s="88" t="n"/>
     </row>
     <row r="450" ht="12.75" customHeight="1" s="70">
       <c r="F450" s="66" t="n"/>
@@ -7952,6 +8415,7 @@
       <c r="O450" s="69" t="n"/>
       <c r="P450" s="62" t="n"/>
       <c r="Q450" s="62" t="n"/>
+      <c r="R450" s="88" t="n"/>
     </row>
     <row r="451" ht="12.75" customHeight="1" s="70">
       <c r="F451" s="66" t="n"/>
@@ -7962,6 +8426,7 @@
       <c r="O451" s="69" t="n"/>
       <c r="P451" s="62" t="n"/>
       <c r="Q451" s="62" t="n"/>
+      <c r="R451" s="88" t="n"/>
     </row>
     <row r="452" ht="12.75" customHeight="1" s="70">
       <c r="F452" s="66" t="n"/>
@@ -7972,6 +8437,7 @@
       <c r="O452" s="69" t="n"/>
       <c r="P452" s="62" t="n"/>
       <c r="Q452" s="62" t="n"/>
+      <c r="R452" s="88" t="n"/>
     </row>
     <row r="453" ht="12.75" customHeight="1" s="70">
       <c r="F453" s="66" t="n"/>
@@ -7982,6 +8448,7 @@
       <c r="O453" s="69" t="n"/>
       <c r="P453" s="62" t="n"/>
       <c r="Q453" s="62" t="n"/>
+      <c r="R453" s="88" t="n"/>
     </row>
     <row r="454" ht="12.75" customHeight="1" s="70">
       <c r="F454" s="66" t="n"/>
@@ -7992,6 +8459,7 @@
       <c r="O454" s="69" t="n"/>
       <c r="P454" s="62" t="n"/>
       <c r="Q454" s="62" t="n"/>
+      <c r="R454" s="88" t="n"/>
     </row>
     <row r="455" ht="12.75" customHeight="1" s="70">
       <c r="F455" s="66" t="n"/>
@@ -8002,6 +8470,7 @@
       <c r="O455" s="69" t="n"/>
       <c r="P455" s="62" t="n"/>
       <c r="Q455" s="62" t="n"/>
+      <c r="R455" s="88" t="n"/>
     </row>
     <row r="456" ht="12.75" customHeight="1" s="70">
       <c r="F456" s="66" t="n"/>
@@ -8012,6 +8481,7 @@
       <c r="O456" s="69" t="n"/>
       <c r="P456" s="62" t="n"/>
       <c r="Q456" s="62" t="n"/>
+      <c r="R456" s="88" t="n"/>
     </row>
     <row r="457" ht="12.75" customHeight="1" s="70">
       <c r="F457" s="66" t="n"/>
@@ -8022,6 +8492,7 @@
       <c r="O457" s="69" t="n"/>
       <c r="P457" s="62" t="n"/>
       <c r="Q457" s="62" t="n"/>
+      <c r="R457" s="88" t="n"/>
     </row>
     <row r="458" ht="12.75" customHeight="1" s="70">
       <c r="F458" s="66" t="n"/>
@@ -8032,6 +8503,7 @@
       <c r="O458" s="69" t="n"/>
       <c r="P458" s="62" t="n"/>
       <c r="Q458" s="62" t="n"/>
+      <c r="R458" s="88" t="n"/>
     </row>
     <row r="459" ht="12.75" customHeight="1" s="70">
       <c r="F459" s="66" t="n"/>
@@ -8042,6 +8514,7 @@
       <c r="O459" s="69" t="n"/>
       <c r="P459" s="62" t="n"/>
       <c r="Q459" s="62" t="n"/>
+      <c r="R459" s="88" t="n"/>
     </row>
     <row r="460" ht="12.75" customHeight="1" s="70">
       <c r="F460" s="66" t="n"/>
@@ -8052,6 +8525,7 @@
       <c r="O460" s="69" t="n"/>
       <c r="P460" s="62" t="n"/>
       <c r="Q460" s="62" t="n"/>
+      <c r="R460" s="88" t="n"/>
     </row>
     <row r="461" ht="12.75" customHeight="1" s="70">
       <c r="F461" s="66" t="n"/>
@@ -8062,6 +8536,7 @@
       <c r="O461" s="69" t="n"/>
       <c r="P461" s="62" t="n"/>
       <c r="Q461" s="62" t="n"/>
+      <c r="R461" s="88" t="n"/>
     </row>
     <row r="462" ht="12.75" customHeight="1" s="70">
       <c r="F462" s="66" t="n"/>
@@ -8072,6 +8547,7 @@
       <c r="O462" s="69" t="n"/>
       <c r="P462" s="62" t="n"/>
       <c r="Q462" s="62" t="n"/>
+      <c r="R462" s="88" t="n"/>
     </row>
     <row r="463" ht="12.75" customHeight="1" s="70">
       <c r="F463" s="66" t="n"/>
@@ -8082,6 +8558,7 @@
       <c r="O463" s="69" t="n"/>
       <c r="P463" s="62" t="n"/>
       <c r="Q463" s="62" t="n"/>
+      <c r="R463" s="88" t="n"/>
     </row>
     <row r="464" ht="12.75" customHeight="1" s="70">
       <c r="F464" s="66" t="n"/>
@@ -8092,6 +8569,7 @@
       <c r="O464" s="69" t="n"/>
       <c r="P464" s="62" t="n"/>
       <c r="Q464" s="62" t="n"/>
+      <c r="R464" s="88" t="n"/>
     </row>
     <row r="465" ht="12.75" customHeight="1" s="70">
       <c r="F465" s="66" t="n"/>
@@ -8102,6 +8580,7 @@
       <c r="O465" s="69" t="n"/>
       <c r="P465" s="62" t="n"/>
       <c r="Q465" s="62" t="n"/>
+      <c r="R465" s="88" t="n"/>
     </row>
     <row r="466" ht="12.75" customHeight="1" s="70">
       <c r="F466" s="66" t="n"/>
@@ -8112,6 +8591,7 @@
       <c r="O466" s="69" t="n"/>
       <c r="P466" s="62" t="n"/>
       <c r="Q466" s="62" t="n"/>
+      <c r="R466" s="88" t="n"/>
     </row>
     <row r="467" ht="12.75" customHeight="1" s="70">
       <c r="F467" s="66" t="n"/>
@@ -8122,6 +8602,7 @@
       <c r="O467" s="69" t="n"/>
       <c r="P467" s="62" t="n"/>
       <c r="Q467" s="62" t="n"/>
+      <c r="R467" s="88" t="n"/>
     </row>
     <row r="468" ht="12.75" customHeight="1" s="70">
       <c r="F468" s="66" t="n"/>
@@ -8132,6 +8613,7 @@
       <c r="O468" s="69" t="n"/>
       <c r="P468" s="62" t="n"/>
       <c r="Q468" s="62" t="n"/>
+      <c r="R468" s="88" t="n"/>
     </row>
     <row r="469" ht="12.75" customHeight="1" s="70">
       <c r="F469" s="66" t="n"/>
@@ -8142,6 +8624,7 @@
       <c r="O469" s="69" t="n"/>
       <c r="P469" s="62" t="n"/>
       <c r="Q469" s="62" t="n"/>
+      <c r="R469" s="88" t="n"/>
     </row>
     <row r="470" ht="12.75" customHeight="1" s="70">
       <c r="F470" s="66" t="n"/>
@@ -8152,6 +8635,7 @@
       <c r="O470" s="69" t="n"/>
       <c r="P470" s="62" t="n"/>
       <c r="Q470" s="62" t="n"/>
+      <c r="R470" s="88" t="n"/>
     </row>
     <row r="471" ht="12.75" customHeight="1" s="70">
       <c r="F471" s="66" t="n"/>
@@ -8162,6 +8646,7 @@
       <c r="O471" s="69" t="n"/>
       <c r="P471" s="62" t="n"/>
       <c r="Q471" s="62" t="n"/>
+      <c r="R471" s="88" t="n"/>
     </row>
     <row r="472" ht="12.75" customHeight="1" s="70">
       <c r="F472" s="66" t="n"/>
@@ -8172,6 +8657,7 @@
       <c r="O472" s="69" t="n"/>
       <c r="P472" s="62" t="n"/>
       <c r="Q472" s="62" t="n"/>
+      <c r="R472" s="88" t="n"/>
     </row>
     <row r="473" ht="12.75" customHeight="1" s="70">
       <c r="F473" s="66" t="n"/>
@@ -8182,6 +8668,7 @@
       <c r="O473" s="69" t="n"/>
       <c r="P473" s="62" t="n"/>
       <c r="Q473" s="62" t="n"/>
+      <c r="R473" s="88" t="n"/>
     </row>
     <row r="474" ht="12.75" customHeight="1" s="70">
       <c r="F474" s="66" t="n"/>
@@ -8192,6 +8679,7 @@
       <c r="O474" s="69" t="n"/>
       <c r="P474" s="62" t="n"/>
       <c r="Q474" s="62" t="n"/>
+      <c r="R474" s="88" t="n"/>
     </row>
     <row r="475" ht="12.75" customHeight="1" s="70">
       <c r="F475" s="66" t="n"/>
@@ -8202,6 +8690,7 @@
       <c r="O475" s="69" t="n"/>
       <c r="P475" s="62" t="n"/>
       <c r="Q475" s="62" t="n"/>
+      <c r="R475" s="88" t="n"/>
     </row>
     <row r="476" ht="12.75" customHeight="1" s="70">
       <c r="F476" s="66" t="n"/>
@@ -8212,6 +8701,7 @@
       <c r="O476" s="69" t="n"/>
       <c r="P476" s="62" t="n"/>
       <c r="Q476" s="62" t="n"/>
+      <c r="R476" s="88" t="n"/>
     </row>
     <row r="477" ht="12.75" customHeight="1" s="70">
       <c r="F477" s="66" t="n"/>
@@ -8222,6 +8712,7 @@
       <c r="O477" s="69" t="n"/>
       <c r="P477" s="62" t="n"/>
       <c r="Q477" s="62" t="n"/>
+      <c r="R477" s="88" t="n"/>
     </row>
     <row r="478" ht="12.75" customHeight="1" s="70">
       <c r="F478" s="66" t="n"/>
@@ -8232,6 +8723,7 @@
       <c r="O478" s="69" t="n"/>
       <c r="P478" s="62" t="n"/>
       <c r="Q478" s="62" t="n"/>
+      <c r="R478" s="88" t="n"/>
     </row>
     <row r="479" ht="12.75" customHeight="1" s="70">
       <c r="F479" s="66" t="n"/>
@@ -8242,6 +8734,7 @@
       <c r="O479" s="69" t="n"/>
       <c r="P479" s="62" t="n"/>
       <c r="Q479" s="62" t="n"/>
+      <c r="R479" s="88" t="n"/>
     </row>
     <row r="480" ht="12.75" customHeight="1" s="70">
       <c r="F480" s="66" t="n"/>
@@ -8252,6 +8745,7 @@
       <c r="O480" s="69" t="n"/>
       <c r="P480" s="62" t="n"/>
       <c r="Q480" s="62" t="n"/>
+      <c r="R480" s="88" t="n"/>
     </row>
     <row r="481" ht="12.75" customHeight="1" s="70">
       <c r="F481" s="66" t="n"/>
@@ -8262,6 +8756,7 @@
       <c r="O481" s="69" t="n"/>
       <c r="P481" s="62" t="n"/>
       <c r="Q481" s="62" t="n"/>
+      <c r="R481" s="88" t="n"/>
     </row>
     <row r="482" ht="12.75" customHeight="1" s="70">
       <c r="F482" s="66" t="n"/>
@@ -8272,6 +8767,7 @@
       <c r="O482" s="69" t="n"/>
       <c r="P482" s="62" t="n"/>
       <c r="Q482" s="62" t="n"/>
+      <c r="R482" s="88" t="n"/>
     </row>
     <row r="483" ht="12.75" customHeight="1" s="70">
       <c r="F483" s="66" t="n"/>
@@ -8282,6 +8778,7 @@
       <c r="O483" s="69" t="n"/>
       <c r="P483" s="62" t="n"/>
       <c r="Q483" s="62" t="n"/>
+      <c r="R483" s="88" t="n"/>
     </row>
     <row r="484" ht="12.75" customHeight="1" s="70">
       <c r="F484" s="66" t="n"/>
@@ -8292,6 +8789,7 @@
       <c r="O484" s="69" t="n"/>
       <c r="P484" s="62" t="n"/>
       <c r="Q484" s="62" t="n"/>
+      <c r="R484" s="88" t="n"/>
     </row>
     <row r="485" ht="12.75" customHeight="1" s="70">
       <c r="F485" s="66" t="n"/>
@@ -8302,6 +8800,7 @@
       <c r="O485" s="69" t="n"/>
       <c r="P485" s="62" t="n"/>
       <c r="Q485" s="62" t="n"/>
+      <c r="R485" s="88" t="n"/>
     </row>
     <row r="486" ht="12.75" customHeight="1" s="70">
       <c r="F486" s="66" t="n"/>
@@ -8312,6 +8811,7 @@
       <c r="O486" s="69" t="n"/>
       <c r="P486" s="62" t="n"/>
       <c r="Q486" s="62" t="n"/>
+      <c r="R486" s="88" t="n"/>
     </row>
     <row r="487" ht="12.75" customHeight="1" s="70">
       <c r="F487" s="66" t="n"/>
@@ -8322,6 +8822,7 @@
       <c r="O487" s="69" t="n"/>
       <c r="P487" s="62" t="n"/>
       <c r="Q487" s="62" t="n"/>
+      <c r="R487" s="88" t="n"/>
     </row>
     <row r="488" ht="12.75" customHeight="1" s="70">
       <c r="F488" s="66" t="n"/>
@@ -8332,6 +8833,7 @@
       <c r="O488" s="69" t="n"/>
       <c r="P488" s="62" t="n"/>
       <c r="Q488" s="62" t="n"/>
+      <c r="R488" s="88" t="n"/>
     </row>
     <row r="489" ht="12.75" customHeight="1" s="70">
       <c r="F489" s="66" t="n"/>
@@ -8342,6 +8844,7 @@
       <c r="O489" s="69" t="n"/>
       <c r="P489" s="62" t="n"/>
       <c r="Q489" s="62" t="n"/>
+      <c r="R489" s="88" t="n"/>
     </row>
     <row r="490" ht="12.75" customHeight="1" s="70">
       <c r="F490" s="66" t="n"/>
@@ -8352,6 +8855,7 @@
       <c r="O490" s="69" t="n"/>
       <c r="P490" s="62" t="n"/>
       <c r="Q490" s="62" t="n"/>
+      <c r="R490" s="88" t="n"/>
     </row>
     <row r="491" ht="12.75" customHeight="1" s="70">
       <c r="F491" s="66" t="n"/>
@@ -8362,6 +8866,7 @@
       <c r="O491" s="69" t="n"/>
       <c r="P491" s="62" t="n"/>
       <c r="Q491" s="62" t="n"/>
+      <c r="R491" s="88" t="n"/>
     </row>
     <row r="492" ht="12.75" customHeight="1" s="70">
       <c r="F492" s="66" t="n"/>
@@ -8372,6 +8877,7 @@
       <c r="O492" s="69" t="n"/>
       <c r="P492" s="62" t="n"/>
       <c r="Q492" s="62" t="n"/>
+      <c r="R492" s="88" t="n"/>
     </row>
     <row r="493" ht="12.75" customHeight="1" s="70">
       <c r="F493" s="66" t="n"/>
@@ -8382,6 +8888,7 @@
       <c r="O493" s="69" t="n"/>
       <c r="P493" s="62" t="n"/>
       <c r="Q493" s="62" t="n"/>
+      <c r="R493" s="88" t="n"/>
     </row>
     <row r="494" ht="12.75" customHeight="1" s="70">
       <c r="F494" s="66" t="n"/>
@@ -8392,6 +8899,7 @@
       <c r="O494" s="69" t="n"/>
       <c r="P494" s="62" t="n"/>
       <c r="Q494" s="62" t="n"/>
+      <c r="R494" s="88" t="n"/>
     </row>
     <row r="495" ht="12.75" customHeight="1" s="70">
       <c r="F495" s="66" t="n"/>
@@ -8402,6 +8910,7 @@
       <c r="O495" s="69" t="n"/>
       <c r="P495" s="62" t="n"/>
       <c r="Q495" s="62" t="n"/>
+      <c r="R495" s="88" t="n"/>
     </row>
     <row r="496" ht="12.75" customHeight="1" s="70">
       <c r="F496" s="66" t="n"/>
@@ -8412,6 +8921,7 @@
       <c r="O496" s="69" t="n"/>
       <c r="P496" s="62" t="n"/>
       <c r="Q496" s="62" t="n"/>
+      <c r="R496" s="88" t="n"/>
     </row>
     <row r="497" ht="12.75" customHeight="1" s="70">
       <c r="F497" s="66" t="n"/>
@@ -8422,6 +8932,7 @@
       <c r="O497" s="69" t="n"/>
       <c r="P497" s="62" t="n"/>
       <c r="Q497" s="62" t="n"/>
+      <c r="R497" s="88" t="n"/>
     </row>
     <row r="498" ht="12.75" customHeight="1" s="70">
       <c r="F498" s="66" t="n"/>
@@ -8432,6 +8943,7 @@
       <c r="O498" s="69" t="n"/>
       <c r="P498" s="62" t="n"/>
       <c r="Q498" s="62" t="n"/>
+      <c r="R498" s="88" t="n"/>
     </row>
     <row r="499" ht="12.75" customHeight="1" s="70">
       <c r="F499" s="66" t="n"/>
@@ -8442,6 +8954,7 @@
       <c r="O499" s="69" t="n"/>
       <c r="P499" s="62" t="n"/>
       <c r="Q499" s="62" t="n"/>
+      <c r="R499" s="88" t="n"/>
     </row>
     <row r="500" ht="12.75" customHeight="1" s="70">
       <c r="F500" s="66" t="n"/>
@@ -8452,6 +8965,7 @@
       <c r="O500" s="69" t="n"/>
       <c r="P500" s="62" t="n"/>
       <c r="Q500" s="62" t="n"/>
+      <c r="R500" s="88" t="n"/>
     </row>
     <row r="501" ht="12.75" customHeight="1" s="70">
       <c r="F501" s="66" t="n"/>
@@ -8462,6 +8976,7 @@
       <c r="O501" s="69" t="n"/>
       <c r="P501" s="62" t="n"/>
       <c r="Q501" s="62" t="n"/>
+      <c r="R501" s="88" t="n"/>
     </row>
     <row r="502" ht="12.75" customHeight="1" s="70">
       <c r="F502" s="66" t="n"/>
@@ -8472,6 +8987,7 @@
       <c r="O502" s="69" t="n"/>
       <c r="P502" s="62" t="n"/>
       <c r="Q502" s="62" t="n"/>
+      <c r="R502" s="88" t="n"/>
     </row>
     <row r="503" ht="12.75" customHeight="1" s="70">
       <c r="F503" s="66" t="n"/>
@@ -8482,6 +8998,7 @@
       <c r="O503" s="69" t="n"/>
       <c r="P503" s="62" t="n"/>
       <c r="Q503" s="62" t="n"/>
+      <c r="R503" s="88" t="n"/>
     </row>
     <row r="504" ht="12.75" customHeight="1" s="70">
       <c r="F504" s="66" t="n"/>
@@ -8492,6 +9009,7 @@
       <c r="O504" s="69" t="n"/>
       <c r="P504" s="62" t="n"/>
       <c r="Q504" s="62" t="n"/>
+      <c r="R504" s="88" t="n"/>
     </row>
     <row r="505" ht="12.75" customHeight="1" s="70">
       <c r="F505" s="66" t="n"/>
@@ -8502,6 +9020,7 @@
       <c r="O505" s="69" t="n"/>
       <c r="P505" s="62" t="n"/>
       <c r="Q505" s="62" t="n"/>
+      <c r="R505" s="88" t="n"/>
     </row>
     <row r="506" ht="12.75" customHeight="1" s="70">
       <c r="F506" s="66" t="n"/>
@@ -8512,6 +9031,7 @@
       <c r="O506" s="69" t="n"/>
       <c r="P506" s="62" t="n"/>
       <c r="Q506" s="62" t="n"/>
+      <c r="R506" s="88" t="n"/>
     </row>
     <row r="507" ht="12.75" customHeight="1" s="70">
       <c r="F507" s="66" t="n"/>
@@ -8522,6 +9042,7 @@
       <c r="O507" s="69" t="n"/>
       <c r="P507" s="62" t="n"/>
       <c r="Q507" s="62" t="n"/>
+      <c r="R507" s="88" t="n"/>
     </row>
     <row r="508" ht="12.75" customHeight="1" s="70">
       <c r="F508" s="66" t="n"/>
@@ -8532,6 +9053,7 @@
       <c r="O508" s="69" t="n"/>
       <c r="P508" s="62" t="n"/>
       <c r="Q508" s="62" t="n"/>
+      <c r="R508" s="88" t="n"/>
     </row>
     <row r="509" ht="12.75" customHeight="1" s="70">
       <c r="F509" s="66" t="n"/>
@@ -8542,6 +9064,7 @@
       <c r="O509" s="69" t="n"/>
       <c r="P509" s="62" t="n"/>
       <c r="Q509" s="62" t="n"/>
+      <c r="R509" s="88" t="n"/>
     </row>
     <row r="510" ht="12.75" customHeight="1" s="70">
       <c r="F510" s="66" t="n"/>
@@ -8552,6 +9075,7 @@
       <c r="O510" s="69" t="n"/>
       <c r="P510" s="62" t="n"/>
       <c r="Q510" s="62" t="n"/>
+      <c r="R510" s="88" t="n"/>
     </row>
     <row r="511" ht="12.75" customHeight="1" s="70">
       <c r="F511" s="66" t="n"/>
@@ -8562,6 +9086,7 @@
       <c r="O511" s="69" t="n"/>
       <c r="P511" s="62" t="n"/>
       <c r="Q511" s="62" t="n"/>
+      <c r="R511" s="88" t="n"/>
     </row>
     <row r="512" ht="12.75" customHeight="1" s="70">
       <c r="F512" s="66" t="n"/>
@@ -8572,6 +9097,7 @@
       <c r="O512" s="69" t="n"/>
       <c r="P512" s="62" t="n"/>
       <c r="Q512" s="62" t="n"/>
+      <c r="R512" s="88" t="n"/>
     </row>
     <row r="513" ht="12.75" customHeight="1" s="70">
       <c r="F513" s="66" t="n"/>
@@ -8582,6 +9108,7 @@
       <c r="O513" s="69" t="n"/>
       <c r="P513" s="62" t="n"/>
       <c r="Q513" s="62" t="n"/>
+      <c r="R513" s="88" t="n"/>
     </row>
     <row r="514" ht="12.75" customHeight="1" s="70">
       <c r="F514" s="66" t="n"/>
@@ -8592,6 +9119,7 @@
       <c r="O514" s="69" t="n"/>
       <c r="P514" s="62" t="n"/>
       <c r="Q514" s="62" t="n"/>
+      <c r="R514" s="88" t="n"/>
     </row>
     <row r="515" ht="12.75" customHeight="1" s="70">
       <c r="F515" s="66" t="n"/>
@@ -8602,6 +9130,7 @@
       <c r="O515" s="69" t="n"/>
       <c r="P515" s="62" t="n"/>
       <c r="Q515" s="62" t="n"/>
+      <c r="R515" s="88" t="n"/>
     </row>
     <row r="516" ht="12.75" customHeight="1" s="70">
       <c r="F516" s="66" t="n"/>
@@ -8612,6 +9141,7 @@
       <c r="O516" s="69" t="n"/>
       <c r="P516" s="62" t="n"/>
       <c r="Q516" s="62" t="n"/>
+      <c r="R516" s="88" t="n"/>
     </row>
     <row r="517" ht="12.75" customHeight="1" s="70">
       <c r="F517" s="66" t="n"/>
@@ -8622,6 +9152,7 @@
       <c r="O517" s="69" t="n"/>
       <c r="P517" s="62" t="n"/>
       <c r="Q517" s="62" t="n"/>
+      <c r="R517" s="88" t="n"/>
     </row>
     <row r="518" ht="12.75" customHeight="1" s="70">
       <c r="F518" s="66" t="n"/>
@@ -8632,6 +9163,7 @@
       <c r="O518" s="69" t="n"/>
       <c r="P518" s="62" t="n"/>
       <c r="Q518" s="62" t="n"/>
+      <c r="R518" s="88" t="n"/>
     </row>
     <row r="519" ht="12.75" customHeight="1" s="70">
       <c r="F519" s="66" t="n"/>
@@ -8642,6 +9174,7 @@
       <c r="O519" s="69" t="n"/>
       <c r="P519" s="62" t="n"/>
       <c r="Q519" s="62" t="n"/>
+      <c r="R519" s="88" t="n"/>
     </row>
     <row r="520" ht="12.75" customHeight="1" s="70">
       <c r="F520" s="66" t="n"/>
@@ -8652,6 +9185,7 @@
       <c r="O520" s="69" t="n"/>
       <c r="P520" s="62" t="n"/>
       <c r="Q520" s="62" t="n"/>
+      <c r="R520" s="88" t="n"/>
     </row>
     <row r="521" ht="12.75" customHeight="1" s="70">
       <c r="F521" s="66" t="n"/>
@@ -8662,6 +9196,7 @@
       <c r="O521" s="69" t="n"/>
       <c r="P521" s="62" t="n"/>
       <c r="Q521" s="62" t="n"/>
+      <c r="R521" s="88" t="n"/>
     </row>
     <row r="522" ht="12.75" customHeight="1" s="70">
       <c r="F522" s="66" t="n"/>
@@ -8672,6 +9207,7 @@
       <c r="O522" s="69" t="n"/>
       <c r="P522" s="62" t="n"/>
       <c r="Q522" s="62" t="n"/>
+      <c r="R522" s="88" t="n"/>
     </row>
     <row r="523" ht="12.75" customHeight="1" s="70">
       <c r="F523" s="66" t="n"/>
@@ -8682,6 +9218,7 @@
       <c r="O523" s="69" t="n"/>
       <c r="P523" s="62" t="n"/>
       <c r="Q523" s="62" t="n"/>
+      <c r="R523" s="88" t="n"/>
     </row>
     <row r="524" ht="12.75" customHeight="1" s="70">
       <c r="F524" s="66" t="n"/>
@@ -8692,6 +9229,7 @@
       <c r="O524" s="69" t="n"/>
       <c r="P524" s="62" t="n"/>
       <c r="Q524" s="62" t="n"/>
+      <c r="R524" s="88" t="n"/>
     </row>
     <row r="525" ht="12.75" customHeight="1" s="70">
       <c r="F525" s="66" t="n"/>
@@ -8702,6 +9240,7 @@
       <c r="O525" s="69" t="n"/>
       <c r="P525" s="62" t="n"/>
       <c r="Q525" s="62" t="n"/>
+      <c r="R525" s="88" t="n"/>
     </row>
     <row r="526" ht="12.75" customHeight="1" s="70">
       <c r="F526" s="66" t="n"/>
@@ -8712,6 +9251,7 @@
       <c r="O526" s="69" t="n"/>
       <c r="P526" s="62" t="n"/>
       <c r="Q526" s="62" t="n"/>
+      <c r="R526" s="88" t="n"/>
     </row>
     <row r="527" ht="12.75" customHeight="1" s="70">
       <c r="F527" s="66" t="n"/>
@@ -8722,6 +9262,7 @@
       <c r="O527" s="69" t="n"/>
       <c r="P527" s="62" t="n"/>
       <c r="Q527" s="62" t="n"/>
+      <c r="R527" s="88" t="n"/>
     </row>
     <row r="528" ht="12.75" customHeight="1" s="70">
       <c r="F528" s="66" t="n"/>
@@ -8732,6 +9273,7 @@
       <c r="O528" s="69" t="n"/>
       <c r="P528" s="62" t="n"/>
       <c r="Q528" s="62" t="n"/>
+      <c r="R528" s="88" t="n"/>
     </row>
     <row r="529" ht="12.75" customHeight="1" s="70">
       <c r="F529" s="66" t="n"/>
@@ -8742,6 +9284,7 @@
       <c r="O529" s="69" t="n"/>
       <c r="P529" s="62" t="n"/>
       <c r="Q529" s="62" t="n"/>
+      <c r="R529" s="88" t="n"/>
     </row>
     <row r="530" ht="12.75" customHeight="1" s="70">
       <c r="F530" s="66" t="n"/>
@@ -8752,6 +9295,7 @@
       <c r="O530" s="69" t="n"/>
       <c r="P530" s="62" t="n"/>
       <c r="Q530" s="62" t="n"/>
+      <c r="R530" s="88" t="n"/>
     </row>
     <row r="531" ht="12.75" customHeight="1" s="70">
       <c r="F531" s="66" t="n"/>
@@ -8762,6 +9306,7 @@
       <c r="O531" s="69" t="n"/>
       <c r="P531" s="62" t="n"/>
       <c r="Q531" s="62" t="n"/>
+      <c r="R531" s="88" t="n"/>
     </row>
     <row r="532" ht="12.75" customHeight="1" s="70">
       <c r="F532" s="66" t="n"/>
@@ -8772,6 +9317,7 @@
       <c r="O532" s="69" t="n"/>
       <c r="P532" s="62" t="n"/>
       <c r="Q532" s="62" t="n"/>
+      <c r="R532" s="88" t="n"/>
     </row>
     <row r="533" ht="12.75" customHeight="1" s="70">
       <c r="F533" s="66" t="n"/>
@@ -8782,6 +9328,7 @@
       <c r="O533" s="69" t="n"/>
       <c r="P533" s="62" t="n"/>
       <c r="Q533" s="62" t="n"/>
+      <c r="R533" s="88" t="n"/>
     </row>
     <row r="534" ht="12.75" customHeight="1" s="70">
       <c r="F534" s="66" t="n"/>
@@ -8792,6 +9339,7 @@
       <c r="O534" s="69" t="n"/>
       <c r="P534" s="62" t="n"/>
       <c r="Q534" s="62" t="n"/>
+      <c r="R534" s="88" t="n"/>
     </row>
     <row r="535" ht="12.75" customHeight="1" s="70">
       <c r="F535" s="66" t="n"/>
@@ -8802,6 +9350,7 @@
       <c r="O535" s="69" t="n"/>
       <c r="P535" s="62" t="n"/>
       <c r="Q535" s="62" t="n"/>
+      <c r="R535" s="88" t="n"/>
     </row>
     <row r="536" ht="12.75" customHeight="1" s="70">
       <c r="F536" s="66" t="n"/>
@@ -8812,6 +9361,7 @@
       <c r="O536" s="69" t="n"/>
       <c r="P536" s="62" t="n"/>
       <c r="Q536" s="62" t="n"/>
+      <c r="R536" s="88" t="n"/>
     </row>
     <row r="537" ht="12.75" customHeight="1" s="70">
       <c r="F537" s="66" t="n"/>
@@ -8822,6 +9372,7 @@
       <c r="O537" s="69" t="n"/>
       <c r="P537" s="62" t="n"/>
       <c r="Q537" s="62" t="n"/>
+      <c r="R537" s="88" t="n"/>
     </row>
     <row r="538" ht="12.75" customHeight="1" s="70">
       <c r="F538" s="66" t="n"/>
@@ -8832,6 +9383,7 @@
       <c r="O538" s="69" t="n"/>
       <c r="P538" s="62" t="n"/>
       <c r="Q538" s="62" t="n"/>
+      <c r="R538" s="88" t="n"/>
     </row>
     <row r="539" ht="12.75" customHeight="1" s="70">
       <c r="F539" s="66" t="n"/>
@@ -8842,6 +9394,7 @@
       <c r="O539" s="69" t="n"/>
       <c r="P539" s="62" t="n"/>
       <c r="Q539" s="62" t="n"/>
+      <c r="R539" s="88" t="n"/>
     </row>
     <row r="540" ht="12.75" customHeight="1" s="70">
       <c r="F540" s="66" t="n"/>
@@ -8852,6 +9405,7 @@
       <c r="O540" s="69" t="n"/>
       <c r="P540" s="62" t="n"/>
       <c r="Q540" s="62" t="n"/>
+      <c r="R540" s="88" t="n"/>
     </row>
     <row r="541" ht="12.75" customHeight="1" s="70">
       <c r="F541" s="66" t="n"/>
@@ -8862,6 +9416,7 @@
       <c r="O541" s="69" t="n"/>
       <c r="P541" s="62" t="n"/>
       <c r="Q541" s="62" t="n"/>
+      <c r="R541" s="88" t="n"/>
     </row>
     <row r="542" ht="12.75" customHeight="1" s="70">
       <c r="F542" s="66" t="n"/>
@@ -8872,6 +9427,7 @@
       <c r="O542" s="69" t="n"/>
       <c r="P542" s="62" t="n"/>
       <c r="Q542" s="62" t="n"/>
+      <c r="R542" s="88" t="n"/>
     </row>
     <row r="543" ht="12.75" customHeight="1" s="70">
       <c r="F543" s="66" t="n"/>
@@ -8882,6 +9438,7 @@
       <c r="O543" s="69" t="n"/>
       <c r="P543" s="62" t="n"/>
       <c r="Q543" s="62" t="n"/>
+      <c r="R543" s="88" t="n"/>
     </row>
     <row r="544" ht="12.75" customHeight="1" s="70">
       <c r="F544" s="66" t="n"/>
@@ -8892,6 +9449,7 @@
       <c r="O544" s="69" t="n"/>
       <c r="P544" s="62" t="n"/>
       <c r="Q544" s="62" t="n"/>
+      <c r="R544" s="88" t="n"/>
     </row>
     <row r="545" ht="12.75" customHeight="1" s="70">
       <c r="F545" s="66" t="n"/>
@@ -8902,6 +9460,7 @@
       <c r="O545" s="69" t="n"/>
       <c r="P545" s="62" t="n"/>
       <c r="Q545" s="62" t="n"/>
+      <c r="R545" s="88" t="n"/>
     </row>
     <row r="546" ht="12.75" customHeight="1" s="70">
       <c r="F546" s="66" t="n"/>
@@ -8912,6 +9471,7 @@
       <c r="O546" s="69" t="n"/>
       <c r="P546" s="62" t="n"/>
       <c r="Q546" s="62" t="n"/>
+      <c r="R546" s="88" t="n"/>
     </row>
     <row r="547" ht="12.75" customHeight="1" s="70">
       <c r="F547" s="66" t="n"/>
@@ -8922,6 +9482,7 @@
       <c r="O547" s="69" t="n"/>
       <c r="P547" s="62" t="n"/>
       <c r="Q547" s="62" t="n"/>
+      <c r="R547" s="88" t="n"/>
     </row>
     <row r="548" ht="12.75" customHeight="1" s="70">
       <c r="F548" s="66" t="n"/>
@@ -8932,6 +9493,7 @@
       <c r="O548" s="69" t="n"/>
       <c r="P548" s="62" t="n"/>
       <c r="Q548" s="62" t="n"/>
+      <c r="R548" s="88" t="n"/>
     </row>
     <row r="549" ht="12.75" customHeight="1" s="70">
       <c r="F549" s="66" t="n"/>
@@ -8942,6 +9504,7 @@
       <c r="O549" s="69" t="n"/>
       <c r="P549" s="62" t="n"/>
       <c r="Q549" s="62" t="n"/>
+      <c r="R549" s="88" t="n"/>
     </row>
     <row r="550" ht="12.75" customHeight="1" s="70">
       <c r="F550" s="66" t="n"/>
@@ -8952,6 +9515,7 @@
       <c r="O550" s="69" t="n"/>
       <c r="P550" s="62" t="n"/>
       <c r="Q550" s="62" t="n"/>
+      <c r="R550" s="88" t="n"/>
     </row>
     <row r="551" ht="12.75" customHeight="1" s="70">
       <c r="F551" s="66" t="n"/>
@@ -8962,6 +9526,7 @@
       <c r="O551" s="69" t="n"/>
       <c r="P551" s="62" t="n"/>
       <c r="Q551" s="62" t="n"/>
+      <c r="R551" s="88" t="n"/>
     </row>
     <row r="552" ht="12.75" customHeight="1" s="70">
       <c r="F552" s="66" t="n"/>
@@ -8972,6 +9537,7 @@
       <c r="O552" s="69" t="n"/>
       <c r="P552" s="62" t="n"/>
       <c r="Q552" s="62" t="n"/>
+      <c r="R552" s="88" t="n"/>
     </row>
     <row r="553" ht="12.75" customHeight="1" s="70">
       <c r="F553" s="66" t="n"/>
@@ -8982,6 +9548,7 @@
       <c r="O553" s="69" t="n"/>
       <c r="P553" s="62" t="n"/>
       <c r="Q553" s="62" t="n"/>
+      <c r="R553" s="88" t="n"/>
     </row>
     <row r="554" ht="12.75" customHeight="1" s="70">
       <c r="F554" s="66" t="n"/>
@@ -8992,6 +9559,7 @@
       <c r="O554" s="69" t="n"/>
       <c r="P554" s="62" t="n"/>
       <c r="Q554" s="62" t="n"/>
+      <c r="R554" s="88" t="n"/>
     </row>
     <row r="555" ht="12.75" customHeight="1" s="70">
       <c r="F555" s="66" t="n"/>
@@ -9002,6 +9570,7 @@
       <c r="O555" s="69" t="n"/>
       <c r="P555" s="62" t="n"/>
       <c r="Q555" s="62" t="n"/>
+      <c r="R555" s="88" t="n"/>
     </row>
     <row r="556" ht="12.75" customHeight="1" s="70">
       <c r="F556" s="66" t="n"/>
@@ -9012,6 +9581,7 @@
       <c r="O556" s="69" t="n"/>
       <c r="P556" s="62" t="n"/>
       <c r="Q556" s="62" t="n"/>
+      <c r="R556" s="88" t="n"/>
     </row>
     <row r="557" ht="12.75" customHeight="1" s="70">
       <c r="F557" s="66" t="n"/>
@@ -9022,6 +9592,7 @@
       <c r="O557" s="69" t="n"/>
       <c r="P557" s="62" t="n"/>
       <c r="Q557" s="62" t="n"/>
+      <c r="R557" s="88" t="n"/>
     </row>
     <row r="558" ht="12.75" customHeight="1" s="70">
       <c r="F558" s="66" t="n"/>
@@ -9032,6 +9603,7 @@
       <c r="O558" s="69" t="n"/>
       <c r="P558" s="62" t="n"/>
       <c r="Q558" s="62" t="n"/>
+      <c r="R558" s="88" t="n"/>
     </row>
     <row r="559" ht="12.75" customHeight="1" s="70">
       <c r="F559" s="66" t="n"/>
@@ -9042,6 +9614,7 @@
       <c r="O559" s="69" t="n"/>
       <c r="P559" s="62" t="n"/>
       <c r="Q559" s="62" t="n"/>
+      <c r="R559" s="88" t="n"/>
     </row>
     <row r="560" ht="12.75" customHeight="1" s="70">
       <c r="F560" s="66" t="n"/>
@@ -9052,6 +9625,7 @@
       <c r="O560" s="69" t="n"/>
       <c r="P560" s="62" t="n"/>
       <c r="Q560" s="62" t="n"/>
+      <c r="R560" s="88" t="n"/>
     </row>
     <row r="561" ht="12.75" customHeight="1" s="70">
       <c r="F561" s="66" t="n"/>
@@ -9062,6 +9636,7 @@
       <c r="O561" s="69" t="n"/>
       <c r="P561" s="62" t="n"/>
       <c r="Q561" s="62" t="n"/>
+      <c r="R561" s="88" t="n"/>
     </row>
     <row r="562" ht="12.75" customHeight="1" s="70">
       <c r="F562" s="66" t="n"/>
@@ -9072,6 +9647,7 @@
       <c r="O562" s="69" t="n"/>
       <c r="P562" s="62" t="n"/>
       <c r="Q562" s="62" t="n"/>
+      <c r="R562" s="88" t="n"/>
     </row>
     <row r="563" ht="12.75" customHeight="1" s="70">
       <c r="F563" s="66" t="n"/>
@@ -9082,6 +9658,7 @@
       <c r="O563" s="69" t="n"/>
       <c r="P563" s="62" t="n"/>
       <c r="Q563" s="62" t="n"/>
+      <c r="R563" s="88" t="n"/>
     </row>
     <row r="564" ht="12.75" customHeight="1" s="70">
       <c r="F564" s="66" t="n"/>
@@ -9092,6 +9669,7 @@
       <c r="O564" s="69" t="n"/>
       <c r="P564" s="62" t="n"/>
       <c r="Q564" s="62" t="n"/>
+      <c r="R564" s="88" t="n"/>
     </row>
     <row r="565" ht="12.75" customHeight="1" s="70">
       <c r="F565" s="66" t="n"/>
@@ -9102,6 +9680,7 @@
       <c r="O565" s="69" t="n"/>
       <c r="P565" s="62" t="n"/>
       <c r="Q565" s="62" t="n"/>
+      <c r="R565" s="88" t="n"/>
     </row>
     <row r="566" ht="12.75" customHeight="1" s="70">
       <c r="F566" s="66" t="n"/>
@@ -9112,6 +9691,7 @@
       <c r="O566" s="69" t="n"/>
       <c r="P566" s="62" t="n"/>
       <c r="Q566" s="62" t="n"/>
+      <c r="R566" s="88" t="n"/>
     </row>
     <row r="567" ht="12.75" customHeight="1" s="70">
       <c r="F567" s="66" t="n"/>
@@ -9122,6 +9702,7 @@
       <c r="O567" s="69" t="n"/>
       <c r="P567" s="62" t="n"/>
       <c r="Q567" s="62" t="n"/>
+      <c r="R567" s="88" t="n"/>
     </row>
     <row r="568" ht="12.75" customHeight="1" s="70">
       <c r="F568" s="66" t="n"/>
@@ -9132,6 +9713,7 @@
       <c r="O568" s="69" t="n"/>
       <c r="P568" s="62" t="n"/>
       <c r="Q568" s="62" t="n"/>
+      <c r="R568" s="88" t="n"/>
     </row>
     <row r="569" ht="12.75" customHeight="1" s="70">
       <c r="F569" s="66" t="n"/>
@@ -9142,6 +9724,7 @@
       <c r="O569" s="69" t="n"/>
       <c r="P569" s="62" t="n"/>
       <c r="Q569" s="62" t="n"/>
+      <c r="R569" s="88" t="n"/>
     </row>
     <row r="570" ht="12.75" customHeight="1" s="70">
       <c r="F570" s="66" t="n"/>
@@ -9152,6 +9735,7 @@
       <c r="O570" s="69" t="n"/>
       <c r="P570" s="62" t="n"/>
       <c r="Q570" s="62" t="n"/>
+      <c r="R570" s="88" t="n"/>
     </row>
     <row r="571" ht="12.75" customHeight="1" s="70">
       <c r="F571" s="66" t="n"/>
@@ -9162,6 +9746,7 @@
       <c r="O571" s="69" t="n"/>
       <c r="P571" s="62" t="n"/>
       <c r="Q571" s="62" t="n"/>
+      <c r="R571" s="88" t="n"/>
     </row>
     <row r="572" ht="12.75" customHeight="1" s="70">
       <c r="F572" s="66" t="n"/>
@@ -9172,6 +9757,7 @@
       <c r="O572" s="69" t="n"/>
       <c r="P572" s="62" t="n"/>
       <c r="Q572" s="62" t="n"/>
+      <c r="R572" s="88" t="n"/>
     </row>
     <row r="573" ht="12.75" customHeight="1" s="70">
       <c r="F573" s="66" t="n"/>
@@ -9182,6 +9768,7 @@
       <c r="O573" s="69" t="n"/>
       <c r="P573" s="62" t="n"/>
       <c r="Q573" s="62" t="n"/>
+      <c r="R573" s="88" t="n"/>
     </row>
     <row r="574" ht="12.75" customHeight="1" s="70">
       <c r="F574" s="66" t="n"/>
@@ -9192,6 +9779,7 @@
       <c r="O574" s="69" t="n"/>
       <c r="P574" s="62" t="n"/>
       <c r="Q574" s="62" t="n"/>
+      <c r="R574" s="88" t="n"/>
     </row>
     <row r="575" ht="12.75" customHeight="1" s="70">
       <c r="F575" s="66" t="n"/>
@@ -9202,6 +9790,7 @@
       <c r="O575" s="69" t="n"/>
       <c r="P575" s="62" t="n"/>
       <c r="Q575" s="62" t="n"/>
+      <c r="R575" s="88" t="n"/>
     </row>
     <row r="576" ht="12.75" customHeight="1" s="70">
       <c r="F576" s="66" t="n"/>
@@ -9212,6 +9801,7 @@
       <c r="O576" s="69" t="n"/>
       <c r="P576" s="62" t="n"/>
       <c r="Q576" s="62" t="n"/>
+      <c r="R576" s="88" t="n"/>
     </row>
     <row r="577" ht="12.75" customHeight="1" s="70">
       <c r="F577" s="66" t="n"/>
@@ -9222,6 +9812,7 @@
       <c r="O577" s="69" t="n"/>
       <c r="P577" s="62" t="n"/>
       <c r="Q577" s="62" t="n"/>
+      <c r="R577" s="88" t="n"/>
     </row>
     <row r="578" ht="12.75" customHeight="1" s="70">
       <c r="F578" s="66" t="n"/>
@@ -9232,6 +9823,7 @@
       <c r="O578" s="69" t="n"/>
       <c r="P578" s="62" t="n"/>
       <c r="Q578" s="62" t="n"/>
+      <c r="R578" s="88" t="n"/>
     </row>
     <row r="579" ht="12.75" customHeight="1" s="70">
       <c r="F579" s="66" t="n"/>
@@ -9242,6 +9834,7 @@
       <c r="O579" s="69" t="n"/>
       <c r="P579" s="62" t="n"/>
       <c r="Q579" s="62" t="n"/>
+      <c r="R579" s="88" t="n"/>
     </row>
     <row r="580" ht="12.75" customHeight="1" s="70">
       <c r="F580" s="66" t="n"/>
@@ -9252,6 +9845,7 @@
       <c r="O580" s="69" t="n"/>
       <c r="P580" s="62" t="n"/>
       <c r="Q580" s="62" t="n"/>
+      <c r="R580" s="88" t="n"/>
     </row>
     <row r="581" ht="12.75" customHeight="1" s="70">
       <c r="F581" s="66" t="n"/>
@@ -9262,6 +9856,7 @@
       <c r="O581" s="69" t="n"/>
       <c r="P581" s="62" t="n"/>
       <c r="Q581" s="62" t="n"/>
+      <c r="R581" s="88" t="n"/>
     </row>
     <row r="582" ht="12.75" customHeight="1" s="70">
       <c r="F582" s="66" t="n"/>
@@ -9272,6 +9867,7 @@
       <c r="O582" s="69" t="n"/>
       <c r="P582" s="62" t="n"/>
       <c r="Q582" s="62" t="n"/>
+      <c r="R582" s="88" t="n"/>
     </row>
     <row r="583" ht="12.75" customHeight="1" s="70">
       <c r="F583" s="66" t="n"/>
@@ -9282,6 +9878,7 @@
       <c r="O583" s="69" t="n"/>
       <c r="P583" s="62" t="n"/>
       <c r="Q583" s="62" t="n"/>
+      <c r="R583" s="88" t="n"/>
     </row>
     <row r="584" ht="12.75" customHeight="1" s="70">
       <c r="F584" s="66" t="n"/>
@@ -9292,6 +9889,7 @@
       <c r="O584" s="69" t="n"/>
       <c r="P584" s="62" t="n"/>
       <c r="Q584" s="62" t="n"/>
+      <c r="R584" s="88" t="n"/>
     </row>
     <row r="585" ht="12.75" customHeight="1" s="70">
       <c r="F585" s="66" t="n"/>
@@ -9302,6 +9900,7 @@
       <c r="O585" s="69" t="n"/>
       <c r="P585" s="62" t="n"/>
       <c r="Q585" s="62" t="n"/>
+      <c r="R585" s="88" t="n"/>
     </row>
     <row r="586" ht="12.75" customHeight="1" s="70">
       <c r="F586" s="66" t="n"/>
@@ -9312,6 +9911,7 @@
       <c r="O586" s="69" t="n"/>
       <c r="P586" s="62" t="n"/>
       <c r="Q586" s="62" t="n"/>
+      <c r="R586" s="88" t="n"/>
     </row>
     <row r="587" ht="12.75" customHeight="1" s="70">
       <c r="F587" s="66" t="n"/>
@@ -9322,6 +9922,7 @@
       <c r="O587" s="69" t="n"/>
       <c r="P587" s="62" t="n"/>
       <c r="Q587" s="62" t="n"/>
+      <c r="R587" s="88" t="n"/>
     </row>
     <row r="588" ht="12.75" customHeight="1" s="70">
       <c r="F588" s="66" t="n"/>
@@ -9332,6 +9933,7 @@
       <c r="O588" s="69" t="n"/>
       <c r="P588" s="62" t="n"/>
       <c r="Q588" s="62" t="n"/>
+      <c r="R588" s="88" t="n"/>
     </row>
     <row r="589" ht="12.75" customHeight="1" s="70">
       <c r="F589" s="66" t="n"/>
@@ -9342,6 +9944,7 @@
       <c r="O589" s="69" t="n"/>
       <c r="P589" s="62" t="n"/>
       <c r="Q589" s="62" t="n"/>
+      <c r="R589" s="88" t="n"/>
     </row>
     <row r="590" ht="12.75" customHeight="1" s="70">
       <c r="F590" s="66" t="n"/>
@@ -9352,6 +9955,7 @@
       <c r="O590" s="69" t="n"/>
       <c r="P590" s="62" t="n"/>
       <c r="Q590" s="62" t="n"/>
+      <c r="R590" s="88" t="n"/>
     </row>
     <row r="591" ht="12.75" customHeight="1" s="70">
       <c r="F591" s="66" t="n"/>
@@ -9362,6 +9966,7 @@
       <c r="O591" s="69" t="n"/>
       <c r="P591" s="62" t="n"/>
       <c r="Q591" s="62" t="n"/>
+      <c r="R591" s="88" t="n"/>
     </row>
     <row r="592" ht="12.75" customHeight="1" s="70">
       <c r="F592" s="66" t="n"/>
@@ -9372,6 +9977,7 @@
       <c r="O592" s="69" t="n"/>
       <c r="P592" s="62" t="n"/>
       <c r="Q592" s="62" t="n"/>
+      <c r="R592" s="88" t="n"/>
     </row>
     <row r="593" ht="12.75" customHeight="1" s="70">
       <c r="F593" s="66" t="n"/>
@@ -9382,6 +9988,7 @@
       <c r="O593" s="69" t="n"/>
       <c r="P593" s="62" t="n"/>
       <c r="Q593" s="62" t="n"/>
+      <c r="R593" s="88" t="n"/>
     </row>
     <row r="594" ht="12.75" customHeight="1" s="70">
       <c r="F594" s="66" t="n"/>
@@ -9392,6 +9999,7 @@
       <c r="O594" s="69" t="n"/>
       <c r="P594" s="62" t="n"/>
       <c r="Q594" s="62" t="n"/>
+      <c r="R594" s="88" t="n"/>
     </row>
     <row r="595" ht="12.75" customHeight="1" s="70">
       <c r="F595" s="66" t="n"/>
@@ -9402,6 +10010,7 @@
       <c r="O595" s="69" t="n"/>
       <c r="P595" s="62" t="n"/>
       <c r="Q595" s="62" t="n"/>
+      <c r="R595" s="88" t="n"/>
     </row>
     <row r="596" ht="12.75" customHeight="1" s="70">
       <c r="F596" s="66" t="n"/>
@@ -9412,6 +10021,7 @@
       <c r="O596" s="69" t="n"/>
       <c r="P596" s="62" t="n"/>
       <c r="Q596" s="62" t="n"/>
+      <c r="R596" s="88" t="n"/>
     </row>
     <row r="597" ht="12.75" customHeight="1" s="70">
       <c r="F597" s="66" t="n"/>
@@ -9422,6 +10032,7 @@
       <c r="O597" s="69" t="n"/>
       <c r="P597" s="62" t="n"/>
       <c r="Q597" s="62" t="n"/>
+      <c r="R597" s="88" t="n"/>
     </row>
     <row r="598" ht="12.75" customHeight="1" s="70">
       <c r="F598" s="66" t="n"/>
@@ -9432,6 +10043,7 @@
       <c r="O598" s="69" t="n"/>
       <c r="P598" s="62" t="n"/>
       <c r="Q598" s="62" t="n"/>
+      <c r="R598" s="88" t="n"/>
     </row>
     <row r="599" ht="12.75" customHeight="1" s="70">
       <c r="F599" s="66" t="n"/>
@@ -9442,6 +10054,7 @@
       <c r="O599" s="69" t="n"/>
       <c r="P599" s="62" t="n"/>
       <c r="Q599" s="62" t="n"/>
+      <c r="R599" s="88" t="n"/>
     </row>
     <row r="600" ht="12.75" customHeight="1" s="70">
       <c r="F600" s="66" t="n"/>
@@ -9452,6 +10065,7 @@
       <c r="O600" s="69" t="n"/>
       <c r="P600" s="62" t="n"/>
       <c r="Q600" s="62" t="n"/>
+      <c r="R600" s="88" t="n"/>
     </row>
     <row r="601" ht="12.75" customHeight="1" s="70">
       <c r="F601" s="66" t="n"/>
@@ -9462,6 +10076,7 @@
       <c r="O601" s="69" t="n"/>
       <c r="P601" s="62" t="n"/>
       <c r="Q601" s="62" t="n"/>
+      <c r="R601" s="88" t="n"/>
     </row>
     <row r="602" ht="12.75" customHeight="1" s="70">
       <c r="F602" s="66" t="n"/>
@@ -9472,6 +10087,7 @@
       <c r="O602" s="69" t="n"/>
       <c r="P602" s="62" t="n"/>
       <c r="Q602" s="62" t="n"/>
+      <c r="R602" s="88" t="n"/>
     </row>
     <row r="603" ht="12.75" customHeight="1" s="70">
       <c r="F603" s="66" t="n"/>
@@ -9482,6 +10098,7 @@
       <c r="O603" s="69" t="n"/>
       <c r="P603" s="62" t="n"/>
       <c r="Q603" s="62" t="n"/>
+      <c r="R603" s="88" t="n"/>
     </row>
     <row r="604" ht="12.75" customHeight="1" s="70">
       <c r="F604" s="66" t="n"/>
@@ -9492,6 +10109,7 @@
       <c r="O604" s="69" t="n"/>
       <c r="P604" s="62" t="n"/>
       <c r="Q604" s="62" t="n"/>
+      <c r="R604" s="88" t="n"/>
     </row>
     <row r="605" ht="12.75" customHeight="1" s="70">
       <c r="F605" s="66" t="n"/>
@@ -9502,6 +10120,7 @@
       <c r="O605" s="69" t="n"/>
       <c r="P605" s="62" t="n"/>
       <c r="Q605" s="62" t="n"/>
+      <c r="R605" s="88" t="n"/>
     </row>
     <row r="606" ht="12.75" customHeight="1" s="70">
       <c r="F606" s="66" t="n"/>
@@ -9512,6 +10131,7 @@
       <c r="O606" s="69" t="n"/>
       <c r="P606" s="62" t="n"/>
       <c r="Q606" s="62" t="n"/>
+      <c r="R606" s="88" t="n"/>
     </row>
     <row r="607" ht="12.75" customHeight="1" s="70">
       <c r="F607" s="66" t="n"/>
@@ -9522,6 +10142,7 @@
       <c r="O607" s="69" t="n"/>
       <c r="P607" s="62" t="n"/>
       <c r="Q607" s="62" t="n"/>
+      <c r="R607" s="88" t="n"/>
     </row>
     <row r="608" ht="12.75" customHeight="1" s="70">
       <c r="F608" s="66" t="n"/>
@@ -9532,6 +10153,7 @@
       <c r="O608" s="69" t="n"/>
       <c r="P608" s="62" t="n"/>
       <c r="Q608" s="62" t="n"/>
+      <c r="R608" s="88" t="n"/>
     </row>
     <row r="609" ht="12.75" customHeight="1" s="70">
       <c r="F609" s="66" t="n"/>
@@ -9542,6 +10164,7 @@
       <c r="O609" s="69" t="n"/>
       <c r="P609" s="62" t="n"/>
       <c r="Q609" s="62" t="n"/>
+      <c r="R609" s="88" t="n"/>
     </row>
     <row r="610" ht="12.75" customHeight="1" s="70">
       <c r="F610" s="66" t="n"/>
@@ -9552,6 +10175,7 @@
       <c r="O610" s="69" t="n"/>
       <c r="P610" s="62" t="n"/>
       <c r="Q610" s="62" t="n"/>
+      <c r="R610" s="88" t="n"/>
     </row>
     <row r="611" ht="12.75" customHeight="1" s="70">
       <c r="F611" s="66" t="n"/>
@@ -9562,6 +10186,7 @@
       <c r="O611" s="69" t="n"/>
       <c r="P611" s="62" t="n"/>
       <c r="Q611" s="62" t="n"/>
+      <c r="R611" s="88" t="n"/>
     </row>
     <row r="612" ht="12.75" customHeight="1" s="70">
       <c r="F612" s="66" t="n"/>
@@ -9572,6 +10197,7 @@
       <c r="O612" s="69" t="n"/>
       <c r="P612" s="62" t="n"/>
       <c r="Q612" s="62" t="n"/>
+      <c r="R612" s="88" t="n"/>
     </row>
     <row r="613" ht="12.75" customHeight="1" s="70">
       <c r="F613" s="66" t="n"/>
@@ -9582,6 +10208,7 @@
       <c r="O613" s="69" t="n"/>
       <c r="P613" s="62" t="n"/>
       <c r="Q613" s="62" t="n"/>
+      <c r="R613" s="88" t="n"/>
     </row>
     <row r="614" ht="12.75" customHeight="1" s="70">
       <c r="F614" s="66" t="n"/>
@@ -9592,6 +10219,7 @@
       <c r="O614" s="69" t="n"/>
       <c r="P614" s="62" t="n"/>
       <c r="Q614" s="62" t="n"/>
+      <c r="R614" s="88" t="n"/>
     </row>
     <row r="615" ht="12.75" customHeight="1" s="70">
       <c r="F615" s="66" t="n"/>
@@ -9602,6 +10230,7 @@
       <c r="O615" s="69" t="n"/>
       <c r="P615" s="62" t="n"/>
       <c r="Q615" s="62" t="n"/>
+      <c r="R615" s="88" t="n"/>
     </row>
     <row r="616" ht="12.75" customHeight="1" s="70">
       <c r="F616" s="66" t="n"/>
@@ -9612,6 +10241,7 @@
       <c r="O616" s="69" t="n"/>
       <c r="P616" s="62" t="n"/>
       <c r="Q616" s="62" t="n"/>
+      <c r="R616" s="88" t="n"/>
     </row>
     <row r="617" ht="12.75" customHeight="1" s="70">
       <c r="F617" s="66" t="n"/>
@@ -9622,6 +10252,7 @@
       <c r="O617" s="69" t="n"/>
       <c r="P617" s="62" t="n"/>
       <c r="Q617" s="62" t="n"/>
+      <c r="R617" s="88" t="n"/>
     </row>
     <row r="618" ht="12.75" customHeight="1" s="70">
       <c r="F618" s="66" t="n"/>
@@ -9632,6 +10263,7 @@
       <c r="O618" s="69" t="n"/>
       <c r="P618" s="62" t="n"/>
       <c r="Q618" s="62" t="n"/>
+      <c r="R618" s="88" t="n"/>
     </row>
     <row r="619" ht="12.75" customHeight="1" s="70">
       <c r="F619" s="66" t="n"/>
@@ -9642,6 +10274,7 @@
       <c r="O619" s="69" t="n"/>
       <c r="P619" s="62" t="n"/>
       <c r="Q619" s="62" t="n"/>
+      <c r="R619" s="88" t="n"/>
     </row>
     <row r="620" ht="12.75" customHeight="1" s="70">
       <c r="F620" s="66" t="n"/>
@@ -9652,6 +10285,7 @@
       <c r="O620" s="69" t="n"/>
       <c r="P620" s="62" t="n"/>
       <c r="Q620" s="62" t="n"/>
+      <c r="R620" s="88" t="n"/>
     </row>
     <row r="621" ht="12.75" customHeight="1" s="70">
       <c r="F621" s="66" t="n"/>
@@ -9662,6 +10296,7 @@
       <c r="O621" s="69" t="n"/>
       <c r="P621" s="62" t="n"/>
       <c r="Q621" s="62" t="n"/>
+      <c r="R621" s="88" t="n"/>
     </row>
     <row r="622" ht="12.75" customHeight="1" s="70">
       <c r="F622" s="66" t="n"/>
@@ -9672,6 +10307,7 @@
       <c r="O622" s="69" t="n"/>
       <c r="P622" s="62" t="n"/>
       <c r="Q622" s="62" t="n"/>
+      <c r="R622" s="88" t="n"/>
     </row>
     <row r="623" ht="12.75" customHeight="1" s="70">
       <c r="F623" s="66" t="n"/>
@@ -9682,6 +10318,7 @@
       <c r="O623" s="69" t="n"/>
       <c r="P623" s="62" t="n"/>
       <c r="Q623" s="62" t="n"/>
+      <c r="R623" s="88" t="n"/>
     </row>
     <row r="624" ht="12.75" customHeight="1" s="70">
       <c r="F624" s="66" t="n"/>
@@ -9692,6 +10329,7 @@
       <c r="O624" s="69" t="n"/>
       <c r="P624" s="62" t="n"/>
       <c r="Q624" s="62" t="n"/>
+      <c r="R624" s="88" t="n"/>
     </row>
     <row r="625" ht="12.75" customHeight="1" s="70">
       <c r="F625" s="66" t="n"/>
@@ -9702,6 +10340,7 @@
       <c r="O625" s="69" t="n"/>
       <c r="P625" s="62" t="n"/>
       <c r="Q625" s="62" t="n"/>
+      <c r="R625" s="88" t="n"/>
     </row>
     <row r="626" ht="12.75" customHeight="1" s="70">
       <c r="F626" s="66" t="n"/>
@@ -9712,6 +10351,7 @@
       <c r="O626" s="69" t="n"/>
       <c r="P626" s="62" t="n"/>
       <c r="Q626" s="62" t="n"/>
+      <c r="R626" s="88" t="n"/>
     </row>
     <row r="627" ht="12.75" customHeight="1" s="70">
       <c r="F627" s="66" t="n"/>
@@ -9722,6 +10362,7 @@
       <c r="O627" s="69" t="n"/>
       <c r="P627" s="62" t="n"/>
       <c r="Q627" s="62" t="n"/>
+      <c r="R627" s="88" t="n"/>
     </row>
     <row r="628" ht="12.75" customHeight="1" s="70">
       <c r="F628" s="66" t="n"/>
@@ -9732,6 +10373,7 @@
       <c r="O628" s="69" t="n"/>
       <c r="P628" s="62" t="n"/>
       <c r="Q628" s="62" t="n"/>
+      <c r="R628" s="88" t="n"/>
     </row>
     <row r="629" ht="12.75" customHeight="1" s="70">
       <c r="F629" s="66" t="n"/>
@@ -9742,6 +10384,7 @@
       <c r="O629" s="69" t="n"/>
       <c r="P629" s="62" t="n"/>
       <c r="Q629" s="62" t="n"/>
+      <c r="R629" s="88" t="n"/>
     </row>
     <row r="630" ht="12.75" customHeight="1" s="70">
       <c r="F630" s="66" t="n"/>
@@ -9752,6 +10395,7 @@
       <c r="O630" s="69" t="n"/>
       <c r="P630" s="62" t="n"/>
       <c r="Q630" s="62" t="n"/>
+      <c r="R630" s="88" t="n"/>
     </row>
     <row r="631" ht="12.75" customHeight="1" s="70">
       <c r="F631" s="66" t="n"/>
@@ -9762,6 +10406,7 @@
       <c r="O631" s="69" t="n"/>
       <c r="P631" s="62" t="n"/>
       <c r="Q631" s="62" t="n"/>
+      <c r="R631" s="88" t="n"/>
     </row>
     <row r="632" ht="12.75" customHeight="1" s="70">
       <c r="F632" s="66" t="n"/>
@@ -9772,6 +10417,7 @@
       <c r="O632" s="69" t="n"/>
       <c r="P632" s="62" t="n"/>
       <c r="Q632" s="62" t="n"/>
+      <c r="R632" s="88" t="n"/>
     </row>
     <row r="633" ht="12.75" customHeight="1" s="70">
       <c r="F633" s="66" t="n"/>
@@ -9782,6 +10428,7 @@
       <c r="O633" s="69" t="n"/>
       <c r="P633" s="62" t="n"/>
       <c r="Q633" s="62" t="n"/>
+      <c r="R633" s="88" t="n"/>
     </row>
     <row r="634" ht="12.75" customHeight="1" s="70">
       <c r="F634" s="66" t="n"/>
@@ -9792,6 +10439,7 @@
       <c r="O634" s="69" t="n"/>
       <c r="P634" s="62" t="n"/>
       <c r="Q634" s="62" t="n"/>
+      <c r="R634" s="88" t="n"/>
     </row>
     <row r="635" ht="12.75" customHeight="1" s="70">
       <c r="F635" s="66" t="n"/>
@@ -9802,6 +10450,7 @@
       <c r="O635" s="69" t="n"/>
       <c r="P635" s="62" t="n"/>
       <c r="Q635" s="62" t="n"/>
+      <c r="R635" s="88" t="n"/>
     </row>
     <row r="636" ht="12.75" customHeight="1" s="70">
       <c r="F636" s="66" t="n"/>
@@ -9812,6 +10461,7 @@
       <c r="O636" s="69" t="n"/>
       <c r="P636" s="62" t="n"/>
       <c r="Q636" s="62" t="n"/>
+      <c r="R636" s="88" t="n"/>
     </row>
     <row r="637" ht="12.75" customHeight="1" s="70">
       <c r="F637" s="66" t="n"/>
@@ -9822,6 +10472,7 @@
       <c r="O637" s="69" t="n"/>
       <c r="P637" s="62" t="n"/>
       <c r="Q637" s="62" t="n"/>
+      <c r="R637" s="88" t="n"/>
     </row>
     <row r="638" ht="12.75" customHeight="1" s="70">
       <c r="F638" s="66" t="n"/>
@@ -9832,6 +10483,7 @@
       <c r="O638" s="69" t="n"/>
       <c r="P638" s="62" t="n"/>
       <c r="Q638" s="62" t="n"/>
+      <c r="R638" s="88" t="n"/>
     </row>
     <row r="639" ht="12.75" customHeight="1" s="70">
       <c r="F639" s="66" t="n"/>
@@ -9842,6 +10494,7 @@
       <c r="O639" s="69" t="n"/>
       <c r="P639" s="62" t="n"/>
       <c r="Q639" s="62" t="n"/>
+      <c r="R639" s="88" t="n"/>
     </row>
     <row r="640" ht="12.75" customHeight="1" s="70">
       <c r="F640" s="66" t="n"/>
@@ -9852,6 +10505,7 @@
       <c r="O640" s="69" t="n"/>
       <c r="P640" s="62" t="n"/>
       <c r="Q640" s="62" t="n"/>
+      <c r="R640" s="88" t="n"/>
     </row>
     <row r="641" ht="12.75" customHeight="1" s="70">
       <c r="F641" s="66" t="n"/>
@@ -9862,6 +10516,7 @@
       <c r="O641" s="69" t="n"/>
       <c r="P641" s="62" t="n"/>
       <c r="Q641" s="62" t="n"/>
+      <c r="R641" s="88" t="n"/>
     </row>
     <row r="642" ht="12.75" customHeight="1" s="70">
       <c r="F642" s="66" t="n"/>
@@ -9872,6 +10527,7 @@
       <c r="O642" s="69" t="n"/>
       <c r="P642" s="62" t="n"/>
       <c r="Q642" s="62" t="n"/>
+      <c r="R642" s="88" t="n"/>
     </row>
     <row r="643" ht="12.75" customHeight="1" s="70">
       <c r="F643" s="66" t="n"/>
@@ -9882,6 +10538,7 @@
       <c r="O643" s="69" t="n"/>
       <c r="P643" s="62" t="n"/>
       <c r="Q643" s="62" t="n"/>
+      <c r="R643" s="88" t="n"/>
     </row>
     <row r="644" ht="12.75" customHeight="1" s="70">
       <c r="F644" s="66" t="n"/>
@@ -9892,6 +10549,7 @@
       <c r="O644" s="69" t="n"/>
       <c r="P644" s="62" t="n"/>
       <c r="Q644" s="62" t="n"/>
+      <c r="R644" s="88" t="n"/>
     </row>
     <row r="645" ht="12.75" customHeight="1" s="70">
       <c r="F645" s="66" t="n"/>
@@ -9902,6 +10560,7 @@
       <c r="O645" s="69" t="n"/>
       <c r="P645" s="62" t="n"/>
       <c r="Q645" s="62" t="n"/>
+      <c r="R645" s="88" t="n"/>
     </row>
     <row r="646" ht="12.75" customHeight="1" s="70">
       <c r="F646" s="66" t="n"/>
@@ -9912,6 +10571,7 @@
       <c r="O646" s="69" t="n"/>
       <c r="P646" s="62" t="n"/>
       <c r="Q646" s="62" t="n"/>
+      <c r="R646" s="88" t="n"/>
     </row>
     <row r="647" ht="12.75" customHeight="1" s="70">
       <c r="F647" s="66" t="n"/>
@@ -9922,6 +10582,7 @@
       <c r="O647" s="69" t="n"/>
       <c r="P647" s="62" t="n"/>
       <c r="Q647" s="62" t="n"/>
+      <c r="R647" s="88" t="n"/>
     </row>
     <row r="648" ht="12.75" customHeight="1" s="70">
       <c r="F648" s="66" t="n"/>
@@ -9932,6 +10593,7 @@
       <c r="O648" s="69" t="n"/>
       <c r="P648" s="62" t="n"/>
       <c r="Q648" s="62" t="n"/>
+      <c r="R648" s="88" t="n"/>
     </row>
     <row r="649" ht="12.75" customHeight="1" s="70">
       <c r="F649" s="66" t="n"/>
@@ -9942,6 +10604,7 @@
       <c r="O649" s="69" t="n"/>
       <c r="P649" s="62" t="n"/>
       <c r="Q649" s="62" t="n"/>
+      <c r="R649" s="88" t="n"/>
     </row>
     <row r="650" ht="12.75" customHeight="1" s="70">
       <c r="F650" s="66" t="n"/>
@@ -9952,6 +10615,7 @@
       <c r="O650" s="69" t="n"/>
       <c r="P650" s="62" t="n"/>
       <c r="Q650" s="62" t="n"/>
+      <c r="R650" s="88" t="n"/>
     </row>
     <row r="651" ht="12.75" customHeight="1" s="70">
       <c r="F651" s="66" t="n"/>
@@ -9962,6 +10626,7 @@
       <c r="O651" s="69" t="n"/>
       <c r="P651" s="62" t="n"/>
       <c r="Q651" s="62" t="n"/>
+      <c r="R651" s="88" t="n"/>
     </row>
     <row r="652" ht="12.75" customHeight="1" s="70">
       <c r="F652" s="66" t="n"/>
@@ -9972,6 +10637,7 @@
       <c r="O652" s="69" t="n"/>
       <c r="P652" s="62" t="n"/>
       <c r="Q652" s="62" t="n"/>
+      <c r="R652" s="88" t="n"/>
     </row>
     <row r="653" ht="12.75" customHeight="1" s="70">
       <c r="F653" s="66" t="n"/>
@@ -9982,6 +10648,7 @@
       <c r="O653" s="69" t="n"/>
       <c r="P653" s="62" t="n"/>
       <c r="Q653" s="62" t="n"/>
+      <c r="R653" s="88" t="n"/>
     </row>
     <row r="654" ht="12.75" customHeight="1" s="70">
       <c r="F654" s="66" t="n"/>
@@ -9992,6 +10659,7 @@
       <c r="O654" s="69" t="n"/>
       <c r="P654" s="62" t="n"/>
       <c r="Q654" s="62" t="n"/>
+      <c r="R654" s="88" t="n"/>
     </row>
     <row r="655" ht="12.75" customHeight="1" s="70">
       <c r="F655" s="66" t="n"/>
@@ -10002,6 +10670,7 @@
       <c r="O655" s="69" t="n"/>
       <c r="P655" s="62" t="n"/>
       <c r="Q655" s="62" t="n"/>
+      <c r="R655" s="88" t="n"/>
     </row>
     <row r="656" ht="12.75" customHeight="1" s="70">
       <c r="F656" s="66" t="n"/>
@@ -10012,6 +10681,7 @@
       <c r="O656" s="69" t="n"/>
       <c r="P656" s="62" t="n"/>
       <c r="Q656" s="62" t="n"/>
+      <c r="R656" s="88" t="n"/>
     </row>
     <row r="657" ht="12.75" customHeight="1" s="70">
       <c r="F657" s="66" t="n"/>
@@ -10022,6 +10692,7 @@
       <c r="O657" s="69" t="n"/>
       <c r="P657" s="62" t="n"/>
       <c r="Q657" s="62" t="n"/>
+      <c r="R657" s="88" t="n"/>
     </row>
     <row r="658" ht="12.75" customHeight="1" s="70">
       <c r="F658" s="66" t="n"/>
@@ -10032,6 +10703,7 @@
       <c r="O658" s="69" t="n"/>
       <c r="P658" s="62" t="n"/>
       <c r="Q658" s="62" t="n"/>
+      <c r="R658" s="88" t="n"/>
     </row>
     <row r="659" ht="12.75" customHeight="1" s="70">
       <c r="F659" s="66" t="n"/>
@@ -10042,6 +10714,7 @@
       <c r="O659" s="69" t="n"/>
       <c r="P659" s="62" t="n"/>
       <c r="Q659" s="62" t="n"/>
+      <c r="R659" s="88" t="n"/>
     </row>
     <row r="660" ht="12.75" customHeight="1" s="70">
       <c r="F660" s="66" t="n"/>
@@ -10052,6 +10725,7 @@
       <c r="O660" s="69" t="n"/>
       <c r="P660" s="62" t="n"/>
       <c r="Q660" s="62" t="n"/>
+      <c r="R660" s="88" t="n"/>
     </row>
     <row r="661" ht="12.75" customHeight="1" s="70">
       <c r="F661" s="66" t="n"/>
@@ -10062,6 +10736,7 @@
       <c r="O661" s="69" t="n"/>
       <c r="P661" s="62" t="n"/>
       <c r="Q661" s="62" t="n"/>
+      <c r="R661" s="88" t="n"/>
     </row>
     <row r="662" ht="12.75" customHeight="1" s="70">
       <c r="F662" s="66" t="n"/>
@@ -10072,6 +10747,7 @@
       <c r="O662" s="69" t="n"/>
       <c r="P662" s="62" t="n"/>
       <c r="Q662" s="62" t="n"/>
+      <c r="R662" s="88" t="n"/>
     </row>
     <row r="663" ht="12.75" customHeight="1" s="70">
       <c r="F663" s="66" t="n"/>
@@ -10082,6 +10758,7 @@
       <c r="O663" s="69" t="n"/>
       <c r="P663" s="62" t="n"/>
       <c r="Q663" s="62" t="n"/>
+      <c r="R663" s="88" t="n"/>
     </row>
     <row r="664" ht="12.75" customHeight="1" s="70">
       <c r="F664" s="66" t="n"/>
@@ -10092,6 +10769,7 @@
       <c r="O664" s="69" t="n"/>
       <c r="P664" s="62" t="n"/>
       <c r="Q664" s="62" t="n"/>
+      <c r="R664" s="88" t="n"/>
     </row>
     <row r="665" ht="12.75" customHeight="1" s="70">
       <c r="F665" s="66" t="n"/>
@@ -10102,6 +10780,7 @@
       <c r="O665" s="69" t="n"/>
       <c r="P665" s="62" t="n"/>
       <c r="Q665" s="62" t="n"/>
+      <c r="R665" s="88" t="n"/>
     </row>
     <row r="666" ht="12.75" customHeight="1" s="70">
       <c r="F666" s="66" t="n"/>
@@ -10112,6 +10791,7 @@
       <c r="O666" s="69" t="n"/>
       <c r="P666" s="62" t="n"/>
       <c r="Q666" s="62" t="n"/>
+      <c r="R666" s="88" t="n"/>
     </row>
     <row r="667" ht="12.75" customHeight="1" s="70">
       <c r="F667" s="66" t="n"/>
@@ -10122,6 +10802,7 @@
       <c r="O667" s="69" t="n"/>
       <c r="P667" s="62" t="n"/>
       <c r="Q667" s="62" t="n"/>
+      <c r="R667" s="88" t="n"/>
     </row>
     <row r="668" ht="12.75" customHeight="1" s="70">
       <c r="F668" s="66" t="n"/>
@@ -10132,6 +10813,7 @@
       <c r="O668" s="69" t="n"/>
       <c r="P668" s="62" t="n"/>
       <c r="Q668" s="62" t="n"/>
+      <c r="R668" s="88" t="n"/>
     </row>
     <row r="669" ht="12.75" customHeight="1" s="70">
       <c r="F669" s="66" t="n"/>
@@ -10142,6 +10824,7 @@
       <c r="O669" s="69" t="n"/>
       <c r="P669" s="62" t="n"/>
       <c r="Q669" s="62" t="n"/>
+      <c r="R669" s="88" t="n"/>
     </row>
     <row r="670" ht="12.75" customHeight="1" s="70">
       <c r="F670" s="66" t="n"/>
@@ -10152,6 +10835,7 @@
       <c r="O670" s="69" t="n"/>
       <c r="P670" s="62" t="n"/>
       <c r="Q670" s="62" t="n"/>
+      <c r="R670" s="88" t="n"/>
     </row>
     <row r="671" ht="12.75" customHeight="1" s="70">
       <c r="F671" s="66" t="n"/>
@@ -10162,6 +10846,7 @@
       <c r="O671" s="69" t="n"/>
       <c r="P671" s="62" t="n"/>
       <c r="Q671" s="62" t="n"/>
+      <c r="R671" s="88" t="n"/>
     </row>
     <row r="672" ht="12.75" customHeight="1" s="70">
       <c r="F672" s="66" t="n"/>
@@ -10172,6 +10857,7 @@
       <c r="O672" s="69" t="n"/>
       <c r="P672" s="62" t="n"/>
       <c r="Q672" s="62" t="n"/>
+      <c r="R672" s="88" t="n"/>
     </row>
     <row r="673" ht="12.75" customHeight="1" s="70">
       <c r="F673" s="66" t="n"/>
@@ -10182,6 +10868,7 @@
       <c r="O673" s="69" t="n"/>
       <c r="P673" s="62" t="n"/>
       <c r="Q673" s="62" t="n"/>
+      <c r="R673" s="88" t="n"/>
     </row>
     <row r="674" ht="12.75" customHeight="1" s="70">
       <c r="F674" s="66" t="n"/>
@@ -10192,6 +10879,7 @@
       <c r="O674" s="69" t="n"/>
       <c r="P674" s="62" t="n"/>
       <c r="Q674" s="62" t="n"/>
+      <c r="R674" s="88" t="n"/>
     </row>
     <row r="675" ht="12.75" customHeight="1" s="70">
       <c r="F675" s="66" t="n"/>
@@ -10202,6 +10890,7 @@
       <c r="O675" s="69" t="n"/>
       <c r="P675" s="62" t="n"/>
       <c r="Q675" s="62" t="n"/>
+      <c r="R675" s="88" t="n"/>
     </row>
     <row r="676" ht="12.75" customHeight="1" s="70">
       <c r="F676" s="66" t="n"/>
@@ -10212,6 +10901,7 @@
       <c r="O676" s="69" t="n"/>
       <c r="P676" s="62" t="n"/>
       <c r="Q676" s="62" t="n"/>
+      <c r="R676" s="88" t="n"/>
     </row>
     <row r="677" ht="12.75" customHeight="1" s="70">
       <c r="F677" s="66" t="n"/>
@@ -10222,6 +10912,7 @@
       <c r="O677" s="69" t="n"/>
       <c r="P677" s="62" t="n"/>
       <c r="Q677" s="62" t="n"/>
+      <c r="R677" s="88" t="n"/>
     </row>
     <row r="678" ht="12.75" customHeight="1" s="70">
       <c r="F678" s="66" t="n"/>
@@ -10232,6 +10923,7 @@
       <c r="O678" s="69" t="n"/>
       <c r="P678" s="62" t="n"/>
       <c r="Q678" s="62" t="n"/>
+      <c r="R678" s="88" t="n"/>
     </row>
     <row r="679" ht="12.75" customHeight="1" s="70">
       <c r="F679" s="66" t="n"/>
@@ -10242,6 +10934,7 @@
       <c r="O679" s="69" t="n"/>
       <c r="P679" s="62" t="n"/>
       <c r="Q679" s="62" t="n"/>
+      <c r="R679" s="88" t="n"/>
     </row>
     <row r="680" ht="12.75" customHeight="1" s="70">
       <c r="F680" s="66" t="n"/>
@@ -10252,6 +10945,7 @@
       <c r="O680" s="69" t="n"/>
       <c r="P680" s="62" t="n"/>
       <c r="Q680" s="62" t="n"/>
+      <c r="R680" s="88" t="n"/>
     </row>
     <row r="681" ht="12.75" customHeight="1" s="70">
       <c r="F681" s="66" t="n"/>
@@ -10262,6 +10956,7 @@
       <c r="O681" s="69" t="n"/>
       <c r="P681" s="62" t="n"/>
       <c r="Q681" s="62" t="n"/>
+      <c r="R681" s="88" t="n"/>
     </row>
     <row r="682" ht="12.75" customHeight="1" s="70">
       <c r="F682" s="66" t="n"/>
@@ -10272,6 +10967,7 @@
       <c r="O682" s="69" t="n"/>
       <c r="P682" s="62" t="n"/>
       <c r="Q682" s="62" t="n"/>
+      <c r="R682" s="88" t="n"/>
     </row>
     <row r="683" ht="12.75" customHeight="1" s="70">
       <c r="F683" s="66" t="n"/>
@@ -10282,6 +10978,7 @@
       <c r="O683" s="69" t="n"/>
       <c r="P683" s="62" t="n"/>
       <c r="Q683" s="62" t="n"/>
+      <c r="R683" s="88" t="n"/>
     </row>
     <row r="684" ht="12.75" customHeight="1" s="70">
       <c r="F684" s="66" t="n"/>
@@ -10292,6 +10989,7 @@
       <c r="O684" s="69" t="n"/>
       <c r="P684" s="62" t="n"/>
       <c r="Q684" s="62" t="n"/>
+      <c r="R684" s="88" t="n"/>
     </row>
     <row r="685" ht="12.75" customHeight="1" s="70">
       <c r="F685" s="66" t="n"/>
@@ -10302,6 +11000,7 @@
       <c r="O685" s="69" t="n"/>
       <c r="P685" s="62" t="n"/>
       <c r="Q685" s="62" t="n"/>
+      <c r="R685" s="88" t="n"/>
     </row>
     <row r="686" ht="12.75" customHeight="1" s="70">
       <c r="F686" s="66" t="n"/>
@@ -10312,6 +11011,7 @@
       <c r="O686" s="69" t="n"/>
       <c r="P686" s="62" t="n"/>
       <c r="Q686" s="62" t="n"/>
+      <c r="R686" s="88" t="n"/>
     </row>
     <row r="687" ht="12.75" customHeight="1" s="70">
       <c r="F687" s="66" t="n"/>
@@ -10322,6 +11022,7 @@
       <c r="O687" s="69" t="n"/>
       <c r="P687" s="62" t="n"/>
       <c r="Q687" s="62" t="n"/>
+      <c r="R687" s="88" t="n"/>
     </row>
     <row r="688" ht="12.75" customHeight="1" s="70">
       <c r="F688" s="66" t="n"/>
@@ -10332,6 +11033,7 @@
       <c r="O688" s="69" t="n"/>
       <c r="P688" s="62" t="n"/>
       <c r="Q688" s="62" t="n"/>
+      <c r="R688" s="88" t="n"/>
     </row>
     <row r="689" ht="12.75" customHeight="1" s="70">
       <c r="F689" s="66" t="n"/>
@@ -10342,6 +11044,7 @@
       <c r="O689" s="69" t="n"/>
       <c r="P689" s="62" t="n"/>
       <c r="Q689" s="62" t="n"/>
+      <c r="R689" s="88" t="n"/>
     </row>
     <row r="690" ht="12.75" customHeight="1" s="70">
       <c r="F690" s="66" t="n"/>
@@ -10352,6 +11055,7 @@
       <c r="O690" s="69" t="n"/>
       <c r="P690" s="62" t="n"/>
       <c r="Q690" s="62" t="n"/>
+      <c r="R690" s="88" t="n"/>
     </row>
     <row r="691" ht="12.75" customHeight="1" s="70">
       <c r="F691" s="66" t="n"/>
@@ -10362,6 +11066,7 @@
       <c r="O691" s="69" t="n"/>
       <c r="P691" s="62" t="n"/>
       <c r="Q691" s="62" t="n"/>
+      <c r="R691" s="88" t="n"/>
     </row>
     <row r="692" ht="12.75" customHeight="1" s="70">
       <c r="F692" s="66" t="n"/>
@@ -10372,6 +11077,7 @@
       <c r="O692" s="69" t="n"/>
       <c r="P692" s="62" t="n"/>
       <c r="Q692" s="62" t="n"/>
+      <c r="R692" s="88" t="n"/>
     </row>
     <row r="693" ht="12.75" customHeight="1" s="70">
       <c r="F693" s="66" t="n"/>
@@ -10382,6 +11088,7 @@
       <c r="O693" s="69" t="n"/>
       <c r="P693" s="62" t="n"/>
       <c r="Q693" s="62" t="n"/>
+      <c r="R693" s="88" t="n"/>
     </row>
     <row r="694" ht="12.75" customHeight="1" s="70">
       <c r="F694" s="66" t="n"/>
@@ -10392,6 +11099,7 @@
       <c r="O694" s="69" t="n"/>
       <c r="P694" s="62" t="n"/>
       <c r="Q694" s="62" t="n"/>
+      <c r="R694" s="88" t="n"/>
     </row>
     <row r="695" ht="12.75" customHeight="1" s="70">
       <c r="F695" s="66" t="n"/>
@@ -10402,6 +11110,7 @@
       <c r="O695" s="69" t="n"/>
       <c r="P695" s="62" t="n"/>
       <c r="Q695" s="62" t="n"/>
+      <c r="R695" s="88" t="n"/>
     </row>
     <row r="696" ht="12.75" customHeight="1" s="70">
       <c r="F696" s="66" t="n"/>
@@ -10412,6 +11121,7 @@
       <c r="O696" s="69" t="n"/>
       <c r="P696" s="62" t="n"/>
       <c r="Q696" s="62" t="n"/>
+      <c r="R696" s="88" t="n"/>
     </row>
     <row r="697" ht="12.75" customHeight="1" s="70">
       <c r="F697" s="66" t="n"/>
@@ -10422,6 +11132,7 @@
       <c r="O697" s="69" t="n"/>
       <c r="P697" s="62" t="n"/>
       <c r="Q697" s="62" t="n"/>
+      <c r="R697" s="88" t="n"/>
     </row>
     <row r="698" ht="12.75" customHeight="1" s="70">
       <c r="F698" s="66" t="n"/>
@@ -10432,6 +11143,7 @@
       <c r="O698" s="69" t="n"/>
       <c r="P698" s="62" t="n"/>
       <c r="Q698" s="62" t="n"/>
+      <c r="R698" s="88" t="n"/>
     </row>
     <row r="699" ht="12.75" customHeight="1" s="70">
       <c r="F699" s="66" t="n"/>
@@ -10442,6 +11154,7 @@
       <c r="O699" s="69" t="n"/>
       <c r="P699" s="62" t="n"/>
       <c r="Q699" s="62" t="n"/>
+      <c r="R699" s="88" t="n"/>
     </row>
     <row r="700" ht="12.75" customHeight="1" s="70">
       <c r="F700" s="66" t="n"/>
@@ -10452,6 +11165,7 @@
       <c r="O700" s="69" t="n"/>
       <c r="P700" s="62" t="n"/>
       <c r="Q700" s="62" t="n"/>
+      <c r="R700" s="88" t="n"/>
     </row>
     <row r="701" ht="12.75" customHeight="1" s="70">
       <c r="F701" s="66" t="n"/>
@@ -10462,6 +11176,7 @@
       <c r="O701" s="69" t="n"/>
       <c r="P701" s="62" t="n"/>
       <c r="Q701" s="62" t="n"/>
+      <c r="R701" s="88" t="n"/>
     </row>
     <row r="702" ht="12.75" customHeight="1" s="70">
       <c r="F702" s="66" t="n"/>
@@ -10472,6 +11187,7 @@
       <c r="O702" s="69" t="n"/>
       <c r="P702" s="62" t="n"/>
       <c r="Q702" s="62" t="n"/>
+      <c r="R702" s="88" t="n"/>
     </row>
     <row r="703" ht="12.75" customHeight="1" s="70">
       <c r="F703" s="66" t="n"/>
@@ -10482,6 +11198,7 @@
       <c r="O703" s="69" t="n"/>
       <c r="P703" s="62" t="n"/>
       <c r="Q703" s="62" t="n"/>
+      <c r="R703" s="88" t="n"/>
     </row>
     <row r="704" ht="12.75" customHeight="1" s="70">
       <c r="F704" s="66" t="n"/>
@@ -10492,6 +11209,7 @@
       <c r="O704" s="69" t="n"/>
       <c r="P704" s="62" t="n"/>
       <c r="Q704" s="62" t="n"/>
+      <c r="R704" s="88" t="n"/>
     </row>
     <row r="705" ht="12.75" customHeight="1" s="70">
       <c r="F705" s="66" t="n"/>
@@ -10502,6 +11220,7 @@
       <c r="O705" s="69" t="n"/>
       <c r="P705" s="62" t="n"/>
       <c r="Q705" s="62" t="n"/>
+      <c r="R705" s="88" t="n"/>
     </row>
     <row r="706" ht="12.75" customHeight="1" s="70">
       <c r="F706" s="66" t="n"/>
@@ -10512,6 +11231,7 @@
       <c r="O706" s="69" t="n"/>
       <c r="P706" s="62" t="n"/>
       <c r="Q706" s="62" t="n"/>
+      <c r="R706" s="88" t="n"/>
     </row>
     <row r="707" ht="12.75" customHeight="1" s="70">
       <c r="F707" s="66" t="n"/>
@@ -10522,6 +11242,7 @@
       <c r="O707" s="69" t="n"/>
       <c r="P707" s="62" t="n"/>
       <c r="Q707" s="62" t="n"/>
+      <c r="R707" s="88" t="n"/>
     </row>
     <row r="708" ht="12.75" customHeight="1" s="70">
       <c r="F708" s="66" t="n"/>
@@ -10532,6 +11253,7 @@
       <c r="O708" s="69" t="n"/>
       <c r="P708" s="62" t="n"/>
       <c r="Q708" s="62" t="n"/>
+      <c r="R708" s="88" t="n"/>
     </row>
     <row r="709" ht="12.75" customHeight="1" s="70">
       <c r="F709" s="66" t="n"/>
@@ -10542,6 +11264,7 @@
       <c r="O709" s="69" t="n"/>
       <c r="P709" s="62" t="n"/>
       <c r="Q709" s="62" t="n"/>
+      <c r="R709" s="88" t="n"/>
     </row>
     <row r="710" ht="12.75" customHeight="1" s="70">
       <c r="F710" s="66" t="n"/>
@@ -10552,6 +11275,7 @@
       <c r="O710" s="69" t="n"/>
       <c r="P710" s="62" t="n"/>
       <c r="Q710" s="62" t="n"/>
+      <c r="R710" s="88" t="n"/>
     </row>
     <row r="711" ht="12.75" customHeight="1" s="70">
       <c r="F711" s="66" t="n"/>
@@ -10562,6 +11286,7 @@
       <c r="O711" s="69" t="n"/>
       <c r="P711" s="62" t="n"/>
       <c r="Q711" s="62" t="n"/>
+      <c r="R711" s="88" t="n"/>
     </row>
     <row r="712" ht="12.75" customHeight="1" s="70">
       <c r="F712" s="66" t="n"/>
@@ -10572,6 +11297,7 @@
       <c r="O712" s="69" t="n"/>
       <c r="P712" s="62" t="n"/>
       <c r="Q712" s="62" t="n"/>
+      <c r="R712" s="88" t="n"/>
     </row>
     <row r="713" ht="12.75" customHeight="1" s="70">
       <c r="F713" s="66" t="n"/>
@@ -10582,6 +11308,7 @@
       <c r="O713" s="69" t="n"/>
       <c r="P713" s="62" t="n"/>
       <c r="Q713" s="62" t="n"/>
+      <c r="R713" s="88" t="n"/>
     </row>
     <row r="714" ht="12.75" customHeight="1" s="70">
       <c r="F714" s="66" t="n"/>
@@ -10592,6 +11319,7 @@
       <c r="O714" s="69" t="n"/>
       <c r="P714" s="62" t="n"/>
       <c r="Q714" s="62" t="n"/>
+      <c r="R714" s="88" t="n"/>
     </row>
     <row r="715" ht="12.75" customHeight="1" s="70">
       <c r="F715" s="66" t="n"/>
@@ -10602,6 +11330,7 @@
       <c r="O715" s="69" t="n"/>
       <c r="P715" s="62" t="n"/>
       <c r="Q715" s="62" t="n"/>
+      <c r="R715" s="88" t="n"/>
     </row>
     <row r="716" ht="12.75" customHeight="1" s="70">
       <c r="F716" s="66" t="n"/>
@@ -10612,6 +11341,7 @@
       <c r="O716" s="69" t="n"/>
       <c r="P716" s="62" t="n"/>
       <c r="Q716" s="62" t="n"/>
+      <c r="R716" s="88" t="n"/>
     </row>
     <row r="717" ht="12.75" customHeight="1" s="70">
       <c r="F717" s="66" t="n"/>
@@ -10622,6 +11352,7 @@
       <c r="O717" s="69" t="n"/>
       <c r="P717" s="62" t="n"/>
       <c r="Q717" s="62" t="n"/>
+      <c r="R717" s="88" t="n"/>
     </row>
     <row r="718" ht="12.75" customHeight="1" s="70">
       <c r="F718" s="66" t="n"/>
@@ -10632,6 +11363,7 @@
       <c r="O718" s="69" t="n"/>
       <c r="P718" s="62" t="n"/>
       <c r="Q718" s="62" t="n"/>
+      <c r="R718" s="88" t="n"/>
     </row>
     <row r="719" ht="12.75" customHeight="1" s="70">
       <c r="F719" s="66" t="n"/>
@@ -10642,6 +11374,7 @@
       <c r="O719" s="69" t="n"/>
       <c r="P719" s="62" t="n"/>
       <c r="Q719" s="62" t="n"/>
+      <c r="R719" s="88" t="n"/>
     </row>
     <row r="720" ht="12.75" customHeight="1" s="70">
       <c r="F720" s="66" t="n"/>
@@ -10652,6 +11385,7 @@
       <c r="O720" s="69" t="n"/>
       <c r="P720" s="62" t="n"/>
       <c r="Q720" s="62" t="n"/>
+      <c r="R720" s="88" t="n"/>
     </row>
     <row r="721" ht="12.75" customHeight="1" s="70">
       <c r="F721" s="66" t="n"/>
@@ -10662,6 +11396,7 @@
       <c r="O721" s="69" t="n"/>
       <c r="P721" s="62" t="n"/>
       <c r="Q721" s="62" t="n"/>
+      <c r="R721" s="88" t="n"/>
     </row>
     <row r="722" ht="12.75" customHeight="1" s="70">
       <c r="F722" s="66" t="n"/>
@@ -10672,6 +11407,7 @@
       <c r="O722" s="69" t="n"/>
       <c r="P722" s="62" t="n"/>
       <c r="Q722" s="62" t="n"/>
+      <c r="R722" s="88" t="n"/>
     </row>
     <row r="723" ht="12.75" customHeight="1" s="70">
       <c r="F723" s="66" t="n"/>
@@ -10682,6 +11418,7 @@
       <c r="O723" s="69" t="n"/>
       <c r="P723" s="62" t="n"/>
       <c r="Q723" s="62" t="n"/>
+      <c r="R723" s="88" t="n"/>
     </row>
     <row r="724" ht="12.75" customHeight="1" s="70">
       <c r="F724" s="66" t="n"/>
@@ -10692,6 +11429,7 @@
       <c r="O724" s="69" t="n"/>
       <c r="P724" s="62" t="n"/>
       <c r="Q724" s="62" t="n"/>
+      <c r="R724" s="88" t="n"/>
     </row>
     <row r="725" ht="12.75" customHeight="1" s="70">
       <c r="F725" s="66" t="n"/>
@@ -10702,6 +11440,7 @@
       <c r="O725" s="69" t="n"/>
       <c r="P725" s="62" t="n"/>
       <c r="Q725" s="62" t="n"/>
+      <c r="R725" s="88" t="n"/>
     </row>
     <row r="726" ht="12.75" customHeight="1" s="70">
       <c r="F726" s="66" t="n"/>
@@ -10712,6 +11451,7 @@
       <c r="O726" s="69" t="n"/>
       <c r="P726" s="62" t="n"/>
       <c r="Q726" s="62" t="n"/>
+      <c r="R726" s="88" t="n"/>
     </row>
     <row r="727" ht="12.75" customHeight="1" s="70">
       <c r="F727" s="66" t="n"/>
@@ -10722,6 +11462,7 @@
       <c r="O727" s="69" t="n"/>
       <c r="P727" s="62" t="n"/>
       <c r="Q727" s="62" t="n"/>
+      <c r="R727" s="88" t="n"/>
     </row>
     <row r="728" ht="12.75" customHeight="1" s="70">
       <c r="F728" s="66" t="n"/>
@@ -10732,6 +11473,7 @@
       <c r="O728" s="69" t="n"/>
       <c r="P728" s="62" t="n"/>
       <c r="Q728" s="62" t="n"/>
+      <c r="R728" s="88" t="n"/>
     </row>
     <row r="729" ht="12.75" customHeight="1" s="70">
       <c r="F729" s="66" t="n"/>
@@ -10742,6 +11484,7 @@
       <c r="O729" s="69" t="n"/>
       <c r="P729" s="62" t="n"/>
       <c r="Q729" s="62" t="n"/>
+      <c r="R729" s="88" t="n"/>
     </row>
     <row r="730" ht="12.75" customHeight="1" s="70">
       <c r="F730" s="66" t="n"/>
@@ -10752,6 +11495,7 @@
       <c r="O730" s="69" t="n"/>
       <c r="P730" s="62" t="n"/>
       <c r="Q730" s="62" t="n"/>
+      <c r="R730" s="88" t="n"/>
     </row>
     <row r="731" ht="12.75" customHeight="1" s="70">
       <c r="F731" s="66" t="n"/>
@@ -10762,6 +11506,7 @@
       <c r="O731" s="69" t="n"/>
       <c r="P731" s="62" t="n"/>
       <c r="Q731" s="62" t="n"/>
+      <c r="R731" s="88" t="n"/>
     </row>
     <row r="732" ht="12.75" customHeight="1" s="70">
       <c r="F732" s="66" t="n"/>
@@ -10772,6 +11517,7 @@
       <c r="O732" s="69" t="n"/>
       <c r="P732" s="62" t="n"/>
       <c r="Q732" s="62" t="n"/>
+      <c r="R732" s="88" t="n"/>
     </row>
     <row r="733" ht="12.75" customHeight="1" s="70">
       <c r="F733" s="66" t="n"/>
@@ -10782,6 +11528,7 @@
       <c r="O733" s="69" t="n"/>
       <c r="P733" s="62" t="n"/>
       <c r="Q733" s="62" t="n"/>
+      <c r="R733" s="88" t="n"/>
     </row>
     <row r="734" ht="12.75" customHeight="1" s="70">
       <c r="F734" s="66" t="n"/>
@@ -10792,6 +11539,7 @@
       <c r="O734" s="69" t="n"/>
       <c r="P734" s="62" t="n"/>
       <c r="Q734" s="62" t="n"/>
+      <c r="R734" s="88" t="n"/>
     </row>
     <row r="735" ht="12.75" customHeight="1" s="70">
       <c r="F735" s="66" t="n"/>
@@ -10802,6 +11550,7 @@
       <c r="O735" s="69" t="n"/>
       <c r="P735" s="62" t="n"/>
       <c r="Q735" s="62" t="n"/>
+      <c r="R735" s="88" t="n"/>
     </row>
     <row r="736" ht="12.75" customHeight="1" s="70">
       <c r="F736" s="66" t="n"/>
@@ -10812,6 +11561,7 @@
       <c r="O736" s="69" t="n"/>
       <c r="P736" s="62" t="n"/>
       <c r="Q736" s="62" t="n"/>
+      <c r="R736" s="88" t="n"/>
     </row>
     <row r="737" ht="12.75" customHeight="1" s="70">
       <c r="F737" s="66" t="n"/>
@@ -10822,6 +11572,7 @@
       <c r="O737" s="69" t="n"/>
       <c r="P737" s="62" t="n"/>
       <c r="Q737" s="62" t="n"/>
+      <c r="R737" s="88" t="n"/>
     </row>
     <row r="738" ht="12.75" customHeight="1" s="70">
       <c r="F738" s="66" t="n"/>
@@ -10832,6 +11583,7 @@
       <c r="O738" s="69" t="n"/>
       <c r="P738" s="62" t="n"/>
       <c r="Q738" s="62" t="n"/>
+      <c r="R738" s="88" t="n"/>
     </row>
     <row r="739" ht="12.75" customHeight="1" s="70">
       <c r="F739" s="66" t="n"/>
@@ -10842,6 +11594,7 @@
       <c r="O739" s="69" t="n"/>
       <c r="P739" s="62" t="n"/>
       <c r="Q739" s="62" t="n"/>
+      <c r="R739" s="88" t="n"/>
     </row>
     <row r="740" ht="12.75" customHeight="1" s="70">
       <c r="F740" s="66" t="n"/>
@@ -10852,6 +11605,7 @@
       <c r="O740" s="69" t="n"/>
       <c r="P740" s="62" t="n"/>
       <c r="Q740" s="62" t="n"/>
+      <c r="R740" s="88" t="n"/>
     </row>
     <row r="741" ht="12.75" customHeight="1" s="70">
       <c r="F741" s="66" t="n"/>
@@ -10862,6 +11616,7 @@
       <c r="O741" s="69" t="n"/>
       <c r="P741" s="62" t="n"/>
       <c r="Q741" s="62" t="n"/>
+      <c r="R741" s="88" t="n"/>
     </row>
     <row r="742" ht="12.75" customHeight="1" s="70">
       <c r="F742" s="66" t="n"/>
@@ -10872,6 +11627,7 @@
       <c r="O742" s="69" t="n"/>
       <c r="P742" s="62" t="n"/>
       <c r="Q742" s="62" t="n"/>
+      <c r="R742" s="88" t="n"/>
     </row>
     <row r="743" ht="12.75" customHeight="1" s="70">
       <c r="F743" s="66" t="n"/>
@@ -10882,6 +11638,7 @@
       <c r="O743" s="69" t="n"/>
       <c r="P743" s="62" t="n"/>
       <c r="Q743" s="62" t="n"/>
+      <c r="R743" s="88" t="n"/>
     </row>
     <row r="744" ht="12.75" customHeight="1" s="70">
       <c r="F744" s="66" t="n"/>
@@ -10892,6 +11649,7 @@
       <c r="O744" s="69" t="n"/>
       <c r="P744" s="62" t="n"/>
       <c r="Q744" s="62" t="n"/>
+      <c r="R744" s="88" t="n"/>
     </row>
     <row r="745" ht="12.75" customHeight="1" s="70">
       <c r="F745" s="66" t="n"/>
@@ -10902,6 +11660,7 @@
       <c r="O745" s="69" t="n"/>
       <c r="P745" s="62" t="n"/>
       <c r="Q745" s="62" t="n"/>
+      <c r="R745" s="88" t="n"/>
     </row>
     <row r="746" ht="12.75" customHeight="1" s="70">
       <c r="F746" s="66" t="n"/>
@@ -10912,6 +11671,7 @@
       <c r="O746" s="69" t="n"/>
       <c r="P746" s="62" t="n"/>
       <c r="Q746" s="62" t="n"/>
+      <c r="R746" s="88" t="n"/>
     </row>
     <row r="747" ht="12.75" customHeight="1" s="70">
       <c r="F747" s="66" t="n"/>
@@ -10922,6 +11682,7 @@
       <c r="O747" s="69" t="n"/>
       <c r="P747" s="62" t="n"/>
       <c r="Q747" s="62" t="n"/>
+      <c r="R747" s="88" t="n"/>
     </row>
     <row r="748" ht="12.75" customHeight="1" s="70">
       <c r="F748" s="66" t="n"/>
@@ -10932,6 +11693,7 @@
       <c r="O748" s="69" t="n"/>
       <c r="P748" s="62" t="n"/>
       <c r="Q748" s="62" t="n"/>
+      <c r="R748" s="88" t="n"/>
     </row>
     <row r="749" ht="12.75" customHeight="1" s="70">
       <c r="F749" s="66" t="n"/>
@@ -10942,6 +11704,7 @@
       <c r="O749" s="69" t="n"/>
       <c r="P749" s="62" t="n"/>
       <c r="Q749" s="62" t="n"/>
+      <c r="R749" s="88" t="n"/>
     </row>
     <row r="750" ht="12.75" customHeight="1" s="70">
       <c r="F750" s="66" t="n"/>
@@ -10952,6 +11715,7 @@
       <c r="O750" s="69" t="n"/>
       <c r="P750" s="62" t="n"/>
       <c r="Q750" s="62" t="n"/>
+      <c r="R750" s="88" t="n"/>
     </row>
     <row r="751" ht="12.75" customHeight="1" s="70">
       <c r="F751" s="66" t="n"/>
@@ -10962,6 +11726,7 @@
       <c r="O751" s="69" t="n"/>
       <c r="P751" s="62" t="n"/>
       <c r="Q751" s="62" t="n"/>
+      <c r="R751" s="88" t="n"/>
     </row>
     <row r="752" ht="12.75" customHeight="1" s="70">
       <c r="F752" s="66" t="n"/>
@@ -10972,6 +11737,7 @@
       <c r="O752" s="69" t="n"/>
       <c r="P752" s="62" t="n"/>
       <c r="Q752" s="62" t="n"/>
+      <c r="R752" s="88" t="n"/>
     </row>
     <row r="753" ht="12.75" customHeight="1" s="70">
       <c r="F753" s="66" t="n"/>
@@ -10982,6 +11748,7 @@
       <c r="O753" s="69" t="n"/>
       <c r="P753" s="62" t="n"/>
       <c r="Q753" s="62" t="n"/>
+      <c r="R753" s="88" t="n"/>
     </row>
     <row r="754" ht="12.75" customHeight="1" s="70">
       <c r="F754" s="66" t="n"/>
@@ -10992,6 +11759,7 @@
       <c r="O754" s="69" t="n"/>
       <c r="P754" s="62" t="n"/>
       <c r="Q754" s="62" t="n"/>
+      <c r="R754" s="88" t="n"/>
     </row>
     <row r="755" ht="12.75" customHeight="1" s="70">
       <c r="F755" s="66" t="n"/>
@@ -11002,6 +11770,7 @@
       <c r="O755" s="69" t="n"/>
       <c r="P755" s="62" t="n"/>
       <c r="Q755" s="62" t="n"/>
+      <c r="R755" s="88" t="n"/>
     </row>
     <row r="756" ht="12.75" customHeight="1" s="70">
       <c r="F756" s="66" t="n"/>
@@ -11012,6 +11781,7 @@
       <c r="O756" s="69" t="n"/>
       <c r="P756" s="62" t="n"/>
       <c r="Q756" s="62" t="n"/>
+      <c r="R756" s="88" t="n"/>
     </row>
     <row r="757" ht="12.75" customHeight="1" s="70">
       <c r="F757" s="66" t="n"/>
@@ -11022,6 +11792,7 @@
       <c r="O757" s="69" t="n"/>
       <c r="P757" s="62" t="n"/>
       <c r="Q757" s="62" t="n"/>
+      <c r="R757" s="88" t="n"/>
     </row>
     <row r="758" ht="12.75" customHeight="1" s="70">
       <c r="F758" s="66" t="n"/>
@@ -11032,6 +11803,7 @@
       <c r="O758" s="69" t="n"/>
       <c r="P758" s="62" t="n"/>
       <c r="Q758" s="62" t="n"/>
+      <c r="R758" s="88" t="n"/>
     </row>
     <row r="759" ht="12.75" customHeight="1" s="70">
       <c r="F759" s="66" t="n"/>
@@ -11042,6 +11814,7 @@
       <c r="O759" s="69" t="n"/>
       <c r="P759" s="62" t="n"/>
       <c r="Q759" s="62" t="n"/>
+      <c r="R759" s="88" t="n"/>
     </row>
     <row r="760" ht="12.75" customHeight="1" s="70">
       <c r="F760" s="66" t="n"/>
@@ -11052,6 +11825,7 @@
       <c r="O760" s="69" t="n"/>
       <c r="P760" s="62" t="n"/>
       <c r="Q760" s="62" t="n"/>
+      <c r="R760" s="88" t="n"/>
     </row>
     <row r="761" ht="12.75" customHeight="1" s="70">
       <c r="F761" s="66" t="n"/>
@@ -11062,6 +11836,7 @@
       <c r="O761" s="69" t="n"/>
       <c r="P761" s="62" t="n"/>
       <c r="Q761" s="62" t="n"/>
+      <c r="R761" s="88" t="n"/>
     </row>
     <row r="762" ht="12.75" customHeight="1" s="70">
       <c r="F762" s="66" t="n"/>
@@ -11072,6 +11847,7 @@
       <c r="O762" s="69" t="n"/>
       <c r="P762" s="62" t="n"/>
       <c r="Q762" s="62" t="n"/>
+      <c r="R762" s="88" t="n"/>
     </row>
     <row r="763" ht="12.75" customHeight="1" s="70">
       <c r="F763" s="66" t="n"/>
@@ -11082,6 +11858,7 @@
       <c r="O763" s="69" t="n"/>
       <c r="P763" s="62" t="n"/>
       <c r="Q763" s="62" t="n"/>
+      <c r="R763" s="88" t="n"/>
     </row>
     <row r="764" ht="12.75" customHeight="1" s="70">
       <c r="F764" s="66" t="n"/>
@@ -11092,6 +11869,7 @@
       <c r="O764" s="69" t="n"/>
       <c r="P764" s="62" t="n"/>
       <c r="Q764" s="62" t="n"/>
+      <c r="R764" s="88" t="n"/>
     </row>
     <row r="765" ht="12.75" customHeight="1" s="70">
       <c r="F765" s="66" t="n"/>
@@ -11102,6 +11880,7 @@
       <c r="O765" s="69" t="n"/>
       <c r="P765" s="62" t="n"/>
       <c r="Q765" s="62" t="n"/>
+      <c r="R765" s="88" t="n"/>
     </row>
     <row r="766" ht="12.75" customHeight="1" s="70">
       <c r="F766" s="66" t="n"/>
@@ -11112,6 +11891,7 @@
       <c r="O766" s="69" t="n"/>
       <c r="P766" s="62" t="n"/>
       <c r="Q766" s="62" t="n"/>
+      <c r="R766" s="88" t="n"/>
     </row>
     <row r="767" ht="12.75" customHeight="1" s="70">
       <c r="F767" s="66" t="n"/>
@@ -11122,6 +11902,7 @@
       <c r="O767" s="69" t="n"/>
       <c r="P767" s="62" t="n"/>
       <c r="Q767" s="62" t="n"/>
+      <c r="R767" s="88" t="n"/>
     </row>
     <row r="768" ht="12.75" customHeight="1" s="70">
       <c r="F768" s="66" t="n"/>
@@ -11132,6 +11913,7 @@
       <c r="O768" s="69" t="n"/>
       <c r="P768" s="62" t="n"/>
       <c r="Q768" s="62" t="n"/>
+      <c r="R768" s="88" t="n"/>
     </row>
     <row r="769" ht="12.75" customHeight="1" s="70">
       <c r="F769" s="66" t="n"/>
@@ -11142,6 +11924,7 @@
       <c r="O769" s="69" t="n"/>
       <c r="P769" s="62" t="n"/>
       <c r="Q769" s="62" t="n"/>
+      <c r="R769" s="88" t="n"/>
     </row>
     <row r="770" ht="12.75" customHeight="1" s="70">
       <c r="F770" s="66" t="n"/>
@@ -11152,6 +11935,7 @@
       <c r="O770" s="69" t="n"/>
       <c r="P770" s="62" t="n"/>
       <c r="Q770" s="62" t="n"/>
+      <c r="R770" s="88" t="n"/>
     </row>
     <row r="771" ht="12.75" customHeight="1" s="70">
       <c r="F771" s="66" t="n"/>
@@ -11162,6 +11946,7 @@
       <c r="O771" s="69" t="n"/>
       <c r="P771" s="62" t="n"/>
       <c r="Q771" s="62" t="n"/>
+      <c r="R771" s="88" t="n"/>
     </row>
     <row r="772" ht="12.75" customHeight="1" s="70">
       <c r="F772" s="66" t="n"/>
@@ -11172,6 +11957,7 @@
       <c r="O772" s="69" t="n"/>
       <c r="P772" s="62" t="n"/>
       <c r="Q772" s="62" t="n"/>
+      <c r="R772" s="88" t="n"/>
     </row>
     <row r="773" ht="12.75" customHeight="1" s="70">
       <c r="F773" s="66" t="n"/>
@@ -11182,6 +11968,7 @@
       <c r="O773" s="69" t="n"/>
       <c r="P773" s="62" t="n"/>
       <c r="Q773" s="62" t="n"/>
+      <c r="R773" s="88" t="n"/>
     </row>
     <row r="774" ht="12.75" customHeight="1" s="70">
       <c r="F774" s="66" t="n"/>
@@ -11192,6 +11979,7 @@
       <c r="O774" s="69" t="n"/>
       <c r="P774" s="62" t="n"/>
       <c r="Q774" s="62" t="n"/>
+      <c r="R774" s="88" t="n"/>
     </row>
     <row r="775" ht="12.75" customHeight="1" s="70">
       <c r="F775" s="66" t="n"/>
@@ -11202,6 +11990,7 @@
       <c r="O775" s="69" t="n"/>
       <c r="P775" s="62" t="n"/>
       <c r="Q775" s="62" t="n"/>
+      <c r="R775" s="88" t="n"/>
     </row>
     <row r="776" ht="12.75" customHeight="1" s="70">
       <c r="F776" s="66" t="n"/>
@@ -11212,6 +12001,7 @@
       <c r="O776" s="69" t="n"/>
       <c r="P776" s="62" t="n"/>
       <c r="Q776" s="62" t="n"/>
+      <c r="R776" s="88" t="n"/>
     </row>
     <row r="777" ht="12.75" customHeight="1" s="70">
       <c r="F777" s="66" t="n"/>
@@ -11222,6 +12012,7 @@
       <c r="O777" s="69" t="n"/>
       <c r="P777" s="62" t="n"/>
       <c r="Q777" s="62" t="n"/>
+      <c r="R777" s="88" t="n"/>
     </row>
     <row r="778" ht="12.75" customHeight="1" s="70">
       <c r="F778" s="66" t="n"/>
@@ -11232,6 +12023,7 @@
       <c r="O778" s="69" t="n"/>
       <c r="P778" s="62" t="n"/>
       <c r="Q778" s="62" t="n"/>
+      <c r="R778" s="88" t="n"/>
     </row>
     <row r="779" ht="12.75" customHeight="1" s="70">
       <c r="F779" s="66" t="n"/>
@@ -11242,6 +12034,7 @@
       <c r="O779" s="69" t="n"/>
       <c r="P779" s="62" t="n"/>
       <c r="Q779" s="62" t="n"/>
+      <c r="R779" s="88" t="n"/>
     </row>
     <row r="780" ht="12.75" customHeight="1" s="70">
       <c r="F780" s="66" t="n"/>
@@ -11252,6 +12045,7 @@
       <c r="O780" s="69" t="n"/>
       <c r="P780" s="62" t="n"/>
       <c r="Q780" s="62" t="n"/>
+      <c r="R780" s="88" t="n"/>
     </row>
     <row r="781" ht="12.75" customHeight="1" s="70">
       <c r="F781" s="66" t="n"/>
@@ -11262,6 +12056,7 @@
       <c r="O781" s="69" t="n"/>
       <c r="P781" s="62" t="n"/>
       <c r="Q781" s="62" t="n"/>
+      <c r="R781" s="88" t="n"/>
     </row>
     <row r="782" ht="12.75" customHeight="1" s="70">
       <c r="F782" s="66" t="n"/>
@@ -11272,6 +12067,7 @@
       <c r="O782" s="69" t="n"/>
       <c r="P782" s="62" t="n"/>
       <c r="Q782" s="62" t="n"/>
+      <c r="R782" s="88" t="n"/>
     </row>
     <row r="783" ht="12.75" customHeight="1" s="70">
       <c r="F783" s="66" t="n"/>
@@ -11282,6 +12078,7 @@
       <c r="O783" s="69" t="n"/>
       <c r="P783" s="62" t="n"/>
       <c r="Q783" s="62" t="n"/>
+      <c r="R783" s="88" t="n"/>
     </row>
     <row r="784" ht="12.75" customHeight="1" s="70">
       <c r="F784" s="66" t="n"/>
@@ -11292,6 +12089,7 @@
       <c r="O784" s="69" t="n"/>
       <c r="P784" s="62" t="n"/>
       <c r="Q784" s="62" t="n"/>
+      <c r="R784" s="88" t="n"/>
     </row>
     <row r="785" ht="12.75" customHeight="1" s="70">
       <c r="F785" s="66" t="n"/>
@@ -11302,6 +12100,7 @@
       <c r="O785" s="69" t="n"/>
       <c r="P785" s="62" t="n"/>
       <c r="Q785" s="62" t="n"/>
+      <c r="R785" s="88" t="n"/>
     </row>
     <row r="786" ht="12.75" customHeight="1" s="70">
       <c r="F786" s="66" t="n"/>
@@ -11312,6 +12111,7 @@
       <c r="O786" s="69" t="n"/>
       <c r="P786" s="62" t="n"/>
       <c r="Q786" s="62" t="n"/>
+      <c r="R786" s="88" t="n"/>
     </row>
     <row r="787" ht="12.75" customHeight="1" s="70">
       <c r="F787" s="66" t="n"/>
@@ -11322,6 +12122,7 @@
       <c r="O787" s="69" t="n"/>
       <c r="P787" s="62" t="n"/>
       <c r="Q787" s="62" t="n"/>
+      <c r="R787" s="88" t="n"/>
     </row>
     <row r="788" ht="12.75" customHeight="1" s="70">
       <c r="F788" s="66" t="n"/>
@@ -11332,6 +12133,7 @@
       <c r="O788" s="69" t="n"/>
       <c r="P788" s="62" t="n"/>
       <c r="Q788" s="62" t="n"/>
+      <c r="R788" s="88" t="n"/>
     </row>
     <row r="789" ht="12.75" customHeight="1" s="70">
       <c r="F789" s="66" t="n"/>
@@ -11342,6 +12144,7 @@
       <c r="O789" s="69" t="n"/>
       <c r="P789" s="62" t="n"/>
       <c r="Q789" s="62" t="n"/>
+      <c r="R789" s="88" t="n"/>
     </row>
     <row r="790" ht="12.75" customHeight="1" s="70">
       <c r="F790" s="66" t="n"/>
@@ -11352,6 +12155,7 @@
       <c r="O790" s="69" t="n"/>
       <c r="P790" s="62" t="n"/>
       <c r="Q790" s="62" t="n"/>
+      <c r="R790" s="88" t="n"/>
     </row>
     <row r="791" ht="12.75" customHeight="1" s="70">
       <c r="F791" s="66" t="n"/>
@@ -11362,6 +12166,7 @@
       <c r="O791" s="69" t="n"/>
       <c r="P791" s="62" t="n"/>
       <c r="Q791" s="62" t="n"/>
+      <c r="R791" s="88" t="n"/>
     </row>
     <row r="792" ht="12.75" customHeight="1" s="70">
       <c r="F792" s="66" t="n"/>
@@ -11372,6 +12177,7 @@
       <c r="O792" s="69" t="n"/>
       <c r="P792" s="62" t="n"/>
       <c r="Q792" s="62" t="n"/>
+      <c r="R792" s="88" t="n"/>
     </row>
     <row r="793" ht="12.75" customHeight="1" s="70">
       <c r="F793" s="66" t="n"/>
@@ -11382,6 +12188,7 @@
       <c r="O793" s="69" t="n"/>
       <c r="P793" s="62" t="n"/>
       <c r="Q793" s="62" t="n"/>
+      <c r="R793" s="88" t="n"/>
     </row>
     <row r="794" ht="12.75" customHeight="1" s="70">
       <c r="F794" s="66" t="n"/>
@@ -11392,6 +12199,7 @@
       <c r="O794" s="69" t="n"/>
       <c r="P794" s="62" t="n"/>
       <c r="Q794" s="62" t="n"/>
+      <c r="R794" s="88" t="n"/>
     </row>
     <row r="795" ht="12.75" customHeight="1" s="70">
       <c r="F795" s="66" t="n"/>
@@ -11402,6 +12210,7 @@
       <c r="O795" s="69" t="n"/>
       <c r="P795" s="62" t="n"/>
       <c r="Q795" s="62" t="n"/>
+      <c r="R795" s="88" t="n"/>
     </row>
     <row r="796" ht="12.75" customHeight="1" s="70">
       <c r="F796" s="66" t="n"/>
@@ -11412,6 +12221,7 @@
       <c r="O796" s="69" t="n"/>
       <c r="P796" s="62" t="n"/>
       <c r="Q796" s="62" t="n"/>
+      <c r="R796" s="88" t="n"/>
     </row>
     <row r="797" ht="12.75" customHeight="1" s="70">
       <c r="F797" s="66" t="n"/>
@@ -11422,6 +12232,7 @@
       <c r="O797" s="69" t="n"/>
       <c r="P797" s="62" t="n"/>
       <c r="Q797" s="62" t="n"/>
+      <c r="R797" s="88" t="n"/>
     </row>
     <row r="798" ht="12.75" customHeight="1" s="70">
       <c r="F798" s="66" t="n"/>
@@ -11432,6 +12243,7 @@
       <c r="O798" s="69" t="n"/>
       <c r="P798" s="62" t="n"/>
       <c r="Q798" s="62" t="n"/>
+      <c r="R798" s="88" t="n"/>
     </row>
     <row r="799" ht="12.75" customHeight="1" s="70">
       <c r="F799" s="66" t="n"/>
@@ -11442,6 +12254,7 @@
       <c r="O799" s="69" t="n"/>
       <c r="P799" s="62" t="n"/>
       <c r="Q799" s="62" t="n"/>
+      <c r="R799" s="88" t="n"/>
     </row>
     <row r="800" ht="12.75" customHeight="1" s="70">
       <c r="F800" s="66" t="n"/>
@@ -11452,6 +12265,7 @@
       <c r="O800" s="69" t="n"/>
       <c r="P800" s="62" t="n"/>
       <c r="Q800" s="62" t="n"/>
+      <c r="R800" s="88" t="n"/>
     </row>
     <row r="801" ht="12.75" customHeight="1" s="70">
       <c r="F801" s="66" t="n"/>
@@ -11462,6 +12276,7 @@
       <c r="O801" s="69" t="n"/>
       <c r="P801" s="62" t="n"/>
       <c r="Q801" s="62" t="n"/>
+      <c r="R801" s="88" t="n"/>
     </row>
     <row r="802" ht="12.75" customHeight="1" s="70">
       <c r="F802" s="66" t="n"/>
@@ -11472,6 +12287,7 @@
       <c r="O802" s="69" t="n"/>
       <c r="P802" s="62" t="n"/>
       <c r="Q802" s="62" t="n"/>
+      <c r="R802" s="88" t="n"/>
     </row>
     <row r="803" ht="12.75" customHeight="1" s="70">
       <c r="F803" s="66" t="n"/>
@@ -11482,6 +12298,7 @@
       <c r="O803" s="69" t="n"/>
       <c r="P803" s="62" t="n"/>
       <c r="Q803" s="62" t="n"/>
+      <c r="R803" s="88" t="n"/>
     </row>
     <row r="804" ht="12.75" customHeight="1" s="70">
       <c r="F804" s="66" t="n"/>
@@ -11492,6 +12309,7 @@
       <c r="O804" s="69" t="n"/>
       <c r="P804" s="62" t="n"/>
       <c r="Q804" s="62" t="n"/>
+      <c r="R804" s="88" t="n"/>
     </row>
     <row r="805" ht="12.75" customHeight="1" s="70">
       <c r="F805" s="66" t="n"/>
@@ -11502,6 +12320,7 @@
       <c r="O805" s="69" t="n"/>
       <c r="P805" s="62" t="n"/>
       <c r="Q805" s="62" t="n"/>
+      <c r="R805" s="88" t="n"/>
     </row>
     <row r="806" ht="12.75" customHeight="1" s="70">
       <c r="F806" s="66" t="n"/>
@@ -11512,6 +12331,7 @@
       <c r="O806" s="69" t="n"/>
       <c r="P806" s="62" t="n"/>
       <c r="Q806" s="62" t="n"/>
+      <c r="R806" s="88" t="n"/>
     </row>
     <row r="807" ht="12.75" customHeight="1" s="70">
       <c r="F807" s="66" t="n"/>
@@ -11522,6 +12342,7 @@
       <c r="O807" s="69" t="n"/>
       <c r="P807" s="62" t="n"/>
       <c r="Q807" s="62" t="n"/>
+      <c r="R807" s="88" t="n"/>
     </row>
     <row r="808" ht="12.75" customHeight="1" s="70">
       <c r="F808" s="66" t="n"/>
@@ -11532,6 +12353,7 @@
       <c r="O808" s="69" t="n"/>
       <c r="P808" s="62" t="n"/>
       <c r="Q808" s="62" t="n"/>
+      <c r="R808" s="88" t="n"/>
     </row>
     <row r="809" ht="12.75" customHeight="1" s="70">
       <c r="F809" s="66" t="n"/>
@@ -11542,6 +12364,7 @@
       <c r="O809" s="69" t="n"/>
       <c r="P809" s="62" t="n"/>
       <c r="Q809" s="62" t="n"/>
+      <c r="R809" s="88" t="n"/>
     </row>
     <row r="810" ht="12.75" customHeight="1" s="70">
       <c r="F810" s="66" t="n"/>
@@ -11552,6 +12375,7 @@
       <c r="O810" s="69" t="n"/>
       <c r="P810" s="62" t="n"/>
       <c r="Q810" s="62" t="n"/>
+      <c r="R810" s="88" t="n"/>
     </row>
     <row r="811" ht="12.75" customHeight="1" s="70">
       <c r="F811" s="66" t="n"/>
@@ -11562,6 +12386,7 @@
       <c r="O811" s="69" t="n"/>
       <c r="P811" s="62" t="n"/>
       <c r="Q811" s="62" t="n"/>
+      <c r="R811" s="88" t="n"/>
     </row>
     <row r="812" ht="12.75" customHeight="1" s="70">
       <c r="F812" s="66" t="n"/>
@@ -11572,6 +12397,7 @@
       <c r="O812" s="69" t="n"/>
       <c r="P812" s="62" t="n"/>
       <c r="Q812" s="62" t="n"/>
+      <c r="R812" s="88" t="n"/>
     </row>
     <row r="813" ht="12.75" customHeight="1" s="70">
       <c r="F813" s="66" t="n"/>
@@ -11582,6 +12408,7 @@
       <c r="O813" s="69" t="n"/>
       <c r="P813" s="62" t="n"/>
       <c r="Q813" s="62" t="n"/>
+      <c r="R813" s="88" t="n"/>
     </row>
     <row r="814" ht="12.75" customHeight="1" s="70">
       <c r="F814" s="66" t="n"/>
@@ -11592,6 +12419,7 @@
       <c r="O814" s="69" t="n"/>
       <c r="P814" s="62" t="n"/>
       <c r="Q814" s="62" t="n"/>
+      <c r="R814" s="88" t="n"/>
     </row>
     <row r="815" ht="12.75" customHeight="1" s="70">
       <c r="F815" s="66" t="n"/>
@@ -11602,6 +12430,7 @@
       <c r="O815" s="69" t="n"/>
       <c r="P815" s="62" t="n"/>
       <c r="Q815" s="62" t="n"/>
+      <c r="R815" s="88" t="n"/>
     </row>
     <row r="816" ht="12.75" customHeight="1" s="70">
       <c r="F816" s="66" t="n"/>
@@ -11612,6 +12441,7 @@
       <c r="O816" s="69" t="n"/>
       <c r="P816" s="62" t="n"/>
       <c r="Q816" s="62" t="n"/>
+      <c r="R816" s="88" t="n"/>
     </row>
     <row r="817" ht="12.75" customHeight="1" s="70">
       <c r="F817" s="66" t="n"/>
@@ -11622,6 +12452,7 @@
       <c r="O817" s="69" t="n"/>
       <c r="P817" s="62" t="n"/>
       <c r="Q817" s="62" t="n"/>
+      <c r="R817" s="88" t="n"/>
     </row>
     <row r="818" ht="12.75" customHeight="1" s="70">
       <c r="F818" s="66" t="n"/>
@@ -11632,6 +12463,7 @@
       <c r="O818" s="69" t="n"/>
       <c r="P818" s="62" t="n"/>
       <c r="Q818" s="62" t="n"/>
+      <c r="R818" s="88" t="n"/>
     </row>
     <row r="819" ht="12.75" customHeight="1" s="70">
       <c r="F819" s="66" t="n"/>
@@ -11642,6 +12474,7 @@
       <c r="O819" s="69" t="n"/>
       <c r="P819" s="62" t="n"/>
       <c r="Q819" s="62" t="n"/>
+      <c r="R819" s="88" t="n"/>
     </row>
     <row r="820" ht="12.75" customHeight="1" s="70">
       <c r="F820" s="66" t="n"/>
@@ -11652,6 +12485,7 @@
       <c r="O820" s="69" t="n"/>
       <c r="P820" s="62" t="n"/>
       <c r="Q820" s="62" t="n"/>
+      <c r="R820" s="88" t="n"/>
     </row>
     <row r="821" ht="12.75" customHeight="1" s="70">
       <c r="F821" s="66" t="n"/>
@@ -11662,6 +12496,7 @@
       <c r="O821" s="69" t="n"/>
       <c r="P821" s="62" t="n"/>
       <c r="Q821" s="62" t="n"/>
+      <c r="R821" s="88" t="n"/>
     </row>
     <row r="822" ht="12.75" customHeight="1" s="70">
       <c r="F822" s="66" t="n"/>
@@ -11672,6 +12507,7 @@
       <c r="O822" s="69" t="n"/>
       <c r="P822" s="62" t="n"/>
       <c r="Q822" s="62" t="n"/>
+      <c r="R822" s="88" t="n"/>
     </row>
     <row r="823" ht="12.75" customHeight="1" s="70">
       <c r="F823" s="66" t="n"/>
@@ -11682,6 +12518,7 @@
       <c r="O823" s="69" t="n"/>
       <c r="P823" s="62" t="n"/>
       <c r="Q823" s="62" t="n"/>
+      <c r="R823" s="88" t="n"/>
     </row>
     <row r="824" ht="12.75" customHeight="1" s="70">
       <c r="F824" s="66" t="n"/>
@@ -11692,6 +12529,7 @@
       <c r="O824" s="69" t="n"/>
       <c r="P824" s="62" t="n"/>
       <c r="Q824" s="62" t="n"/>
+      <c r="R824" s="88" t="n"/>
     </row>
     <row r="825" ht="12.75" customHeight="1" s="70">
       <c r="F825" s="66" t="n"/>
@@ -11702,6 +12540,7 @@
       <c r="O825" s="69" t="n"/>
       <c r="P825" s="62" t="n"/>
       <c r="Q825" s="62" t="n"/>
+      <c r="R825" s="88" t="n"/>
     </row>
     <row r="826" ht="12.75" customHeight="1" s="70">
       <c r="F826" s="66" t="n"/>
@@ -11712,6 +12551,7 @@
       <c r="O826" s="69" t="n"/>
       <c r="P826" s="62" t="n"/>
       <c r="Q826" s="62" t="n"/>
+      <c r="R826" s="88" t="n"/>
     </row>
     <row r="827" ht="12.75" customHeight="1" s="70">
       <c r="F827" s="66" t="n"/>
@@ -11722,6 +12562,7 @@
       <c r="O827" s="69" t="n"/>
       <c r="P827" s="62" t="n"/>
       <c r="Q827" s="62" t="n"/>
+      <c r="R827" s="88" t="n"/>
     </row>
     <row r="828" ht="12.75" customHeight="1" s="70">
       <c r="F828" s="66" t="n"/>
@@ -11732,6 +12573,7 @@
       <c r="O828" s="69" t="n"/>
       <c r="P828" s="62" t="n"/>
       <c r="Q828" s="62" t="n"/>
+      <c r="R828" s="88" t="n"/>
     </row>
     <row r="829" ht="12.75" customHeight="1" s="70">
       <c r="F829" s="66" t="n"/>
@@ -11742,6 +12584,7 @@
       <c r="O829" s="69" t="n"/>
       <c r="P829" s="62" t="n"/>
       <c r="Q829" s="62" t="n"/>
+      <c r="R829" s="88" t="n"/>
     </row>
     <row r="830" ht="12.75" customHeight="1" s="70">
       <c r="F830" s="66" t="n"/>
@@ -11752,6 +12595,7 @@
       <c r="O830" s="69" t="n"/>
       <c r="P830" s="62" t="n"/>
       <c r="Q830" s="62" t="n"/>
+      <c r="R830" s="88" t="n"/>
     </row>
     <row r="831" ht="12.75" customHeight="1" s="70">
       <c r="F831" s="66" t="n"/>
@@ -11762,6 +12606,7 @@
       <c r="O831" s="69" t="n"/>
       <c r="P831" s="62" t="n"/>
       <c r="Q831" s="62" t="n"/>
+      <c r="R831" s="88" t="n"/>
     </row>
     <row r="832" ht="12.75" customHeight="1" s="70">
       <c r="F832" s="66" t="n"/>
@@ -11772,6 +12617,7 @@
       <c r="O832" s="69" t="n"/>
       <c r="P832" s="62" t="n"/>
       <c r="Q832" s="62" t="n"/>
+      <c r="R832" s="88" t="n"/>
     </row>
     <row r="833" ht="12.75" customHeight="1" s="70">
       <c r="F833" s="66" t="n"/>
@@ -11782,6 +12628,7 @@
       <c r="O833" s="69" t="n"/>
       <c r="P833" s="62" t="n"/>
       <c r="Q833" s="62" t="n"/>
+      <c r="R833" s="88" t="n"/>
     </row>
     <row r="834" ht="12.75" customHeight="1" s="70">
       <c r="F834" s="66" t="n"/>
@@ -11792,6 +12639,7 @@
       <c r="O834" s="69" t="n"/>
       <c r="P834" s="62" t="n"/>
       <c r="Q834" s="62" t="n"/>
+      <c r="R834" s="88" t="n"/>
     </row>
     <row r="835" ht="12.75" customHeight="1" s="70">
       <c r="F835" s="66" t="n"/>
@@ -11802,6 +12650,7 @@
       <c r="O835" s="69" t="n"/>
       <c r="P835" s="62" t="n"/>
       <c r="Q835" s="62" t="n"/>
+      <c r="R835" s="88" t="n"/>
     </row>
     <row r="836" ht="12.75" customHeight="1" s="70">
       <c r="F836" s="66" t="n"/>
@@ -11812,6 +12661,7 @@
       <c r="O836" s="69" t="n"/>
       <c r="P836" s="62" t="n"/>
       <c r="Q836" s="62" t="n"/>
+      <c r="R836" s="88" t="n"/>
     </row>
     <row r="837" ht="12.75" customHeight="1" s="70">
       <c r="F837" s="66" t="n"/>
@@ -11822,6 +12672,7 @@
       <c r="O837" s="69" t="n"/>
       <c r="P837" s="62" t="n"/>
       <c r="Q837" s="62" t="n"/>
+      <c r="R837" s="88" t="n"/>
     </row>
     <row r="838" ht="12.75" customHeight="1" s="70">
       <c r="F838" s="66" t="n"/>
@@ -11832,6 +12683,7 @@
       <c r="O838" s="69" t="n"/>
       <c r="P838" s="62" t="n"/>
       <c r="Q838" s="62" t="n"/>
+      <c r="R838" s="88" t="n"/>
     </row>
     <row r="839" ht="12.75" customHeight="1" s="70">
       <c r="F839" s="66" t="n"/>
@@ -11842,6 +12694,7 @@
       <c r="O839" s="69" t="n"/>
       <c r="P839" s="62" t="n"/>
       <c r="Q839" s="62" t="n"/>
+      <c r="R839" s="88" t="n"/>
     </row>
     <row r="840" ht="12.75" customHeight="1" s="70">
       <c r="F840" s="66" t="n"/>
@@ -11852,6 +12705,7 @@
       <c r="O840" s="69" t="n"/>
       <c r="P840" s="62" t="n"/>
       <c r="Q840" s="62" t="n"/>
+      <c r="R840" s="88" t="n"/>
     </row>
     <row r="841" ht="12.75" customHeight="1" s="70">
       <c r="F841" s="66" t="n"/>
@@ -11862,6 +12716,7 @@
       <c r="O841" s="69" t="n"/>
       <c r="P841" s="62" t="n"/>
       <c r="Q841" s="62" t="n"/>
+      <c r="R841" s="88" t="n"/>
     </row>
     <row r="842" ht="12.75" customHeight="1" s="70">
       <c r="F842" s="66" t="n"/>
@@ -11872,6 +12727,7 @@
       <c r="O842" s="69" t="n"/>
       <c r="P842" s="62" t="n"/>
       <c r="Q842" s="62" t="n"/>
+      <c r="R842" s="88" t="n"/>
     </row>
     <row r="843" ht="12.75" customHeight="1" s="70">
       <c r="F843" s="66" t="n"/>
@@ -11882,6 +12738,7 @@
       <c r="O843" s="69" t="n"/>
       <c r="P843" s="62" t="n"/>
       <c r="Q843" s="62" t="n"/>
+      <c r="R843" s="88" t="n"/>
     </row>
     <row r="844" ht="12.75" customHeight="1" s="70">
       <c r="F844" s="66" t="n"/>
@@ -11892,6 +12749,7 @@
       <c r="O844" s="69" t="n"/>
       <c r="P844" s="62" t="n"/>
       <c r="Q844" s="62" t="n"/>
+      <c r="R844" s="88" t="n"/>
     </row>
     <row r="845" ht="12.75" customHeight="1" s="70">
       <c r="F845" s="66" t="n"/>
@@ -11902,6 +12760,7 @@
       <c r="O845" s="69" t="n"/>
       <c r="P845" s="62" t="n"/>
       <c r="Q845" s="62" t="n"/>
+      <c r="R845" s="88" t="n"/>
     </row>
     <row r="846" ht="12.75" customHeight="1" s="70">
       <c r="F846" s="66" t="n"/>
@@ -11912,6 +12771,7 @@
       <c r="O846" s="69" t="n"/>
       <c r="P846" s="62" t="n"/>
       <c r="Q846" s="62" t="n"/>
+      <c r="R846" s="88" t="n"/>
     </row>
     <row r="847" ht="12.75" customHeight="1" s="70">
       <c r="F847" s="66" t="n"/>
@@ -11922,6 +12782,7 @@
       <c r="O847" s="69" t="n"/>
       <c r="P847" s="62" t="n"/>
       <c r="Q847" s="62" t="n"/>
+      <c r="R847" s="88" t="n"/>
     </row>
     <row r="848" ht="12.75" customHeight="1" s="70">
       <c r="F848" s="66" t="n"/>
@@ -11932,6 +12793,7 @@
       <c r="O848" s="69" t="n"/>
       <c r="P848" s="62" t="n"/>
       <c r="Q848" s="62" t="n"/>
+      <c r="R848" s="88" t="n"/>
     </row>
     <row r="849" ht="12.75" customHeight="1" s="70">
       <c r="F849" s="66" t="n"/>
@@ -11942,6 +12804,7 @@
       <c r="O849" s="69" t="n"/>
       <c r="P849" s="62" t="n"/>
       <c r="Q849" s="62" t="n"/>
+      <c r="R849" s="88" t="n"/>
     </row>
     <row r="850" ht="12.75" customHeight="1" s="70">
       <c r="F850" s="66" t="n"/>
@@ -11952,6 +12815,7 @@
       <c r="O850" s="69" t="n"/>
       <c r="P850" s="62" t="n"/>
       <c r="Q850" s="62" t="n"/>
+      <c r="R850" s="88" t="n"/>
     </row>
     <row r="851" ht="12.75" customHeight="1" s="70">
       <c r="F851" s="66" t="n"/>
@@ -11962,6 +12826,7 @@
       <c r="O851" s="69" t="n"/>
       <c r="P851" s="62" t="n"/>
       <c r="Q851" s="62" t="n"/>
+      <c r="R851" s="88" t="n"/>
     </row>
     <row r="852" ht="12.75" customHeight="1" s="70">
       <c r="F852" s="66" t="n"/>
@@ -11972,6 +12837,7 @@
       <c r="O852" s="69" t="n"/>
       <c r="P852" s="62" t="n"/>
       <c r="Q852" s="62" t="n"/>
+      <c r="R852" s="88" t="n"/>
     </row>
     <row r="853" ht="12.75" customHeight="1" s="70">
       <c r="F853" s="66" t="n"/>
@@ -11982,6 +12848,7 @@
       <c r="O853" s="69" t="n"/>
       <c r="P853" s="62" t="n"/>
       <c r="Q853" s="62" t="n"/>
+      <c r="R853" s="88" t="n"/>
     </row>
     <row r="854" ht="12.75" customHeight="1" s="70">
       <c r="F854" s="66" t="n"/>
@@ -11992,6 +12859,7 @@
       <c r="O854" s="69" t="n"/>
       <c r="P854" s="62" t="n"/>
       <c r="Q854" s="62" t="n"/>
+      <c r="R854" s="88" t="n"/>
     </row>
     <row r="855" ht="12.75" customHeight="1" s="70">
       <c r="F855" s="66" t="n"/>
@@ -12002,6 +12870,7 @@
       <c r="O855" s="69" t="n"/>
       <c r="P855" s="62" t="n"/>
       <c r="Q855" s="62" t="n"/>
+      <c r="R855" s="88" t="n"/>
     </row>
     <row r="856" ht="12.75" customHeight="1" s="70">
       <c r="F856" s="66" t="n"/>
@@ -12012,6 +12881,7 @@
       <c r="O856" s="69" t="n"/>
       <c r="P856" s="62" t="n"/>
       <c r="Q856" s="62" t="n"/>
+      <c r="R856" s="88" t="n"/>
     </row>
     <row r="857" ht="12.75" customHeight="1" s="70">
       <c r="F857" s="66" t="n"/>
@@ -12022,6 +12892,7 @@
       <c r="O857" s="69" t="n"/>
       <c r="P857" s="62" t="n"/>
       <c r="Q857" s="62" t="n"/>
+      <c r="R857" s="88" t="n"/>
     </row>
     <row r="858" ht="12.75" customHeight="1" s="70">
       <c r="F858" s="66" t="n"/>
@@ -12032,6 +12903,7 @@
       <c r="O858" s="69" t="n"/>
       <c r="P858" s="62" t="n"/>
       <c r="Q858" s="62" t="n"/>
+      <c r="R858" s="88" t="n"/>
     </row>
     <row r="859" ht="12.75" customHeight="1" s="70">
       <c r="F859" s="66" t="n"/>
@@ -12042,6 +12914,7 @@
       <c r="O859" s="69" t="n"/>
       <c r="P859" s="62" t="n"/>
       <c r="Q859" s="62" t="n"/>
+      <c r="R859" s="88" t="n"/>
     </row>
     <row r="860" ht="12.75" customHeight="1" s="70">
       <c r="F860" s="66" t="n"/>
@@ -12052,6 +12925,7 @@
       <c r="O860" s="69" t="n"/>
       <c r="P860" s="62" t="n"/>
       <c r="Q860" s="62" t="n"/>
+      <c r="R860" s="88" t="n"/>
     </row>
     <row r="861" ht="12.75" customHeight="1" s="70">
       <c r="F861" s="66" t="n"/>
@@ -12062,6 +12936,7 @@
       <c r="O861" s="69" t="n"/>
       <c r="P861" s="62" t="n"/>
       <c r="Q861" s="62" t="n"/>
+      <c r="R861" s="88" t="n"/>
     </row>
     <row r="862" ht="12.75" customHeight="1" s="70">
       <c r="F862" s="66" t="n"/>
@@ -12072,6 +12947,7 @@
       <c r="O862" s="69" t="n"/>
       <c r="P862" s="62" t="n"/>
       <c r="Q862" s="62" t="n"/>
+      <c r="R862" s="88" t="n"/>
     </row>
     <row r="863" ht="12.75" customHeight="1" s="70">
       <c r="F863" s="66" t="n"/>
@@ -12082,6 +12958,7 @@
       <c r="O863" s="69" t="n"/>
       <c r="P863" s="62" t="n"/>
       <c r="Q863" s="62" t="n"/>
+      <c r="R863" s="88" t="n"/>
     </row>
     <row r="864" ht="12.75" customHeight="1" s="70">
       <c r="F864" s="66" t="n"/>
@@ -12092,6 +12969,7 @@
       <c r="O864" s="69" t="n"/>
       <c r="P864" s="62" t="n"/>
       <c r="Q864" s="62" t="n"/>
+      <c r="R864" s="88" t="n"/>
     </row>
     <row r="865" ht="12.75" customHeight="1" s="70">
       <c r="F865" s="66" t="n"/>
@@ -12102,6 +12980,7 @@
       <c r="O865" s="69" t="n"/>
       <c r="P865" s="62" t="n"/>
       <c r="Q865" s="62" t="n"/>
+      <c r="R865" s="88" t="n"/>
     </row>
     <row r="866" ht="12.75" customHeight="1" s="70">
       <c r="F866" s="66" t="n"/>
@@ -12112,6 +12991,7 @@
       <c r="O866" s="69" t="n"/>
       <c r="P866" s="62" t="n"/>
       <c r="Q866" s="62" t="n"/>
+      <c r="R866" s="88" t="n"/>
     </row>
     <row r="867" ht="12.75" customHeight="1" s="70">
       <c r="F867" s="66" t="n"/>
@@ -12122,6 +13002,7 @@
       <c r="O867" s="69" t="n"/>
       <c r="P867" s="62" t="n"/>
       <c r="Q867" s="62" t="n"/>
+      <c r="R867" s="88" t="n"/>
     </row>
     <row r="868" ht="12.75" customHeight="1" s="70">
       <c r="F868" s="66" t="n"/>
@@ -12132,6 +13013,7 @@
       <c r="O868" s="69" t="n"/>
       <c r="P868" s="62" t="n"/>
       <c r="Q868" s="62" t="n"/>
+      <c r="R868" s="88" t="n"/>
     </row>
     <row r="869" ht="12.75" customHeight="1" s="70">
       <c r="F869" s="66" t="n"/>
@@ -12142,6 +13024,7 @@
       <c r="O869" s="69" t="n"/>
       <c r="P869" s="62" t="n"/>
       <c r="Q869" s="62" t="n"/>
+      <c r="R869" s="88" t="n"/>
     </row>
     <row r="870" ht="12.75" customHeight="1" s="70">
       <c r="F870" s="66" t="n"/>
@@ -12152,6 +13035,7 @@
       <c r="O870" s="69" t="n"/>
       <c r="P870" s="62" t="n"/>
       <c r="Q870" s="62" t="n"/>
+      <c r="R870" s="88" t="n"/>
     </row>
     <row r="871" ht="12.75" customHeight="1" s="70">
       <c r="F871" s="66" t="n"/>
@@ -12162,6 +13046,7 @@
       <c r="O871" s="69" t="n"/>
       <c r="P871" s="62" t="n"/>
       <c r="Q871" s="62" t="n"/>
+      <c r="R871" s="88" t="n"/>
     </row>
     <row r="872" ht="12.75" customHeight="1" s="70">
       <c r="F872" s="66" t="n"/>
@@ -12172,6 +13057,7 @@
       <c r="O872" s="69" t="n"/>
       <c r="P872" s="62" t="n"/>
       <c r="Q872" s="62" t="n"/>
+      <c r="R872" s="88" t="n"/>
     </row>
     <row r="873" ht="12.75" customHeight="1" s="70">
       <c r="F873" s="66" t="n"/>
@@ -12182,6 +13068,7 @@
       <c r="O873" s="69" t="n"/>
       <c r="P873" s="62" t="n"/>
       <c r="Q873" s="62" t="n"/>
+      <c r="R873" s="88" t="n"/>
     </row>
     <row r="874" ht="12.75" customHeight="1" s="70">
       <c r="F874" s="66" t="n"/>
@@ -12192,6 +13079,7 @@
       <c r="O874" s="69" t="n"/>
       <c r="P874" s="62" t="n"/>
       <c r="Q874" s="62" t="n"/>
+      <c r="R874" s="88" t="n"/>
     </row>
     <row r="875" ht="12.75" customHeight="1" s="70">
       <c r="F875" s="66" t="n"/>
@@ -12202,6 +13090,7 @@
       <c r="O875" s="69" t="n"/>
       <c r="P875" s="62" t="n"/>
       <c r="Q875" s="62" t="n"/>
+      <c r="R875" s="88" t="n"/>
     </row>
     <row r="876" ht="12.75" customHeight="1" s="70">
       <c r="F876" s="66" t="n"/>
@@ -12212,6 +13101,7 @@
       <c r="O876" s="69" t="n"/>
       <c r="P876" s="62" t="n"/>
       <c r="Q876" s="62" t="n"/>
+      <c r="R876" s="88" t="n"/>
     </row>
     <row r="877" ht="12.75" customHeight="1" s="70">
       <c r="F877" s="66" t="n"/>
@@ -12222,6 +13112,7 @@
       <c r="O877" s="69" t="n"/>
       <c r="P877" s="62" t="n"/>
       <c r="Q877" s="62" t="n"/>
+      <c r="R877" s="88" t="n"/>
     </row>
     <row r="878" ht="12.75" customHeight="1" s="70">
       <c r="F878" s="66" t="n"/>
@@ -12232,6 +13123,7 @@
       <c r="O878" s="69" t="n"/>
       <c r="P878" s="62" t="n"/>
       <c r="Q878" s="62" t="n"/>
+      <c r="R878" s="88" t="n"/>
     </row>
     <row r="879" ht="12.75" customHeight="1" s="70">
       <c r="F879" s="66" t="n"/>
@@ -12242,6 +13134,7 @@
       <c r="O879" s="69" t="n"/>
       <c r="P879" s="62" t="n"/>
       <c r="Q879" s="62" t="n"/>
+      <c r="R879" s="88" t="n"/>
     </row>
     <row r="880" ht="12.75" customHeight="1" s="70">
       <c r="F880" s="66" t="n"/>
@@ -12252,6 +13145,7 @@
       <c r="O880" s="69" t="n"/>
       <c r="P880" s="62" t="n"/>
       <c r="Q880" s="62" t="n"/>
+      <c r="R880" s="88" t="n"/>
     </row>
     <row r="881" ht="12.75" customHeight="1" s="70">
       <c r="F881" s="66" t="n"/>
@@ -12262,6 +13156,7 @@
       <c r="O881" s="69" t="n"/>
       <c r="P881" s="62" t="n"/>
       <c r="Q881" s="62" t="n"/>
+      <c r="R881" s="88" t="n"/>
     </row>
     <row r="882" ht="12.75" customHeight="1" s="70">
       <c r="F882" s="66" t="n"/>
@@ -12272,6 +13167,7 @@
       <c r="O882" s="69" t="n"/>
       <c r="P882" s="62" t="n"/>
       <c r="Q882" s="62" t="n"/>
+      <c r="R882" s="88" t="n"/>
     </row>
     <row r="883" ht="12.75" customHeight="1" s="70">
       <c r="F883" s="66" t="n"/>
@@ -12282,6 +13178,7 @@
       <c r="O883" s="69" t="n"/>
       <c r="P883" s="62" t="n"/>
       <c r="Q883" s="62" t="n"/>
+      <c r="R883" s="88" t="n"/>
     </row>
     <row r="884" ht="12.75" customHeight="1" s="70">
       <c r="F884" s="66" t="n"/>
@@ -12292,6 +13189,7 @@
       <c r="O884" s="69" t="n"/>
       <c r="P884" s="62" t="n"/>
       <c r="Q884" s="62" t="n"/>
+      <c r="R884" s="88" t="n"/>
     </row>
     <row r="885" ht="12.75" customHeight="1" s="70">
       <c r="F885" s="66" t="n"/>
@@ -12302,6 +13200,7 @@
       <c r="O885" s="69" t="n"/>
       <c r="P885" s="62" t="n"/>
       <c r="Q885" s="62" t="n"/>
+      <c r="R885" s="88" t="n"/>
     </row>
     <row r="886" ht="12.75" customHeight="1" s="70">
       <c r="F886" s="66" t="n"/>
@@ -12312,6 +13211,7 @@
       <c r="O886" s="69" t="n"/>
       <c r="P886" s="62" t="n"/>
       <c r="Q886" s="62" t="n"/>
+      <c r="R886" s="88" t="n"/>
     </row>
     <row r="887" ht="12.75" customHeight="1" s="70">
       <c r="F887" s="66" t="n"/>
@@ -12322,6 +13222,7 @@
       <c r="O887" s="69" t="n"/>
       <c r="P887" s="62" t="n"/>
       <c r="Q887" s="62" t="n"/>
+      <c r="R887" s="88" t="n"/>
     </row>
     <row r="888" ht="12.75" customHeight="1" s="70">
       <c r="F888" s="66" t="n"/>
@@ -12332,6 +13233,7 @@
       <c r="O888" s="69" t="n"/>
       <c r="P888" s="62" t="n"/>
       <c r="Q888" s="62" t="n"/>
+      <c r="R888" s="88" t="n"/>
     </row>
     <row r="889" ht="12.75" customHeight="1" s="70">
       <c r="F889" s="66" t="n"/>
@@ -12342,6 +13244,7 @@
       <c r="O889" s="69" t="n"/>
       <c r="P889" s="62" t="n"/>
       <c r="Q889" s="62" t="n"/>
+      <c r="R889" s="88" t="n"/>
     </row>
     <row r="890" ht="12.75" customHeight="1" s="70">
       <c r="F890" s="66" t="n"/>
@@ -12352,6 +13255,7 @@
       <c r="O890" s="69" t="n"/>
       <c r="P890" s="62" t="n"/>
       <c r="Q890" s="62" t="n"/>
+      <c r="R890" s="88" t="n"/>
     </row>
     <row r="891" ht="12.75" customHeight="1" s="70">
       <c r="F891" s="66" t="n"/>
@@ -12362,6 +13266,7 @@
       <c r="O891" s="69" t="n"/>
       <c r="P891" s="62" t="n"/>
       <c r="Q891" s="62" t="n"/>
+      <c r="R891" s="88" t="n"/>
     </row>
     <row r="892" ht="12.75" customHeight="1" s="70">
       <c r="F892" s="66" t="n"/>
@@ -12372,6 +13277,7 @@
       <c r="O892" s="69" t="n"/>
       <c r="P892" s="62" t="n"/>
       <c r="Q892" s="62" t="n"/>
+      <c r="R892" s="88" t="n"/>
     </row>
     <row r="893" ht="12.75" customHeight="1" s="70">
       <c r="F893" s="66" t="n"/>
@@ -12382,6 +13288,7 @@
       <c r="O893" s="69" t="n"/>
       <c r="P893" s="62" t="n"/>
       <c r="Q893" s="62" t="n"/>
+      <c r="R893" s="88" t="n"/>
     </row>
     <row r="894" ht="12.75" customHeight="1" s="70">
       <c r="F894" s="66" t="n"/>
@@ -12392,6 +13299,7 @@
       <c r="O894" s="69" t="n"/>
       <c r="P894" s="62" t="n"/>
       <c r="Q894" s="62" t="n"/>
+      <c r="R894" s="88" t="n"/>
     </row>
     <row r="895" ht="12.75" customHeight="1" s="70">
       <c r="F895" s="66" t="n"/>
@@ -12402,6 +13310,7 @@
       <c r="O895" s="69" t="n"/>
       <c r="P895" s="62" t="n"/>
       <c r="Q895" s="62" t="n"/>
+      <c r="R895" s="88" t="n"/>
     </row>
     <row r="896" ht="12.75" customHeight="1" s="70">
       <c r="F896" s="66" t="n"/>
@@ -12412,6 +13321,7 @@
       <c r="O896" s="69" t="n"/>
       <c r="P896" s="62" t="n"/>
       <c r="Q896" s="62" t="n"/>
+      <c r="R896" s="88" t="n"/>
     </row>
     <row r="897" ht="12.75" customHeight="1" s="70">
       <c r="F897" s="66" t="n"/>
@@ -12422,6 +13332,7 @@
       <c r="O897" s="69" t="n"/>
       <c r="P897" s="62" t="n"/>
       <c r="Q897" s="62" t="n"/>
+      <c r="R897" s="88" t="n"/>
     </row>
     <row r="898" ht="12.75" customHeight="1" s="70">
       <c r="F898" s="66" t="n"/>
@@ -12432,6 +13343,7 @@
       <c r="O898" s="69" t="n"/>
       <c r="P898" s="62" t="n"/>
       <c r="Q898" s="62" t="n"/>
+      <c r="R898" s="88" t="n"/>
     </row>
     <row r="899" ht="12.75" customHeight="1" s="70">
       <c r="F899" s="66" t="n"/>
@@ -12442,6 +13354,7 @@
       <c r="O899" s="69" t="n"/>
       <c r="P899" s="62" t="n"/>
       <c r="Q899" s="62" t="n"/>
+      <c r="R899" s="88" t="n"/>
     </row>
     <row r="900" ht="12.75" customHeight="1" s="70">
       <c r="F900" s="66" t="n"/>
@@ -12452,6 +13365,7 @@
       <c r="O900" s="69" t="n"/>
       <c r="P900" s="62" t="n"/>
       <c r="Q900" s="62" t="n"/>
+      <c r="R900" s="88" t="n"/>
     </row>
     <row r="901" ht="12.75" customHeight="1" s="70">
       <c r="F901" s="66" t="n"/>
@@ -12462,6 +13376,7 @@
       <c r="O901" s="69" t="n"/>
       <c r="P901" s="62" t="n"/>
       <c r="Q901" s="62" t="n"/>
+      <c r="R901" s="88" t="n"/>
     </row>
     <row r="902" ht="12.75" customHeight="1" s="70">
       <c r="F902" s="66" t="n"/>
@@ -12472,6 +13387,7 @@
       <c r="O902" s="69" t="n"/>
       <c r="P902" s="62" t="n"/>
       <c r="Q902" s="62" t="n"/>
+      <c r="R902" s="88" t="n"/>
     </row>
     <row r="903" ht="12.75" customHeight="1" s="70">
       <c r="F903" s="66" t="n"/>
@@ -12482,6 +13398,7 @@
       <c r="O903" s="69" t="n"/>
       <c r="P903" s="62" t="n"/>
       <c r="Q903" s="62" t="n"/>
+      <c r="R903" s="88" t="n"/>
     </row>
     <row r="904" ht="12.75" customHeight="1" s="70">
       <c r="F904" s="66" t="n"/>
@@ -12492,6 +13409,7 @@
       <c r="O904" s="69" t="n"/>
       <c r="P904" s="62" t="n"/>
       <c r="Q904" s="62" t="n"/>
+      <c r="R904" s="88" t="n"/>
     </row>
     <row r="905" ht="12.75" customHeight="1" s="70">
       <c r="F905" s="66" t="n"/>
@@ -12502,6 +13420,7 @@
       <c r="O905" s="69" t="n"/>
       <c r="P905" s="62" t="n"/>
       <c r="Q905" s="62" t="n"/>
+      <c r="R905" s="88" t="n"/>
     </row>
     <row r="906" ht="12.75" customHeight="1" s="70">
       <c r="F906" s="66" t="n"/>
@@ -12512,6 +13431,7 @@
       <c r="O906" s="69" t="n"/>
       <c r="P906" s="62" t="n"/>
       <c r="Q906" s="62" t="n"/>
+      <c r="R906" s="88" t="n"/>
     </row>
     <row r="907" ht="12.75" customHeight="1" s="70">
       <c r="F907" s="66" t="n"/>
@@ -12522,6 +13442,7 @@
       <c r="O907" s="69" t="n"/>
       <c r="P907" s="62" t="n"/>
       <c r="Q907" s="62" t="n"/>
+      <c r="R907" s="88" t="n"/>
     </row>
     <row r="908" ht="12.75" customHeight="1" s="70">
       <c r="F908" s="66" t="n"/>
@@ -12532,6 +13453,7 @@
       <c r="O908" s="69" t="n"/>
       <c r="P908" s="62" t="n"/>
       <c r="Q908" s="62" t="n"/>
+      <c r="R908" s="88" t="n"/>
     </row>
     <row r="909" ht="12.75" customHeight="1" s="70">
       <c r="F909" s="66" t="n"/>
@@ -12542,6 +13464,7 @@
       <c r="O909" s="69" t="n"/>
       <c r="P909" s="62" t="n"/>
       <c r="Q909" s="62" t="n"/>
+      <c r="R909" s="88" t="n"/>
     </row>
     <row r="910" ht="12.75" customHeight="1" s="70">
       <c r="F910" s="66" t="n"/>
@@ -12552,6 +13475,7 @@
       <c r="O910" s="69" t="n"/>
       <c r="P910" s="62" t="n"/>
       <c r="Q910" s="62" t="n"/>
+      <c r="R910" s="88" t="n"/>
     </row>
     <row r="911" ht="12.75" customHeight="1" s="70">
       <c r="F911" s="66" t="n"/>
@@ -12562,6 +13486,7 @@
       <c r="O911" s="69" t="n"/>
       <c r="P911" s="62" t="n"/>
       <c r="Q911" s="62" t="n"/>
+      <c r="R911" s="88" t="n"/>
     </row>
     <row r="912" ht="12.75" customHeight="1" s="70">
       <c r="F912" s="66" t="n"/>
@@ -12572,6 +13497,7 @@
       <c r="O912" s="69" t="n"/>
       <c r="P912" s="62" t="n"/>
       <c r="Q912" s="62" t="n"/>
+      <c r="R912" s="88" t="n"/>
     </row>
     <row r="913" ht="12.75" customHeight="1" s="70">
       <c r="F913" s="66" t="n"/>
@@ -12582,6 +13508,7 @@
       <c r="O913" s="69" t="n"/>
       <c r="P913" s="62" t="n"/>
       <c r="Q913" s="62" t="n"/>
+      <c r="R913" s="88" t="n"/>
     </row>
     <row r="914" ht="12.75" customHeight="1" s="70">
       <c r="F914" s="66" t="n"/>
@@ -12592,6 +13519,7 @@
       <c r="O914" s="69" t="n"/>
       <c r="P914" s="62" t="n"/>
       <c r="Q914" s="62" t="n"/>
+      <c r="R914" s="88" t="n"/>
     </row>
     <row r="915" ht="12.75" customHeight="1" s="70">
       <c r="F915" s="66" t="n"/>
@@ -12602,6 +13530,7 @@
       <c r="O915" s="69" t="n"/>
       <c r="P915" s="62" t="n"/>
       <c r="Q915" s="62" t="n"/>
+      <c r="R915" s="88" t="n"/>
     </row>
     <row r="916" ht="12.75" customHeight="1" s="70">
       <c r="F916" s="66" t="n"/>
@@ -12612,6 +13541,7 @@
       <c r="O916" s="69" t="n"/>
       <c r="P916" s="62" t="n"/>
       <c r="Q916" s="62" t="n"/>
+      <c r="R916" s="88" t="n"/>
     </row>
     <row r="917" ht="12.75" customHeight="1" s="70">
       <c r="F917" s="66" t="n"/>
@@ -12622,6 +13552,7 @@
       <c r="O917" s="69" t="n"/>
       <c r="P917" s="62" t="n"/>
       <c r="Q917" s="62" t="n"/>
+      <c r="R917" s="88" t="n"/>
     </row>
     <row r="918" ht="12.75" customHeight="1" s="70">
       <c r="F918" s="66" t="n"/>
@@ -12632,6 +13563,7 @@
       <c r="O918" s="69" t="n"/>
       <c r="P918" s="62" t="n"/>
       <c r="Q918" s="62" t="n"/>
+      <c r="R918" s="88" t="n"/>
     </row>
     <row r="919" ht="12.75" customHeight="1" s="70">
       <c r="F919" s="66" t="n"/>
@@ -12642,6 +13574,7 @@
       <c r="O919" s="69" t="n"/>
       <c r="P919" s="62" t="n"/>
       <c r="Q919" s="62" t="n"/>
+      <c r="R919" s="88" t="n"/>
     </row>
     <row r="920" ht="12.75" customHeight="1" s="70">
       <c r="F920" s="66" t="n"/>
@@ -12652,6 +13585,7 @@
       <c r="O920" s="69" t="n"/>
       <c r="P920" s="62" t="n"/>
       <c r="Q920" s="62" t="n"/>
+      <c r="R920" s="88" t="n"/>
     </row>
     <row r="921" ht="12.75" customHeight="1" s="70">
       <c r="F921" s="66" t="n"/>
@@ -12662,6 +13596,7 @@
       <c r="O921" s="69" t="n"/>
       <c r="P921" s="62" t="n"/>
       <c r="Q921" s="62" t="n"/>
+      <c r="R921" s="88" t="n"/>
     </row>
     <row r="922" ht="12.75" customHeight="1" s="70">
       <c r="F922" s="66" t="n"/>
@@ -12672,6 +13607,7 @@
       <c r="O922" s="69" t="n"/>
       <c r="P922" s="62" t="n"/>
       <c r="Q922" s="62" t="n"/>
+      <c r="R922" s="88" t="n"/>
     </row>
     <row r="923" ht="12.75" customHeight="1" s="70">
       <c r="F923" s="66" t="n"/>
@@ -12682,6 +13618,7 @@
       <c r="O923" s="69" t="n"/>
       <c r="P923" s="62" t="n"/>
       <c r="Q923" s="62" t="n"/>
+      <c r="R923" s="88" t="n"/>
     </row>
     <row r="924" ht="12.75" customHeight="1" s="70">
       <c r="F924" s="66" t="n"/>
@@ -12692,6 +13629,7 @@
       <c r="O924" s="69" t="n"/>
       <c r="P924" s="62" t="n"/>
       <c r="Q924" s="62" t="n"/>
+      <c r="R924" s="88" t="n"/>
     </row>
     <row r="925" ht="12.75" customHeight="1" s="70">
       <c r="F925" s="66" t="n"/>
@@ -12702,6 +13640,7 @@
       <c r="O925" s="69" t="n"/>
       <c r="P925" s="62" t="n"/>
       <c r="Q925" s="62" t="n"/>
+      <c r="R925" s="88" t="n"/>
     </row>
     <row r="926" ht="12.75" customHeight="1" s="70">
       <c r="F926" s="66" t="n"/>
@@ -12712,6 +13651,7 @@
       <c r="O926" s="69" t="n"/>
       <c r="P926" s="62" t="n"/>
       <c r="Q926" s="62" t="n"/>
+      <c r="R926" s="88" t="n"/>
     </row>
     <row r="927" ht="12.75" customHeight="1" s="70">
       <c r="F927" s="66" t="n"/>
@@ -12722,6 +13662,7 @@
       <c r="O927" s="69" t="n"/>
       <c r="P927" s="62" t="n"/>
       <c r="Q927" s="62" t="n"/>
+      <c r="R927" s="88" t="n"/>
     </row>
     <row r="928" ht="12.75" customHeight="1" s="70">
       <c r="F928" s="66" t="n"/>
@@ -12732,6 +13673,7 @@
       <c r="O928" s="69" t="n"/>
       <c r="P928" s="62" t="n"/>
       <c r="Q928" s="62" t="n"/>
+      <c r="R928" s="88" t="n"/>
     </row>
     <row r="929" ht="12.75" customHeight="1" s="70">
       <c r="F929" s="66" t="n"/>
@@ -12742,6 +13684,7 @@
       <c r="O929" s="69" t="n"/>
       <c r="P929" s="62" t="n"/>
       <c r="Q929" s="62" t="n"/>
+      <c r="R929" s="88" t="n"/>
     </row>
     <row r="930" ht="12.75" customHeight="1" s="70">
       <c r="F930" s="66" t="n"/>
@@ -12752,6 +13695,7 @@
       <c r="O930" s="69" t="n"/>
       <c r="P930" s="62" t="n"/>
       <c r="Q930" s="62" t="n"/>
+      <c r="R930" s="88" t="n"/>
     </row>
     <row r="931" ht="12.75" customHeight="1" s="70">
       <c r="F931" s="66" t="n"/>
@@ -12762,6 +13706,7 @@
       <c r="O931" s="69" t="n"/>
       <c r="P931" s="62" t="n"/>
       <c r="Q931" s="62" t="n"/>
+      <c r="R931" s="88" t="n"/>
     </row>
     <row r="932" ht="12.75" customHeight="1" s="70">
       <c r="F932" s="66" t="n"/>
@@ -12772,6 +13717,7 @@
       <c r="O932" s="69" t="n"/>
       <c r="P932" s="62" t="n"/>
       <c r="Q932" s="62" t="n"/>
+      <c r="R932" s="88" t="n"/>
     </row>
     <row r="933" ht="12.75" customHeight="1" s="70">
       <c r="F933" s="66" t="n"/>
@@ -12782,6 +13728,7 @@
       <c r="O933" s="69" t="n"/>
       <c r="P933" s="62" t="n"/>
       <c r="Q933" s="62" t="n"/>
+      <c r="R933" s="88" t="n"/>
     </row>
     <row r="934" ht="12.75" customHeight="1" s="70">
       <c r="F934" s="66" t="n"/>
@@ -12792,6 +13739,7 @@
       <c r="O934" s="69" t="n"/>
       <c r="P934" s="62" t="n"/>
       <c r="Q934" s="62" t="n"/>
+      <c r="R934" s="88" t="n"/>
     </row>
     <row r="935" ht="12.75" customHeight="1" s="70">
       <c r="F935" s="66" t="n"/>
@@ -12802,6 +13750,7 @@
       <c r="O935" s="69" t="n"/>
       <c r="P935" s="62" t="n"/>
       <c r="Q935" s="62" t="n"/>
+      <c r="R935" s="88" t="n"/>
     </row>
     <row r="936" ht="12.75" customHeight="1" s="70">
       <c r="F936" s="66" t="n"/>
@@ -12812,6 +13761,7 @@
       <c r="O936" s="69" t="n"/>
       <c r="P936" s="62" t="n"/>
       <c r="Q936" s="62" t="n"/>
+      <c r="R936" s="88" t="n"/>
     </row>
     <row r="937" ht="12.75" customHeight="1" s="70">
       <c r="F937" s="66" t="n"/>
@@ -12822,6 +13772,7 @@
       <c r="O937" s="69" t="n"/>
       <c r="P937" s="62" t="n"/>
       <c r="Q937" s="62" t="n"/>
+      <c r="R937" s="88" t="n"/>
     </row>
     <row r="938" ht="12.75" customHeight="1" s="70">
       <c r="F938" s="66" t="n"/>
@@ -12832,6 +13783,7 @@
       <c r="O938" s="69" t="n"/>
       <c r="P938" s="62" t="n"/>
       <c r="Q938" s="62" t="n"/>
+      <c r="R938" s="88" t="n"/>
     </row>
     <row r="939" ht="12.75" customHeight="1" s="70">
       <c r="F939" s="66" t="n"/>
@@ -12842,6 +13794,7 @@
       <c r="O939" s="69" t="n"/>
       <c r="P939" s="62" t="n"/>
       <c r="Q939" s="62" t="n"/>
+      <c r="R939" s="88" t="n"/>
     </row>
     <row r="940" ht="12.75" customHeight="1" s="70">
       <c r="F940" s="66" t="n"/>
@@ -12852,6 +13805,7 @@
       <c r="O940" s="69" t="n"/>
       <c r="P940" s="62" t="n"/>
       <c r="Q940" s="62" t="n"/>
+      <c r="R940" s="88" t="n"/>
     </row>
     <row r="941" ht="12.75" customHeight="1" s="70">
       <c r="F941" s="66" t="n"/>
@@ -12862,6 +13816,7 @@
       <c r="O941" s="69" t="n"/>
       <c r="P941" s="62" t="n"/>
       <c r="Q941" s="62" t="n"/>
+      <c r="R941" s="88" t="n"/>
     </row>
     <row r="942" ht="12.75" customHeight="1" s="70">
       <c r="F942" s="66" t="n"/>
@@ -12872,6 +13827,7 @@
       <c r="O942" s="69" t="n"/>
       <c r="P942" s="62" t="n"/>
       <c r="Q942" s="62" t="n"/>
+      <c r="R942" s="88" t="n"/>
     </row>
     <row r="943" ht="12.75" customHeight="1" s="70">
       <c r="F943" s="66" t="n"/>
@@ -12882,6 +13838,7 @@
       <c r="O943" s="69" t="n"/>
       <c r="P943" s="62" t="n"/>
       <c r="Q943" s="62" t="n"/>
+      <c r="R943" s="88" t="n"/>
     </row>
     <row r="944" ht="12.75" customHeight="1" s="70">
       <c r="F944" s="66" t="n"/>
@@ -12892,6 +13849,7 @@
       <c r="O944" s="69" t="n"/>
       <c r="P944" s="62" t="n"/>
       <c r="Q944" s="62" t="n"/>
+      <c r="R944" s="88" t="n"/>
     </row>
     <row r="945" ht="12.75" customHeight="1" s="70">
       <c r="F945" s="66" t="n"/>
@@ -12902,6 +13860,7 @@
       <c r="O945" s="69" t="n"/>
       <c r="P945" s="62" t="n"/>
       <c r="Q945" s="62" t="n"/>
+      <c r="R945" s="88" t="n"/>
     </row>
     <row r="946" ht="12.75" customHeight="1" s="70">
       <c r="F946" s="66" t="n"/>
@@ -12912,6 +13871,7 @@
       <c r="O946" s="69" t="n"/>
       <c r="P946" s="62" t="n"/>
       <c r="Q946" s="62" t="n"/>
+      <c r="R946" s="88" t="n"/>
     </row>
     <row r="947" ht="12.75" customHeight="1" s="70">
       <c r="F947" s="66" t="n"/>
@@ -12922,6 +13882,7 @@
       <c r="O947" s="69" t="n"/>
       <c r="P947" s="62" t="n"/>
       <c r="Q947" s="62" t="n"/>
+      <c r="R947" s="88" t="n"/>
     </row>
     <row r="948" ht="12.75" customHeight="1" s="70">
       <c r="F948" s="66" t="n"/>
@@ -12932,6 +13893,7 @@
       <c r="O948" s="69" t="n"/>
       <c r="P948" s="62" t="n"/>
       <c r="Q948" s="62" t="n"/>
+      <c r="R948" s="88" t="n"/>
     </row>
     <row r="949" ht="12.75" customHeight="1" s="70">
       <c r="F949" s="66" t="n"/>
@@ -12942,6 +13904,7 @@
       <c r="O949" s="69" t="n"/>
       <c r="P949" s="62" t="n"/>
       <c r="Q949" s="62" t="n"/>
+      <c r="R949" s="88" t="n"/>
     </row>
     <row r="950" ht="12.75" customHeight="1" s="70">
       <c r="F950" s="66" t="n"/>
@@ -12952,6 +13915,7 @@
       <c r="O950" s="69" t="n"/>
       <c r="P950" s="62" t="n"/>
       <c r="Q950" s="62" t="n"/>
+      <c r="R950" s="88" t="n"/>
     </row>
     <row r="951" ht="12.75" customHeight="1" s="70">
       <c r="F951" s="66" t="n"/>
@@ -12962,6 +13926,7 @@
       <c r="O951" s="69" t="n"/>
       <c r="P951" s="62" t="n"/>
       <c r="Q951" s="62" t="n"/>
+      <c r="R951" s="88" t="n"/>
     </row>
     <row r="952" ht="12.75" customHeight="1" s="70">
       <c r="F952" s="66" t="n"/>
@@ -12972,6 +13937,7 @@
       <c r="O952" s="69" t="n"/>
       <c r="P952" s="62" t="n"/>
       <c r="Q952" s="62" t="n"/>
+      <c r="R952" s="88" t="n"/>
     </row>
     <row r="953" ht="12.75" customHeight="1" s="70">
       <c r="F953" s="66" t="n"/>
@@ -12982,6 +13948,7 @@
       <c r="O953" s="69" t="n"/>
       <c r="P953" s="62" t="n"/>
       <c r="Q953" s="62" t="n"/>
+      <c r="R953" s="88" t="n"/>
     </row>
     <row r="954" ht="12.75" customHeight="1" s="70">
       <c r="F954" s="66" t="n"/>
@@ -12992,6 +13959,7 @@
       <c r="O954" s="69" t="n"/>
       <c r="P954" s="62" t="n"/>
       <c r="Q954" s="62" t="n"/>
+      <c r="R954" s="88" t="n"/>
     </row>
     <row r="955" ht="12.75" customHeight="1" s="70">
       <c r="F955" s="66" t="n"/>
@@ -13002,6 +13970,7 @@
       <c r="O955" s="69" t="n"/>
       <c r="P955" s="62" t="n"/>
       <c r="Q955" s="62" t="n"/>
+      <c r="R955" s="88" t="n"/>
     </row>
     <row r="956" ht="12.75" customHeight="1" s="70">
       <c r="F956" s="66" t="n"/>
@@ -13012,6 +13981,7 @@
       <c r="O956" s="69" t="n"/>
       <c r="P956" s="62" t="n"/>
       <c r="Q956" s="62" t="n"/>
+      <c r="R956" s="88" t="n"/>
     </row>
     <row r="957" ht="12.75" customHeight="1" s="70">
       <c r="F957" s="66" t="n"/>
@@ -13022,6 +13992,7 @@
       <c r="O957" s="69" t="n"/>
       <c r="P957" s="62" t="n"/>
       <c r="Q957" s="62" t="n"/>
+      <c r="R957" s="88" t="n"/>
     </row>
     <row r="958" ht="12.75" customHeight="1" s="70">
       <c r="F958" s="66" t="n"/>
@@ -13032,6 +14003,7 @@
       <c r="O958" s="69" t="n"/>
       <c r="P958" s="62" t="n"/>
       <c r="Q958" s="62" t="n"/>
+      <c r="R958" s="88" t="n"/>
     </row>
     <row r="959" ht="12.75" customHeight="1" s="70">
       <c r="F959" s="66" t="n"/>
@@ -13042,6 +14014,7 @@
       <c r="O959" s="69" t="n"/>
       <c r="P959" s="62" t="n"/>
       <c r="Q959" s="62" t="n"/>
+      <c r="R959" s="88" t="n"/>
     </row>
     <row r="960" ht="12.75" customHeight="1" s="70">
       <c r="F960" s="66" t="n"/>
@@ -13052,6 +14025,7 @@
       <c r="O960" s="69" t="n"/>
       <c r="P960" s="62" t="n"/>
       <c r="Q960" s="62" t="n"/>
+      <c r="R960" s="88" t="n"/>
     </row>
     <row r="961" ht="12.75" customHeight="1" s="70">
       <c r="F961" s="66" t="n"/>
@@ -13062,6 +14036,7 @@
       <c r="O961" s="69" t="n"/>
       <c r="P961" s="62" t="n"/>
       <c r="Q961" s="62" t="n"/>
+      <c r="R961" s="88" t="n"/>
     </row>
     <row r="962" ht="12.75" customHeight="1" s="70">
       <c r="F962" s="66" t="n"/>
@@ -13072,6 +14047,7 @@
       <c r="O962" s="69" t="n"/>
       <c r="P962" s="62" t="n"/>
       <c r="Q962" s="62" t="n"/>
+      <c r="R962" s="88" t="n"/>
     </row>
     <row r="963" ht="12.75" customHeight="1" s="70">
       <c r="F963" s="66" t="n"/>
@@ -13082,6 +14058,7 @@
       <c r="O963" s="69" t="n"/>
       <c r="P963" s="62" t="n"/>
       <c r="Q963" s="62" t="n"/>
+      <c r="R963" s="88" t="n"/>
     </row>
     <row r="964" ht="12.75" customHeight="1" s="70">
       <c r="F964" s="66" t="n"/>
@@ -13092,6 +14069,7 @@
       <c r="O964" s="69" t="n"/>
       <c r="P964" s="62" t="n"/>
       <c r="Q964" s="62" t="n"/>
+      <c r="R964" s="88" t="n"/>
     </row>
     <row r="965" ht="12.75" customHeight="1" s="70">
       <c r="F965" s="66" t="n"/>
@@ -13102,6 +14080,7 @@
       <c r="O965" s="69" t="n"/>
       <c r="P965" s="62" t="n"/>
       <c r="Q965" s="62" t="n"/>
+      <c r="R965" s="88" t="n"/>
     </row>
     <row r="966" ht="12.75" customHeight="1" s="70">
       <c r="F966" s="66" t="n"/>
@@ -13112,6 +14091,7 @@
       <c r="O966" s="69" t="n"/>
       <c r="P966" s="62" t="n"/>
       <c r="Q966" s="62" t="n"/>
+      <c r="R966" s="88" t="n"/>
     </row>
     <row r="967" ht="12.75" customHeight="1" s="70">
       <c r="F967" s="66" t="n"/>
@@ -13122,6 +14102,7 @@
       <c r="O967" s="69" t="n"/>
       <c r="P967" s="62" t="n"/>
       <c r="Q967" s="62" t="n"/>
+      <c r="R967" s="88" t="n"/>
     </row>
     <row r="968" ht="12.75" customHeight="1" s="70">
       <c r="F968" s="66" t="n"/>
@@ -13132,6 +14113,7 @@
       <c r="O968" s="69" t="n"/>
       <c r="P968" s="62" t="n"/>
       <c r="Q968" s="62" t="n"/>
+      <c r="R968" s="88" t="n"/>
     </row>
     <row r="969" ht="12.75" customHeight="1" s="70">
       <c r="F969" s="66" t="n"/>
@@ -13142,6 +14124,7 @@
       <c r="O969" s="69" t="n"/>
       <c r="P969" s="62" t="n"/>
       <c r="Q969" s="62" t="n"/>
+      <c r="R969" s="88" t="n"/>
     </row>
     <row r="970" ht="12.75" customHeight="1" s="70">
       <c r="F970" s="66" t="n"/>
@@ -13152,6 +14135,7 @@
       <c r="O970" s="69" t="n"/>
       <c r="P970" s="62" t="n"/>
       <c r="Q970" s="62" t="n"/>
+      <c r="R970" s="88" t="n"/>
     </row>
     <row r="971" ht="12.75" customHeight="1" s="70">
       <c r="F971" s="66" t="n"/>
@@ -13162,6 +14146,7 @@
       <c r="O971" s="69" t="n"/>
       <c r="P971" s="62" t="n"/>
       <c r="Q971" s="62" t="n"/>
+      <c r="R971" s="88" t="n"/>
     </row>
     <row r="972" ht="12.75" customHeight="1" s="70">
       <c r="F972" s="66" t="n"/>
@@ -13172,6 +14157,7 @@
       <c r="O972" s="69" t="n"/>
       <c r="P972" s="62" t="n"/>
       <c r="Q972" s="62" t="n"/>
+      <c r="R972" s="88" t="n"/>
     </row>
     <row r="973" ht="12.75" customHeight="1" s="70">
       <c r="F973" s="66" t="n"/>
@@ -13182,6 +14168,7 @@
       <c r="O973" s="69" t="n"/>
       <c r="P973" s="62" t="n"/>
       <c r="Q973" s="62" t="n"/>
+      <c r="R973" s="88" t="n"/>
     </row>
     <row r="974" ht="12.75" customHeight="1" s="70">
       <c r="F974" s="66" t="n"/>
@@ -13192,6 +14179,7 @@
       <c r="O974" s="69" t="n"/>
       <c r="P974" s="62" t="n"/>
       <c r="Q974" s="62" t="n"/>
+      <c r="R974" s="88" t="n"/>
     </row>
     <row r="975" ht="12.75" customHeight="1" s="70">
       <c r="F975" s="66" t="n"/>
@@ -13202,6 +14190,7 @@
       <c r="O975" s="69" t="n"/>
       <c r="P975" s="62" t="n"/>
       <c r="Q975" s="62" t="n"/>
+      <c r="R975" s="88" t="n"/>
     </row>
     <row r="976" ht="12.75" customHeight="1" s="70">
       <c r="F976" s="66" t="n"/>
@@ -13212,6 +14201,7 @@
       <c r="O976" s="69" t="n"/>
       <c r="P976" s="62" t="n"/>
       <c r="Q976" s="62" t="n"/>
+      <c r="R976" s="88" t="n"/>
     </row>
     <row r="977" ht="12.75" customHeight="1" s="70">
       <c r="F977" s="66" t="n"/>
@@ -13222,6 +14212,7 @@
       <c r="O977" s="69" t="n"/>
       <c r="P977" s="62" t="n"/>
       <c r="Q977" s="62" t="n"/>
+      <c r="R977" s="88" t="n"/>
     </row>
     <row r="978" ht="12.75" customHeight="1" s="70">
       <c r="F978" s="66" t="n"/>
@@ -13232,6 +14223,7 @@
       <c r="O978" s="69" t="n"/>
       <c r="P978" s="62" t="n"/>
       <c r="Q978" s="62" t="n"/>
+      <c r="R978" s="88" t="n"/>
     </row>
     <row r="979" ht="12.75" customHeight="1" s="70">
       <c r="F979" s="66" t="n"/>
@@ -13242,6 +14234,7 @@
       <c r="O979" s="69" t="n"/>
       <c r="P979" s="62" t="n"/>
       <c r="Q979" s="62" t="n"/>
+      <c r="R979" s="88" t="n"/>
     </row>
     <row r="980" ht="12.75" customHeight="1" s="70">
       <c r="F980" s="66" t="n"/>
@@ -13252,6 +14245,7 @@
       <c r="O980" s="69" t="n"/>
       <c r="P980" s="62" t="n"/>
       <c r="Q980" s="62" t="n"/>
+      <c r="R980" s="88" t="n"/>
     </row>
     <row r="981" ht="12.75" customHeight="1" s="70">
       <c r="F981" s="66" t="n"/>
@@ -13262,6 +14256,7 @@
       <c r="O981" s="69" t="n"/>
       <c r="P981" s="62" t="n"/>
       <c r="Q981" s="62" t="n"/>
+      <c r="R981" s="88" t="n"/>
     </row>
     <row r="982" ht="12.75" customHeight="1" s="70">
       <c r="F982" s="66" t="n"/>
@@ -13272,6 +14267,7 @@
       <c r="O982" s="69" t="n"/>
       <c r="P982" s="62" t="n"/>
       <c r="Q982" s="62" t="n"/>
+      <c r="R982" s="88" t="n"/>
     </row>
     <row r="983" ht="12.75" customHeight="1" s="70">
       <c r="F983" s="66" t="n"/>
@@ -13282,6 +14278,7 @@
       <c r="O983" s="69" t="n"/>
       <c r="P983" s="62" t="n"/>
       <c r="Q983" s="62" t="n"/>
+      <c r="R983" s="88" t="n"/>
     </row>
     <row r="984" ht="12.75" customHeight="1" s="70">
       <c r="F984" s="66" t="n"/>
@@ -13292,6 +14289,7 @@
       <c r="O984" s="69" t="n"/>
       <c r="P984" s="62" t="n"/>
       <c r="Q984" s="62" t="n"/>
+      <c r="R984" s="88" t="n"/>
     </row>
     <row r="985" ht="12.75" customHeight="1" s="70">
       <c r="F985" s="66" t="n"/>
@@ -13302,6 +14300,7 @@
       <c r="O985" s="69" t="n"/>
       <c r="P985" s="62" t="n"/>
       <c r="Q985" s="62" t="n"/>
+      <c r="R985" s="88" t="n"/>
     </row>
     <row r="986" ht="12.75" customHeight="1" s="70">
       <c r="F986" s="66" t="n"/>
@@ -13312,6 +14311,7 @@
       <c r="O986" s="69" t="n"/>
       <c r="P986" s="62" t="n"/>
       <c r="Q986" s="62" t="n"/>
+      <c r="R986" s="88" t="n"/>
     </row>
     <row r="987" ht="12.75" customHeight="1" s="70">
       <c r="F987" s="66" t="n"/>
@@ -13322,6 +14322,7 @@
       <c r="O987" s="69" t="n"/>
       <c r="P987" s="62" t="n"/>
       <c r="Q987" s="62" t="n"/>
+      <c r="R987" s="88" t="n"/>
     </row>
     <row r="988" ht="12.75" customHeight="1" s="70">
       <c r="F988" s="66" t="n"/>
@@ -13332,6 +14333,7 @@
       <c r="O988" s="69" t="n"/>
       <c r="P988" s="62" t="n"/>
       <c r="Q988" s="62" t="n"/>
+      <c r="R988" s="88" t="n"/>
     </row>
     <row r="989" ht="12.75" customHeight="1" s="70">
       <c r="F989" s="66" t="n"/>
@@ -13342,6 +14344,7 @@
       <c r="O989" s="69" t="n"/>
       <c r="P989" s="62" t="n"/>
       <c r="Q989" s="62" t="n"/>
+      <c r="R989" s="88" t="n"/>
     </row>
     <row r="990" ht="12.75" customHeight="1" s="70">
       <c r="F990" s="66" t="n"/>
@@ -13352,6 +14355,7 @@
       <c r="O990" s="69" t="n"/>
       <c r="P990" s="62" t="n"/>
       <c r="Q990" s="62" t="n"/>
+      <c r="R990" s="88" t="n"/>
     </row>
     <row r="991" ht="12.75" customHeight="1" s="70">
       <c r="F991" s="66" t="n"/>
@@ -13362,6 +14366,7 @@
       <c r="O991" s="69" t="n"/>
       <c r="P991" s="62" t="n"/>
       <c r="Q991" s="62" t="n"/>
+      <c r="R991" s="88" t="n"/>
     </row>
     <row r="992" ht="12.75" customHeight="1" s="70">
       <c r="F992" s="66" t="n"/>
@@ -13372,6 +14377,7 @@
       <c r="O992" s="69" t="n"/>
       <c r="P992" s="62" t="n"/>
       <c r="Q992" s="62" t="n"/>
+      <c r="R992" s="88" t="n"/>
     </row>
     <row r="993" ht="12.75" customHeight="1" s="70">
       <c r="F993" s="66" t="n"/>
@@ -13382,6 +14388,7 @@
       <c r="O993" s="69" t="n"/>
       <c r="P993" s="62" t="n"/>
       <c r="Q993" s="62" t="n"/>
+      <c r="R993" s="88" t="n"/>
     </row>
     <row r="994" ht="12.75" customHeight="1" s="70">
       <c r="F994" s="66" t="n"/>
@@ -13392,6 +14399,7 @@
       <c r="O994" s="69" t="n"/>
       <c r="P994" s="62" t="n"/>
       <c r="Q994" s="62" t="n"/>
+      <c r="R994" s="88" t="n"/>
     </row>
     <row r="995" ht="12.75" customHeight="1" s="70">
       <c r="F995" s="66" t="n"/>
@@ -13402,6 +14410,7 @@
       <c r="O995" s="69" t="n"/>
       <c r="P995" s="62" t="n"/>
       <c r="Q995" s="62" t="n"/>
+      <c r="R995" s="88" t="n"/>
     </row>
     <row r="996" ht="12.75" customHeight="1" s="70">
       <c r="F996" s="66" t="n"/>
@@ -13412,6 +14421,7 @@
       <c r="O996" s="69" t="n"/>
       <c r="P996" s="62" t="n"/>
       <c r="Q996" s="62" t="n"/>
+      <c r="R996" s="88" t="n"/>
     </row>
     <row r="997" ht="12.75" customHeight="1" s="70">
       <c r="F997" s="66" t="n"/>
@@ -13422,6 +14432,7 @@
       <c r="O997" s="69" t="n"/>
       <c r="P997" s="62" t="n"/>
       <c r="Q997" s="62" t="n"/>
+      <c r="R997" s="88" t="n"/>
     </row>
     <row r="998" ht="12.75" customHeight="1" s="70">
       <c r="F998" s="66" t="n"/>
@@ -13432,6 +14443,7 @@
       <c r="O998" s="69" t="n"/>
       <c r="P998" s="62" t="n"/>
       <c r="Q998" s="62" t="n"/>
+      <c r="R998" s="88" t="n"/>
     </row>
     <row r="999" ht="12.75" customHeight="1" s="70">
       <c r="F999" s="66" t="n"/>
@@ -13442,6 +14454,7 @@
       <c r="O999" s="69" t="n"/>
       <c r="P999" s="62" t="n"/>
       <c r="Q999" s="62" t="n"/>
+      <c r="R999" s="88" t="n"/>
     </row>
     <row r="1000" ht="12.75" customHeight="1" s="70">
       <c r="F1000" s="66" t="n"/>
@@ -13452,6 +14465,7 @@
       <c r="O1000" s="69" t="n"/>
       <c r="P1000" s="62" t="n"/>
       <c r="Q1000" s="62" t="n"/>
+      <c r="R1000" s="88" t="n"/>
     </row>
     <row r="1001" ht="12.75" customHeight="1" s="70">
       <c r="F1001" s="66" t="n"/>
@@ -13462,6 +14476,7 @@
       <c r="O1001" s="69" t="n"/>
       <c r="P1001" s="62" t="n"/>
       <c r="Q1001" s="62" t="n"/>
+      <c r="R1001" s="88" t="n"/>
     </row>
     <row r="1002" ht="12.75" customHeight="1" s="70">
       <c r="F1002" s="66" t="n"/>
@@ -13472,6 +14487,7 @@
       <c r="O1002" s="69" t="n"/>
       <c r="P1002" s="62" t="n"/>
       <c r="Q1002" s="62" t="n"/>
+      <c r="R1002" s="88" t="n"/>
     </row>
     <row r="1003" ht="12.75" customHeight="1" s="70">
       <c r="F1003" s="66" t="n"/>
@@ -13482,6 +14498,7 @@
       <c r="O1003" s="69" t="n"/>
       <c r="P1003" s="62" t="n"/>
       <c r="Q1003" s="62" t="n"/>
+      <c r="R1003" s="88" t="n"/>
     </row>
     <row r="1004" ht="12.75" customHeight="1" s="70">
       <c r="F1004" s="66" t="n"/>
@@ -13492,6 +14509,7 @@
       <c r="O1004" s="69" t="n"/>
       <c r="P1004" s="62" t="n"/>
       <c r="Q1004" s="62" t="n"/>
+      <c r="R1004" s="88" t="n"/>
     </row>
     <row r="1005" ht="12.75" customHeight="1" s="70">
       <c r="F1005" s="66" t="n"/>
@@ -13502,6 +14520,7 @@
       <c r="O1005" s="69" t="n"/>
       <c r="P1005" s="62" t="n"/>
       <c r="Q1005" s="62" t="n"/>
+      <c r="R1005" s="88" t="n"/>
     </row>
     <row r="1006" ht="12.75" customHeight="1" s="70">
       <c r="F1006" s="66" t="n"/>
@@ -13512,6 +14531,7 @@
       <c r="O1006" s="69" t="n"/>
       <c r="P1006" s="62" t="n"/>
       <c r="Q1006" s="62" t="n"/>
+      <c r="R1006" s="88" t="n"/>
     </row>
     <row r="1007" ht="12.75" customHeight="1" s="70">
       <c r="F1007" s="66" t="n"/>
@@ -13522,6 +14542,7 @@
       <c r="O1007" s="69" t="n"/>
       <c r="P1007" s="62" t="n"/>
       <c r="Q1007" s="62" t="n"/>
+      <c r="R1007" s="88" t="n"/>
     </row>
     <row r="1008" ht="12.75" customHeight="1" s="70">
       <c r="F1008" s="66" t="n"/>
@@ -13532,6 +14553,7 @@
       <c r="O1008" s="69" t="n"/>
       <c r="P1008" s="62" t="n"/>
       <c r="Q1008" s="62" t="n"/>
+      <c r="R1008" s="88" t="n"/>
     </row>
     <row r="1009" ht="12.75" customHeight="1" s="70">
       <c r="F1009" s="66" t="n"/>
@@ -13542,6 +14564,7 @@
       <c r="O1009" s="69" t="n"/>
       <c r="P1009" s="62" t="n"/>
       <c r="Q1009" s="62" t="n"/>
+      <c r="R1009" s="88" t="n"/>
     </row>
     <row r="1010" ht="12.75" customHeight="1" s="70">
       <c r="F1010" s="66" t="n"/>
@@ -13552,6 +14575,7 @@
       <c r="O1010" s="69" t="n"/>
       <c r="P1010" s="62" t="n"/>
       <c r="Q1010" s="62" t="n"/>
+      <c r="R1010" s="88" t="n"/>
     </row>
     <row r="1011" ht="12.75" customHeight="1" s="70">
       <c r="F1011" s="66" t="n"/>
@@ -13562,6 +14586,7 @@
       <c r="O1011" s="69" t="n"/>
       <c r="P1011" s="62" t="n"/>
       <c r="Q1011" s="62" t="n"/>
+      <c r="R1011" s="88" t="n"/>
     </row>
     <row r="1012" ht="12.75" customHeight="1" s="70">
       <c r="F1012" s="66" t="n"/>
@@ -13572,6 +14597,7 @@
       <c r="O1012" s="69" t="n"/>
       <c r="P1012" s="62" t="n"/>
       <c r="Q1012" s="62" t="n"/>
+      <c r="R1012" s="88" t="n"/>
     </row>
     <row r="1013" ht="12.75" customHeight="1" s="70">
       <c r="F1013" s="66" t="n"/>
@@ -13582,6 +14608,7 @@
       <c r="O1013" s="69" t="n"/>
       <c r="P1013" s="62" t="n"/>
       <c r="Q1013" s="62" t="n"/>
+      <c r="R1013" s="88" t="n"/>
     </row>
     <row r="1014" ht="12.75" customHeight="1" s="70">
       <c r="F1014" s="66" t="n"/>
@@ -13592,6 +14619,7 @@
       <c r="O1014" s="69" t="n"/>
       <c r="P1014" s="62" t="n"/>
       <c r="Q1014" s="62" t="n"/>
+      <c r="R1014" s="88" t="n"/>
     </row>
     <row r="1015" ht="12.75" customHeight="1" s="70">
       <c r="F1015" s="66" t="n"/>
@@ -13602,6 +14630,7 @@
       <c r="O1015" s="69" t="n"/>
       <c r="P1015" s="62" t="n"/>
       <c r="Q1015" s="62" t="n"/>
+      <c r="R1015" s="88" t="n"/>
     </row>
     <row r="1016" ht="12.75" customHeight="1" s="70">
       <c r="F1016" s="66" t="n"/>
@@ -13612,6 +14641,7 @@
       <c r="O1016" s="69" t="n"/>
       <c r="P1016" s="62" t="n"/>
       <c r="Q1016" s="62" t="n"/>
+      <c r="R1016" s="88" t="n"/>
     </row>
     <row r="1017" ht="12.75" customHeight="1" s="70">
       <c r="F1017" s="66" t="n"/>
@@ -13622,6 +14652,7 @@
       <c r="O1017" s="69" t="n"/>
       <c r="P1017" s="62" t="n"/>
       <c r="Q1017" s="62" t="n"/>
+      <c r="R1017" s="88" t="n"/>
     </row>
     <row r="1018" ht="12.75" customHeight="1" s="70">
       <c r="F1018" s="66" t="n"/>
@@ -13632,6 +14663,7 @@
       <c r="O1018" s="69" t="n"/>
       <c r="P1018" s="62" t="n"/>
       <c r="Q1018" s="62" t="n"/>
+      <c r="R1018" s="88" t="n"/>
     </row>
     <row r="1019" ht="12.75" customHeight="1" s="70">
       <c r="F1019" s="66" t="n"/>
@@ -13642,6 +14674,7 @@
       <c r="O1019" s="69" t="n"/>
       <c r="P1019" s="62" t="n"/>
       <c r="Q1019" s="62" t="n"/>
+      <c r="R1019" s="88" t="n"/>
     </row>
     <row r="1020" ht="12.75" customHeight="1" s="70">
       <c r="F1020" s="66" t="n"/>
@@ -13652,6 +14685,7 @@
       <c r="O1020" s="69" t="n"/>
       <c r="P1020" s="62" t="n"/>
       <c r="Q1020" s="62" t="n"/>
+      <c r="R1020" s="88" t="n"/>
     </row>
     <row r="1021" ht="12.75" customHeight="1" s="70">
       <c r="F1021" s="66" t="n"/>
@@ -13662,6 +14696,7 @@
       <c r="O1021" s="69" t="n"/>
       <c r="P1021" s="62" t="n"/>
       <c r="Q1021" s="62" t="n"/>
+      <c r="R1021" s="88" t="n"/>
     </row>
     <row r="1022" ht="12.75" customHeight="1" s="70">
       <c r="F1022" s="66" t="n"/>
@@ -13672,6 +14707,7 @@
       <c r="O1022" s="69" t="n"/>
       <c r="P1022" s="62" t="n"/>
       <c r="Q1022" s="62" t="n"/>
+      <c r="R1022" s="88" t="n"/>
     </row>
     <row r="1023" ht="12.75" customHeight="1" s="70">
       <c r="F1023" s="66" t="n"/>
@@ -13682,6 +14718,7 @@
       <c r="O1023" s="69" t="n"/>
       <c r="P1023" s="62" t="n"/>
       <c r="Q1023" s="62" t="n"/>
+      <c r="R1023" s="88" t="n"/>
     </row>
     <row r="1024" ht="12.75" customHeight="1" s="70">
       <c r="F1024" s="66" t="n"/>
@@ -13692,6 +14729,7 @@
       <c r="O1024" s="69" t="n"/>
       <c r="P1024" s="62" t="n"/>
       <c r="Q1024" s="62" t="n"/>
+      <c r="R1024" s="88" t="n"/>
     </row>
     <row r="1025" ht="12.75" customHeight="1" s="70">
       <c r="F1025" s="66" t="n"/>
@@ -13702,6 +14740,7 @@
       <c r="O1025" s="69" t="n"/>
       <c r="P1025" s="62" t="n"/>
       <c r="Q1025" s="62" t="n"/>
+      <c r="R1025" s="88" t="n"/>
     </row>
     <row r="1026" ht="12.75" customHeight="1" s="70">
       <c r="F1026" s="66" t="n"/>
@@ -13712,6 +14751,7 @@
       <c r="O1026" s="69" t="n"/>
       <c r="P1026" s="62" t="n"/>
       <c r="Q1026" s="62" t="n"/>
+      <c r="R1026" s="88" t="n"/>
     </row>
     <row r="1027" ht="12.75" customHeight="1" s="70">
       <c r="F1027" s="66" t="n"/>
@@ -13722,6 +14762,7 @@
       <c r="O1027" s="69" t="n"/>
       <c r="P1027" s="62" t="n"/>
       <c r="Q1027" s="62" t="n"/>
+      <c r="R1027" s="88" t="n"/>
     </row>
     <row r="1028" ht="12.75" customHeight="1" s="70">
       <c r="F1028" s="66" t="n"/>
@@ -13732,6 +14773,7 @@
       <c r="O1028" s="69" t="n"/>
       <c r="P1028" s="62" t="n"/>
       <c r="Q1028" s="62" t="n"/>
+      <c r="R1028" s="88" t="n"/>
     </row>
     <row r="1029" ht="12.75" customHeight="1" s="70">
       <c r="F1029" s="66" t="n"/>
@@ -13742,6 +14784,7 @@
       <c r="O1029" s="69" t="n"/>
       <c r="P1029" s="62" t="n"/>
       <c r="Q1029" s="62" t="n"/>
+      <c r="R1029" s="88" t="n"/>
     </row>
     <row r="1030" ht="12.75" customHeight="1" s="70">
       <c r="F1030" s="66" t="n"/>
@@ -13752,6 +14795,7 @@
       <c r="O1030" s="69" t="n"/>
       <c r="P1030" s="62" t="n"/>
       <c r="Q1030" s="62" t="n"/>
+      <c r="R1030" s="88" t="n"/>
     </row>
     <row r="1031" ht="12.75" customHeight="1" s="70">
       <c r="F1031" s="66" t="n"/>
@@ -13762,6 +14806,7 @@
       <c r="O1031" s="69" t="n"/>
       <c r="P1031" s="62" t="n"/>
       <c r="Q1031" s="62" t="n"/>
+      <c r="R1031" s="88" t="n"/>
     </row>
     <row r="1032" ht="12.75" customHeight="1" s="70">
       <c r="F1032" s="66" t="n"/>
@@ -13772,6 +14817,7 @@
       <c r="O1032" s="69" t="n"/>
       <c r="P1032" s="62" t="n"/>
       <c r="Q1032" s="62" t="n"/>
+      <c r="R1032" s="88" t="n"/>
     </row>
     <row r="1033" ht="12.75" customHeight="1" s="70">
       <c r="F1033" s="66" t="n"/>
@@ -13782,6 +14828,7 @@
       <c r="O1033" s="69" t="n"/>
       <c r="P1033" s="62" t="n"/>
       <c r="Q1033" s="62" t="n"/>
+      <c r="R1033" s="88" t="n"/>
     </row>
     <row r="1034" ht="12.75" customHeight="1" s="70">
       <c r="F1034" s="66" t="n"/>
@@ -13792,6 +14839,7 @@
       <c r="O1034" s="69" t="n"/>
       <c r="P1034" s="62" t="n"/>
       <c r="Q1034" s="62" t="n"/>
+      <c r="R1034" s="88" t="n"/>
     </row>
     <row r="1035" ht="12.75" customHeight="1" s="70">
       <c r="F1035" s="66" t="n"/>
@@ -13802,6 +14850,7 @@
       <c r="O1035" s="69" t="n"/>
       <c r="P1035" s="62" t="n"/>
       <c r="Q1035" s="62" t="n"/>
+      <c r="R1035" s="88" t="n"/>
     </row>
     <row r="1036" ht="12.75" customHeight="1" s="70">
       <c r="F1036" s="66" t="n"/>
@@ -13812,6 +14861,7 @@
       <c r="O1036" s="69" t="n"/>
       <c r="P1036" s="62" t="n"/>
       <c r="Q1036" s="62" t="n"/>
+      <c r="R1036" s="88" t="n"/>
     </row>
     <row r="1037" ht="12.75" customHeight="1" s="70">
       <c r="F1037" s="66" t="n"/>
@@ -13822,6 +14872,7 @@
       <c r="O1037" s="69" t="n"/>
       <c r="P1037" s="62" t="n"/>
       <c r="Q1037" s="62" t="n"/>
+      <c r="R1037" s="88" t="n"/>
     </row>
     <row r="1038" ht="12.75" customHeight="1" s="70">
       <c r="F1038" s="66" t="n"/>
@@ -13832,6 +14883,7 @@
       <c r="O1038" s="69" t="n"/>
       <c r="P1038" s="62" t="n"/>
       <c r="Q1038" s="62" t="n"/>
+      <c r="R1038" s="88" t="n"/>
     </row>
     <row r="1039" ht="12.75" customHeight="1" s="70">
       <c r="F1039" s="66" t="n"/>
@@ -13842,6 +14894,7 @@
       <c r="O1039" s="69" t="n"/>
       <c r="P1039" s="62" t="n"/>
       <c r="Q1039" s="62" t="n"/>
+      <c r="R1039" s="88" t="n"/>
     </row>
     <row r="1040" ht="12.75" customHeight="1" s="70">
       <c r="F1040" s="66" t="n"/>
@@ -13852,6 +14905,7 @@
       <c r="O1040" s="69" t="n"/>
       <c r="P1040" s="62" t="n"/>
       <c r="Q1040" s="62" t="n"/>
+      <c r="R1040" s="88" t="n"/>
     </row>
     <row r="1041" ht="12.75" customHeight="1" s="70">
       <c r="F1041" s="66" t="n"/>
@@ -13862,6 +14916,7 @@
       <c r="O1041" s="69" t="n"/>
       <c r="P1041" s="62" t="n"/>
       <c r="Q1041" s="62" t="n"/>
+      <c r="R1041" s="88" t="n"/>
     </row>
     <row r="1042" ht="12.75" customHeight="1" s="70">
       <c r="F1042" s="66" t="n"/>
@@ -13872,6 +14927,7 @@
       <c r="O1042" s="69" t="n"/>
       <c r="P1042" s="62" t="n"/>
       <c r="Q1042" s="62" t="n"/>
+      <c r="R1042" s="88" t="n"/>
     </row>
     <row r="1043" ht="12.75" customHeight="1" s="70">
       <c r="F1043" s="66" t="n"/>
@@ -13882,6 +14938,7 @@
       <c r="O1043" s="69" t="n"/>
       <c r="P1043" s="62" t="n"/>
       <c r="Q1043" s="62" t="n"/>
+      <c r="R1043" s="88" t="n"/>
     </row>
     <row r="1044" ht="12.75" customHeight="1" s="70">
       <c r="F1044" s="66" t="n"/>
@@ -13892,6 +14949,7 @@
       <c r="O1044" s="69" t="n"/>
       <c r="P1044" s="62" t="n"/>
       <c r="Q1044" s="62" t="n"/>
+      <c r="R1044" s="88" t="n"/>
     </row>
     <row r="1045" ht="12.75" customHeight="1" s="70">
       <c r="F1045" s="66" t="n"/>
@@ -13902,6 +14960,7 @@
       <c r="O1045" s="69" t="n"/>
       <c r="P1045" s="62" t="n"/>
       <c r="Q1045" s="62" t="n"/>
+      <c r="R1045" s="88" t="n"/>
     </row>
     <row r="1048576" ht="12.75" customHeight="1" s="70"/>
   </sheetData>
@@ -13976,7 +15035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:R1700"/>
+  <dimension ref="A1:R246"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.40625" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24.67" customWidth="1" style="43" min="1" max="1"/>
@@ -13987,7 +15046,6 @@
     <col width="19.5" customWidth="1" style="43" min="7" max="7"/>
     <col width="71.98" customWidth="1" style="43" min="8" max="8"/>
     <col width="34.52" customWidth="1" style="43" min="9" max="9"/>
-    <col width="20" customWidth="1" style="70" min="18" max="18"/>
     <col width="11.52" customWidth="1" style="43" min="1024" max="1024"/>
   </cols>
   <sheetData>
@@ -14028,11 +15086,6 @@
           <t>Тип разрешительной документации</t>
         </is>
       </c>
-      <c r="R1" s="43" t="inlineStr">
-        <is>
-          <t>Вес в граммах</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="13.5" customHeight="1" s="70">
       <c r="D2" s="43" t="inlineStr">
@@ -14152,7 +15205,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="160" customHeight="1" s="70">
+    <row r="6" ht="13.5" customHeight="1" s="70">
       <c r="D6" s="43" t="inlineStr">
         <is>
           <t>БЕСКОЗЫРКА</t>
@@ -14166,11 +15219,6 @@
       <c r="H6" s="73" t="inlineStr">
         <is>
           <t>АЛАНДСКИЕ ОСТРОВА</t>
-        </is>
-      </c>
-      <c r="R6" s="86" t="inlineStr">
-        <is>
-          <t>Обязательное поле: общий вес позиции, целое число больше 0. Просьба указать актуальный вес товара в ГРАММАХ для отчетности РОСПРИРОДНАДЗОР.</t>
         </is>
       </c>
     </row>
@@ -16618,1460 +17666,6 @@
     <row r="246" ht="13.5" customHeight="1" s="70">
       <c r="H246" s="73" t="n"/>
     </row>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
-    <row r="501"/>
-    <row r="502"/>
-    <row r="503"/>
-    <row r="504"/>
-    <row r="505"/>
-    <row r="506"/>
-    <row r="507"/>
-    <row r="508"/>
-    <row r="509"/>
-    <row r="510"/>
-    <row r="511"/>
-    <row r="512"/>
-    <row r="513"/>
-    <row r="514"/>
-    <row r="515"/>
-    <row r="516"/>
-    <row r="517"/>
-    <row r="518"/>
-    <row r="519"/>
-    <row r="520"/>
-    <row r="521"/>
-    <row r="522"/>
-    <row r="523"/>
-    <row r="524"/>
-    <row r="525"/>
-    <row r="526"/>
-    <row r="527"/>
-    <row r="528"/>
-    <row r="529"/>
-    <row r="530"/>
-    <row r="531"/>
-    <row r="532"/>
-    <row r="533"/>
-    <row r="534"/>
-    <row r="535"/>
-    <row r="536"/>
-    <row r="537"/>
-    <row r="538"/>
-    <row r="539"/>
-    <row r="540"/>
-    <row r="541"/>
-    <row r="542"/>
-    <row r="543"/>
-    <row r="544"/>
-    <row r="545"/>
-    <row r="546"/>
-    <row r="547"/>
-    <row r="548"/>
-    <row r="549"/>
-    <row r="550"/>
-    <row r="551"/>
-    <row r="552"/>
-    <row r="553"/>
-    <row r="554"/>
-    <row r="555"/>
-    <row r="556"/>
-    <row r="557"/>
-    <row r="558"/>
-    <row r="559"/>
-    <row r="560"/>
-    <row r="561"/>
-    <row r="562"/>
-    <row r="563"/>
-    <row r="564"/>
-    <row r="565"/>
-    <row r="566"/>
-    <row r="567"/>
-    <row r="568"/>
-    <row r="569"/>
-    <row r="570"/>
-    <row r="571"/>
-    <row r="572"/>
-    <row r="573"/>
-    <row r="574"/>
-    <row r="575"/>
-    <row r="576"/>
-    <row r="577"/>
-    <row r="578"/>
-    <row r="579"/>
-    <row r="580"/>
-    <row r="581"/>
-    <row r="582"/>
-    <row r="583"/>
-    <row r="584"/>
-    <row r="585"/>
-    <row r="586"/>
-    <row r="587"/>
-    <row r="588"/>
-    <row r="589"/>
-    <row r="590"/>
-    <row r="591"/>
-    <row r="592"/>
-    <row r="593"/>
-    <row r="594"/>
-    <row r="595"/>
-    <row r="596"/>
-    <row r="597"/>
-    <row r="598"/>
-    <row r="599"/>
-    <row r="600"/>
-    <row r="601"/>
-    <row r="602"/>
-    <row r="603"/>
-    <row r="604"/>
-    <row r="605"/>
-    <row r="606"/>
-    <row r="607"/>
-    <row r="608"/>
-    <row r="609"/>
-    <row r="610"/>
-    <row r="611"/>
-    <row r="612"/>
-    <row r="613"/>
-    <row r="614"/>
-    <row r="615"/>
-    <row r="616"/>
-    <row r="617"/>
-    <row r="618"/>
-    <row r="619"/>
-    <row r="620"/>
-    <row r="621"/>
-    <row r="622"/>
-    <row r="623"/>
-    <row r="624"/>
-    <row r="625"/>
-    <row r="626"/>
-    <row r="627"/>
-    <row r="628"/>
-    <row r="629"/>
-    <row r="630"/>
-    <row r="631"/>
-    <row r="632"/>
-    <row r="633"/>
-    <row r="634"/>
-    <row r="635"/>
-    <row r="636"/>
-    <row r="637"/>
-    <row r="638"/>
-    <row r="639"/>
-    <row r="640"/>
-    <row r="641"/>
-    <row r="642"/>
-    <row r="643"/>
-    <row r="644"/>
-    <row r="645"/>
-    <row r="646"/>
-    <row r="647"/>
-    <row r="648"/>
-    <row r="649"/>
-    <row r="650"/>
-    <row r="651"/>
-    <row r="652"/>
-    <row r="653"/>
-    <row r="654"/>
-    <row r="655"/>
-    <row r="656"/>
-    <row r="657"/>
-    <row r="658"/>
-    <row r="659"/>
-    <row r="660"/>
-    <row r="661"/>
-    <row r="662"/>
-    <row r="663"/>
-    <row r="664"/>
-    <row r="665"/>
-    <row r="666"/>
-    <row r="667"/>
-    <row r="668"/>
-    <row r="669"/>
-    <row r="670"/>
-    <row r="671"/>
-    <row r="672"/>
-    <row r="673"/>
-    <row r="674"/>
-    <row r="675"/>
-    <row r="676"/>
-    <row r="677"/>
-    <row r="678"/>
-    <row r="679"/>
-    <row r="680"/>
-    <row r="681"/>
-    <row r="682"/>
-    <row r="683"/>
-    <row r="684"/>
-    <row r="685"/>
-    <row r="686"/>
-    <row r="687"/>
-    <row r="688"/>
-    <row r="689"/>
-    <row r="690"/>
-    <row r="691"/>
-    <row r="692"/>
-    <row r="693"/>
-    <row r="694"/>
-    <row r="695"/>
-    <row r="696"/>
-    <row r="697"/>
-    <row r="698"/>
-    <row r="699"/>
-    <row r="700"/>
-    <row r="701"/>
-    <row r="702"/>
-    <row r="703"/>
-    <row r="704"/>
-    <row r="705"/>
-    <row r="706"/>
-    <row r="707"/>
-    <row r="708"/>
-    <row r="709"/>
-    <row r="710"/>
-    <row r="711"/>
-    <row r="712"/>
-    <row r="713"/>
-    <row r="714"/>
-    <row r="715"/>
-    <row r="716"/>
-    <row r="717"/>
-    <row r="718"/>
-    <row r="719"/>
-    <row r="720"/>
-    <row r="721"/>
-    <row r="722"/>
-    <row r="723"/>
-    <row r="724"/>
-    <row r="725"/>
-    <row r="726"/>
-    <row r="727"/>
-    <row r="728"/>
-    <row r="729"/>
-    <row r="730"/>
-    <row r="731"/>
-    <row r="732"/>
-    <row r="733"/>
-    <row r="734"/>
-    <row r="735"/>
-    <row r="736"/>
-    <row r="737"/>
-    <row r="738"/>
-    <row r="739"/>
-    <row r="740"/>
-    <row r="741"/>
-    <row r="742"/>
-    <row r="743"/>
-    <row r="744"/>
-    <row r="745"/>
-    <row r="746"/>
-    <row r="747"/>
-    <row r="748"/>
-    <row r="749"/>
-    <row r="750"/>
-    <row r="751"/>
-    <row r="752"/>
-    <row r="753"/>
-    <row r="754"/>
-    <row r="755"/>
-    <row r="756"/>
-    <row r="757"/>
-    <row r="758"/>
-    <row r="759"/>
-    <row r="760"/>
-    <row r="761"/>
-    <row r="762"/>
-    <row r="763"/>
-    <row r="764"/>
-    <row r="765"/>
-    <row r="766"/>
-    <row r="767"/>
-    <row r="768"/>
-    <row r="769"/>
-    <row r="770"/>
-    <row r="771"/>
-    <row r="772"/>
-    <row r="773"/>
-    <row r="774"/>
-    <row r="775"/>
-    <row r="776"/>
-    <row r="777"/>
-    <row r="778"/>
-    <row r="779"/>
-    <row r="780"/>
-    <row r="781"/>
-    <row r="782"/>
-    <row r="783"/>
-    <row r="784"/>
-    <row r="785"/>
-    <row r="786"/>
-    <row r="787"/>
-    <row r="788"/>
-    <row r="789"/>
-    <row r="790"/>
-    <row r="791"/>
-    <row r="792"/>
-    <row r="793"/>
-    <row r="794"/>
-    <row r="795"/>
-    <row r="796"/>
-    <row r="797"/>
-    <row r="798"/>
-    <row r="799"/>
-    <row r="800"/>
-    <row r="801"/>
-    <row r="802"/>
-    <row r="803"/>
-    <row r="804"/>
-    <row r="805"/>
-    <row r="806"/>
-    <row r="807"/>
-    <row r="808"/>
-    <row r="809"/>
-    <row r="810"/>
-    <row r="811"/>
-    <row r="812"/>
-    <row r="813"/>
-    <row r="814"/>
-    <row r="815"/>
-    <row r="816"/>
-    <row r="817"/>
-    <row r="818"/>
-    <row r="819"/>
-    <row r="820"/>
-    <row r="821"/>
-    <row r="822"/>
-    <row r="823"/>
-    <row r="824"/>
-    <row r="825"/>
-    <row r="826"/>
-    <row r="827"/>
-    <row r="828"/>
-    <row r="829"/>
-    <row r="830"/>
-    <row r="831"/>
-    <row r="832"/>
-    <row r="833"/>
-    <row r="834"/>
-    <row r="835"/>
-    <row r="836"/>
-    <row r="837"/>
-    <row r="838"/>
-    <row r="839"/>
-    <row r="840"/>
-    <row r="841"/>
-    <row r="842"/>
-    <row r="843"/>
-    <row r="844"/>
-    <row r="845"/>
-    <row r="846"/>
-    <row r="847"/>
-    <row r="848"/>
-    <row r="849"/>
-    <row r="850"/>
-    <row r="851"/>
-    <row r="852"/>
-    <row r="853"/>
-    <row r="854"/>
-    <row r="855"/>
-    <row r="856"/>
-    <row r="857"/>
-    <row r="858"/>
-    <row r="859"/>
-    <row r="860"/>
-    <row r="861"/>
-    <row r="862"/>
-    <row r="863"/>
-    <row r="864"/>
-    <row r="865"/>
-    <row r="866"/>
-    <row r="867"/>
-    <row r="868"/>
-    <row r="869"/>
-    <row r="870"/>
-    <row r="871"/>
-    <row r="872"/>
-    <row r="873"/>
-    <row r="874"/>
-    <row r="875"/>
-    <row r="876"/>
-    <row r="877"/>
-    <row r="878"/>
-    <row r="879"/>
-    <row r="880"/>
-    <row r="881"/>
-    <row r="882"/>
-    <row r="883"/>
-    <row r="884"/>
-    <row r="885"/>
-    <row r="886"/>
-    <row r="887"/>
-    <row r="888"/>
-    <row r="889"/>
-    <row r="890"/>
-    <row r="891"/>
-    <row r="892"/>
-    <row r="893"/>
-    <row r="894"/>
-    <row r="895"/>
-    <row r="896"/>
-    <row r="897"/>
-    <row r="898"/>
-    <row r="899"/>
-    <row r="900"/>
-    <row r="901"/>
-    <row r="902"/>
-    <row r="903"/>
-    <row r="904"/>
-    <row r="905"/>
-    <row r="906"/>
-    <row r="907"/>
-    <row r="908"/>
-    <row r="909"/>
-    <row r="910"/>
-    <row r="911"/>
-    <row r="912"/>
-    <row r="913"/>
-    <row r="914"/>
-    <row r="915"/>
-    <row r="916"/>
-    <row r="917"/>
-    <row r="918"/>
-    <row r="919"/>
-    <row r="920"/>
-    <row r="921"/>
-    <row r="922"/>
-    <row r="923"/>
-    <row r="924"/>
-    <row r="925"/>
-    <row r="926"/>
-    <row r="927"/>
-    <row r="928"/>
-    <row r="929"/>
-    <row r="930"/>
-    <row r="931"/>
-    <row r="932"/>
-    <row r="933"/>
-    <row r="934"/>
-    <row r="935"/>
-    <row r="936"/>
-    <row r="937"/>
-    <row r="938"/>
-    <row r="939"/>
-    <row r="940"/>
-    <row r="941"/>
-    <row r="942"/>
-    <row r="943"/>
-    <row r="944"/>
-    <row r="945"/>
-    <row r="946"/>
-    <row r="947"/>
-    <row r="948"/>
-    <row r="949"/>
-    <row r="950"/>
-    <row r="951"/>
-    <row r="952"/>
-    <row r="953"/>
-    <row r="954"/>
-    <row r="955"/>
-    <row r="956"/>
-    <row r="957"/>
-    <row r="958"/>
-    <row r="959"/>
-    <row r="960"/>
-    <row r="961"/>
-    <row r="962"/>
-    <row r="963"/>
-    <row r="964"/>
-    <row r="965"/>
-    <row r="966"/>
-    <row r="967"/>
-    <row r="968"/>
-    <row r="969"/>
-    <row r="970"/>
-    <row r="971"/>
-    <row r="972"/>
-    <row r="973"/>
-    <row r="974"/>
-    <row r="975"/>
-    <row r="976"/>
-    <row r="977"/>
-    <row r="978"/>
-    <row r="979"/>
-    <row r="980"/>
-    <row r="981"/>
-    <row r="982"/>
-    <row r="983"/>
-    <row r="984"/>
-    <row r="985"/>
-    <row r="986"/>
-    <row r="987"/>
-    <row r="988"/>
-    <row r="989"/>
-    <row r="990"/>
-    <row r="991"/>
-    <row r="992"/>
-    <row r="993"/>
-    <row r="994"/>
-    <row r="995"/>
-    <row r="996"/>
-    <row r="997"/>
-    <row r="998"/>
-    <row r="999"/>
-    <row r="1000"/>
-    <row r="1001"/>
-    <row r="1002"/>
-    <row r="1003"/>
-    <row r="1004"/>
-    <row r="1005"/>
-    <row r="1006"/>
-    <row r="1007"/>
-    <row r="1008"/>
-    <row r="1009"/>
-    <row r="1010"/>
-    <row r="1011"/>
-    <row r="1012"/>
-    <row r="1013"/>
-    <row r="1014"/>
-    <row r="1015"/>
-    <row r="1016"/>
-    <row r="1017"/>
-    <row r="1018"/>
-    <row r="1019"/>
-    <row r="1020"/>
-    <row r="1021"/>
-    <row r="1022"/>
-    <row r="1023"/>
-    <row r="1024"/>
-    <row r="1025"/>
-    <row r="1026"/>
-    <row r="1027"/>
-    <row r="1028"/>
-    <row r="1029"/>
-    <row r="1030"/>
-    <row r="1031"/>
-    <row r="1032"/>
-    <row r="1033"/>
-    <row r="1034"/>
-    <row r="1035"/>
-    <row r="1036"/>
-    <row r="1037"/>
-    <row r="1038"/>
-    <row r="1039"/>
-    <row r="1040"/>
-    <row r="1041"/>
-    <row r="1042"/>
-    <row r="1043"/>
-    <row r="1044"/>
-    <row r="1045"/>
-    <row r="1046"/>
-    <row r="1047"/>
-    <row r="1048"/>
-    <row r="1049"/>
-    <row r="1050"/>
-    <row r="1051"/>
-    <row r="1052"/>
-    <row r="1053"/>
-    <row r="1054"/>
-    <row r="1055"/>
-    <row r="1056"/>
-    <row r="1057"/>
-    <row r="1058"/>
-    <row r="1059"/>
-    <row r="1060"/>
-    <row r="1061"/>
-    <row r="1062"/>
-    <row r="1063"/>
-    <row r="1064"/>
-    <row r="1065"/>
-    <row r="1066"/>
-    <row r="1067"/>
-    <row r="1068"/>
-    <row r="1069"/>
-    <row r="1070"/>
-    <row r="1071"/>
-    <row r="1072"/>
-    <row r="1073"/>
-    <row r="1074"/>
-    <row r="1075"/>
-    <row r="1076"/>
-    <row r="1077"/>
-    <row r="1078"/>
-    <row r="1079"/>
-    <row r="1080"/>
-    <row r="1081"/>
-    <row r="1082"/>
-    <row r="1083"/>
-    <row r="1084"/>
-    <row r="1085"/>
-    <row r="1086"/>
-    <row r="1087"/>
-    <row r="1088"/>
-    <row r="1089"/>
-    <row r="1090"/>
-    <row r="1091"/>
-    <row r="1092"/>
-    <row r="1093"/>
-    <row r="1094"/>
-    <row r="1095"/>
-    <row r="1096"/>
-    <row r="1097"/>
-    <row r="1098"/>
-    <row r="1099"/>
-    <row r="1100"/>
-    <row r="1101"/>
-    <row r="1102"/>
-    <row r="1103"/>
-    <row r="1104"/>
-    <row r="1105"/>
-    <row r="1106"/>
-    <row r="1107"/>
-    <row r="1108"/>
-    <row r="1109"/>
-    <row r="1110"/>
-    <row r="1111"/>
-    <row r="1112"/>
-    <row r="1113"/>
-    <row r="1114"/>
-    <row r="1115"/>
-    <row r="1116"/>
-    <row r="1117"/>
-    <row r="1118"/>
-    <row r="1119"/>
-    <row r="1120"/>
-    <row r="1121"/>
-    <row r="1122"/>
-    <row r="1123"/>
-    <row r="1124"/>
-    <row r="1125"/>
-    <row r="1126"/>
-    <row r="1127"/>
-    <row r="1128"/>
-    <row r="1129"/>
-    <row r="1130"/>
-    <row r="1131"/>
-    <row r="1132"/>
-    <row r="1133"/>
-    <row r="1134"/>
-    <row r="1135"/>
-    <row r="1136"/>
-    <row r="1137"/>
-    <row r="1138"/>
-    <row r="1139"/>
-    <row r="1140"/>
-    <row r="1141"/>
-    <row r="1142"/>
-    <row r="1143"/>
-    <row r="1144"/>
-    <row r="1145"/>
-    <row r="1146"/>
-    <row r="1147"/>
-    <row r="1148"/>
-    <row r="1149"/>
-    <row r="1150"/>
-    <row r="1151"/>
-    <row r="1152"/>
-    <row r="1153"/>
-    <row r="1154"/>
-    <row r="1155"/>
-    <row r="1156"/>
-    <row r="1157"/>
-    <row r="1158"/>
-    <row r="1159"/>
-    <row r="1160"/>
-    <row r="1161"/>
-    <row r="1162"/>
-    <row r="1163"/>
-    <row r="1164"/>
-    <row r="1165"/>
-    <row r="1166"/>
-    <row r="1167"/>
-    <row r="1168"/>
-    <row r="1169"/>
-    <row r="1170"/>
-    <row r="1171"/>
-    <row r="1172"/>
-    <row r="1173"/>
-    <row r="1174"/>
-    <row r="1175"/>
-    <row r="1176"/>
-    <row r="1177"/>
-    <row r="1178"/>
-    <row r="1179"/>
-    <row r="1180"/>
-    <row r="1181"/>
-    <row r="1182"/>
-    <row r="1183"/>
-    <row r="1184"/>
-    <row r="1185"/>
-    <row r="1186"/>
-    <row r="1187"/>
-    <row r="1188"/>
-    <row r="1189"/>
-    <row r="1190"/>
-    <row r="1191"/>
-    <row r="1192"/>
-    <row r="1193"/>
-    <row r="1194"/>
-    <row r="1195"/>
-    <row r="1196"/>
-    <row r="1197"/>
-    <row r="1198"/>
-    <row r="1199"/>
-    <row r="1200"/>
-    <row r="1201"/>
-    <row r="1202"/>
-    <row r="1203"/>
-    <row r="1204"/>
-    <row r="1205"/>
-    <row r="1206"/>
-    <row r="1207"/>
-    <row r="1208"/>
-    <row r="1209"/>
-    <row r="1210"/>
-    <row r="1211"/>
-    <row r="1212"/>
-    <row r="1213"/>
-    <row r="1214"/>
-    <row r="1215"/>
-    <row r="1216"/>
-    <row r="1217"/>
-    <row r="1218"/>
-    <row r="1219"/>
-    <row r="1220"/>
-    <row r="1221"/>
-    <row r="1222"/>
-    <row r="1223"/>
-    <row r="1224"/>
-    <row r="1225"/>
-    <row r="1226"/>
-    <row r="1227"/>
-    <row r="1228"/>
-    <row r="1229"/>
-    <row r="1230"/>
-    <row r="1231"/>
-    <row r="1232"/>
-    <row r="1233"/>
-    <row r="1234"/>
-    <row r="1235"/>
-    <row r="1236"/>
-    <row r="1237"/>
-    <row r="1238"/>
-    <row r="1239"/>
-    <row r="1240"/>
-    <row r="1241"/>
-    <row r="1242"/>
-    <row r="1243"/>
-    <row r="1244"/>
-    <row r="1245"/>
-    <row r="1246"/>
-    <row r="1247"/>
-    <row r="1248"/>
-    <row r="1249"/>
-    <row r="1250"/>
-    <row r="1251"/>
-    <row r="1252"/>
-    <row r="1253"/>
-    <row r="1254"/>
-    <row r="1255"/>
-    <row r="1256"/>
-    <row r="1257"/>
-    <row r="1258"/>
-    <row r="1259"/>
-    <row r="1260"/>
-    <row r="1261"/>
-    <row r="1262"/>
-    <row r="1263"/>
-    <row r="1264"/>
-    <row r="1265"/>
-    <row r="1266"/>
-    <row r="1267"/>
-    <row r="1268"/>
-    <row r="1269"/>
-    <row r="1270"/>
-    <row r="1271"/>
-    <row r="1272"/>
-    <row r="1273"/>
-    <row r="1274"/>
-    <row r="1275"/>
-    <row r="1276"/>
-    <row r="1277"/>
-    <row r="1278"/>
-    <row r="1279"/>
-    <row r="1280"/>
-    <row r="1281"/>
-    <row r="1282"/>
-    <row r="1283"/>
-    <row r="1284"/>
-    <row r="1285"/>
-    <row r="1286"/>
-    <row r="1287"/>
-    <row r="1288"/>
-    <row r="1289"/>
-    <row r="1290"/>
-    <row r="1291"/>
-    <row r="1292"/>
-    <row r="1293"/>
-    <row r="1294"/>
-    <row r="1295"/>
-    <row r="1296"/>
-    <row r="1297"/>
-    <row r="1298"/>
-    <row r="1299"/>
-    <row r="1300"/>
-    <row r="1301"/>
-    <row r="1302"/>
-    <row r="1303"/>
-    <row r="1304"/>
-    <row r="1305"/>
-    <row r="1306"/>
-    <row r="1307"/>
-    <row r="1308"/>
-    <row r="1309"/>
-    <row r="1310"/>
-    <row r="1311"/>
-    <row r="1312"/>
-    <row r="1313"/>
-    <row r="1314"/>
-    <row r="1315"/>
-    <row r="1316"/>
-    <row r="1317"/>
-    <row r="1318"/>
-    <row r="1319"/>
-    <row r="1320"/>
-    <row r="1321"/>
-    <row r="1322"/>
-    <row r="1323"/>
-    <row r="1324"/>
-    <row r="1325"/>
-    <row r="1326"/>
-    <row r="1327"/>
-    <row r="1328"/>
-    <row r="1329"/>
-    <row r="1330"/>
-    <row r="1331"/>
-    <row r="1332"/>
-    <row r="1333"/>
-    <row r="1334"/>
-    <row r="1335"/>
-    <row r="1336"/>
-    <row r="1337"/>
-    <row r="1338"/>
-    <row r="1339"/>
-    <row r="1340"/>
-    <row r="1341"/>
-    <row r="1342"/>
-    <row r="1343"/>
-    <row r="1344"/>
-    <row r="1345"/>
-    <row r="1346"/>
-    <row r="1347"/>
-    <row r="1348"/>
-    <row r="1349"/>
-    <row r="1350"/>
-    <row r="1351"/>
-    <row r="1352"/>
-    <row r="1353"/>
-    <row r="1354"/>
-    <row r="1355"/>
-    <row r="1356"/>
-    <row r="1357"/>
-    <row r="1358"/>
-    <row r="1359"/>
-    <row r="1360"/>
-    <row r="1361"/>
-    <row r="1362"/>
-    <row r="1363"/>
-    <row r="1364"/>
-    <row r="1365"/>
-    <row r="1366"/>
-    <row r="1367"/>
-    <row r="1368"/>
-    <row r="1369"/>
-    <row r="1370"/>
-    <row r="1371"/>
-    <row r="1372"/>
-    <row r="1373"/>
-    <row r="1374"/>
-    <row r="1375"/>
-    <row r="1376"/>
-    <row r="1377"/>
-    <row r="1378"/>
-    <row r="1379"/>
-    <row r="1380"/>
-    <row r="1381"/>
-    <row r="1382"/>
-    <row r="1383"/>
-    <row r="1384"/>
-    <row r="1385"/>
-    <row r="1386"/>
-    <row r="1387"/>
-    <row r="1388"/>
-    <row r="1389"/>
-    <row r="1390"/>
-    <row r="1391"/>
-    <row r="1392"/>
-    <row r="1393"/>
-    <row r="1394"/>
-    <row r="1395"/>
-    <row r="1396"/>
-    <row r="1397"/>
-    <row r="1398"/>
-    <row r="1399"/>
-    <row r="1400"/>
-    <row r="1401"/>
-    <row r="1402"/>
-    <row r="1403"/>
-    <row r="1404"/>
-    <row r="1405"/>
-    <row r="1406"/>
-    <row r="1407"/>
-    <row r="1408"/>
-    <row r="1409"/>
-    <row r="1410"/>
-    <row r="1411"/>
-    <row r="1412"/>
-    <row r="1413"/>
-    <row r="1414"/>
-    <row r="1415"/>
-    <row r="1416"/>
-    <row r="1417"/>
-    <row r="1418"/>
-    <row r="1419"/>
-    <row r="1420"/>
-    <row r="1421"/>
-    <row r="1422"/>
-    <row r="1423"/>
-    <row r="1424"/>
-    <row r="1425"/>
-    <row r="1426"/>
-    <row r="1427"/>
-    <row r="1428"/>
-    <row r="1429"/>
-    <row r="1430"/>
-    <row r="1431"/>
-    <row r="1432"/>
-    <row r="1433"/>
-    <row r="1434"/>
-    <row r="1435"/>
-    <row r="1436"/>
-    <row r="1437"/>
-    <row r="1438"/>
-    <row r="1439"/>
-    <row r="1440"/>
-    <row r="1441"/>
-    <row r="1442"/>
-    <row r="1443"/>
-    <row r="1444"/>
-    <row r="1445"/>
-    <row r="1446"/>
-    <row r="1447"/>
-    <row r="1448"/>
-    <row r="1449"/>
-    <row r="1450"/>
-    <row r="1451"/>
-    <row r="1452"/>
-    <row r="1453"/>
-    <row r="1454"/>
-    <row r="1455"/>
-    <row r="1456"/>
-    <row r="1457"/>
-    <row r="1458"/>
-    <row r="1459"/>
-    <row r="1460"/>
-    <row r="1461"/>
-    <row r="1462"/>
-    <row r="1463"/>
-    <row r="1464"/>
-    <row r="1465"/>
-    <row r="1466"/>
-    <row r="1467"/>
-    <row r="1468"/>
-    <row r="1469"/>
-    <row r="1470"/>
-    <row r="1471"/>
-    <row r="1472"/>
-    <row r="1473"/>
-    <row r="1474"/>
-    <row r="1475"/>
-    <row r="1476"/>
-    <row r="1477"/>
-    <row r="1478"/>
-    <row r="1479"/>
-    <row r="1480"/>
-    <row r="1481"/>
-    <row r="1482"/>
-    <row r="1483"/>
-    <row r="1484"/>
-    <row r="1485"/>
-    <row r="1486"/>
-    <row r="1487"/>
-    <row r="1488"/>
-    <row r="1489"/>
-    <row r="1490"/>
-    <row r="1491"/>
-    <row r="1492"/>
-    <row r="1493"/>
-    <row r="1494"/>
-    <row r="1495"/>
-    <row r="1496"/>
-    <row r="1497"/>
-    <row r="1498"/>
-    <row r="1499"/>
-    <row r="1500"/>
-    <row r="1501"/>
-    <row r="1502"/>
-    <row r="1503"/>
-    <row r="1504"/>
-    <row r="1505"/>
-    <row r="1506"/>
-    <row r="1507"/>
-    <row r="1508"/>
-    <row r="1509"/>
-    <row r="1510"/>
-    <row r="1511"/>
-    <row r="1512"/>
-    <row r="1513"/>
-    <row r="1514"/>
-    <row r="1515"/>
-    <row r="1516"/>
-    <row r="1517"/>
-    <row r="1518"/>
-    <row r="1519"/>
-    <row r="1520"/>
-    <row r="1521"/>
-    <row r="1522"/>
-    <row r="1523"/>
-    <row r="1524"/>
-    <row r="1525"/>
-    <row r="1526"/>
-    <row r="1527"/>
-    <row r="1528"/>
-    <row r="1529"/>
-    <row r="1530"/>
-    <row r="1531"/>
-    <row r="1532"/>
-    <row r="1533"/>
-    <row r="1534"/>
-    <row r="1535"/>
-    <row r="1536"/>
-    <row r="1537"/>
-    <row r="1538"/>
-    <row r="1539"/>
-    <row r="1540"/>
-    <row r="1541"/>
-    <row r="1542"/>
-    <row r="1543"/>
-    <row r="1544"/>
-    <row r="1545"/>
-    <row r="1546"/>
-    <row r="1547"/>
-    <row r="1548"/>
-    <row r="1549"/>
-    <row r="1550"/>
-    <row r="1551"/>
-    <row r="1552"/>
-    <row r="1553"/>
-    <row r="1554"/>
-    <row r="1555"/>
-    <row r="1556"/>
-    <row r="1557"/>
-    <row r="1558"/>
-    <row r="1559"/>
-    <row r="1560"/>
-    <row r="1561"/>
-    <row r="1562"/>
-    <row r="1563"/>
-    <row r="1564"/>
-    <row r="1565"/>
-    <row r="1566"/>
-    <row r="1567"/>
-    <row r="1568"/>
-    <row r="1569"/>
-    <row r="1570"/>
-    <row r="1571"/>
-    <row r="1572"/>
-    <row r="1573"/>
-    <row r="1574"/>
-    <row r="1575"/>
-    <row r="1576"/>
-    <row r="1577"/>
-    <row r="1578"/>
-    <row r="1579"/>
-    <row r="1580"/>
-    <row r="1581"/>
-    <row r="1582"/>
-    <row r="1583"/>
-    <row r="1584"/>
-    <row r="1585"/>
-    <row r="1586"/>
-    <row r="1587"/>
-    <row r="1588"/>
-    <row r="1589"/>
-    <row r="1590"/>
-    <row r="1591"/>
-    <row r="1592"/>
-    <row r="1593"/>
-    <row r="1594"/>
-    <row r="1595"/>
-    <row r="1596"/>
-    <row r="1597"/>
-    <row r="1598"/>
-    <row r="1599"/>
-    <row r="1600"/>
-    <row r="1601"/>
-    <row r="1602"/>
-    <row r="1603"/>
-    <row r="1604"/>
-    <row r="1605"/>
-    <row r="1606"/>
-    <row r="1607"/>
-    <row r="1608"/>
-    <row r="1609"/>
-    <row r="1610"/>
-    <row r="1611"/>
-    <row r="1612"/>
-    <row r="1613"/>
-    <row r="1614"/>
-    <row r="1615"/>
-    <row r="1616"/>
-    <row r="1617"/>
-    <row r="1618"/>
-    <row r="1619"/>
-    <row r="1620"/>
-    <row r="1621"/>
-    <row r="1622"/>
-    <row r="1623"/>
-    <row r="1624"/>
-    <row r="1625"/>
-    <row r="1626"/>
-    <row r="1627"/>
-    <row r="1628"/>
-    <row r="1629"/>
-    <row r="1630"/>
-    <row r="1631"/>
-    <row r="1632"/>
-    <row r="1633"/>
-    <row r="1634"/>
-    <row r="1635"/>
-    <row r="1636"/>
-    <row r="1637"/>
-    <row r="1638"/>
-    <row r="1639"/>
-    <row r="1640"/>
-    <row r="1641"/>
-    <row r="1642"/>
-    <row r="1643"/>
-    <row r="1644"/>
-    <row r="1645"/>
-    <row r="1646"/>
-    <row r="1647"/>
-    <row r="1648"/>
-    <row r="1649"/>
-    <row r="1650"/>
-    <row r="1651"/>
-    <row r="1652"/>
-    <row r="1653"/>
-    <row r="1654"/>
-    <row r="1655"/>
-    <row r="1656"/>
-    <row r="1657"/>
-    <row r="1658"/>
-    <row r="1659"/>
-    <row r="1660"/>
-    <row r="1661"/>
-    <row r="1662"/>
-    <row r="1663"/>
-    <row r="1664"/>
-    <row r="1665"/>
-    <row r="1666"/>
-    <row r="1667"/>
-    <row r="1668"/>
-    <row r="1669"/>
-    <row r="1670"/>
-    <row r="1671"/>
-    <row r="1672"/>
-    <row r="1673"/>
-    <row r="1674"/>
-    <row r="1675"/>
-    <row r="1676"/>
-    <row r="1677"/>
-    <row r="1678"/>
-    <row r="1679"/>
-    <row r="1680"/>
-    <row r="1681"/>
-    <row r="1682"/>
-    <row r="1683"/>
-    <row r="1684"/>
-    <row r="1685"/>
-    <row r="1686"/>
-    <row r="1687"/>
-    <row r="1688"/>
-    <row r="1689"/>
-    <row r="1690"/>
-    <row r="1691"/>
-    <row r="1692"/>
-    <row r="1693"/>
-    <row r="1694"/>
-    <row r="1695"/>
-    <row r="1696"/>
-    <row r="1697"/>
-    <row r="1698"/>
-    <row r="1699"/>
-    <row r="1700"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
